--- a/public/data/Mr Tunde Martins AKande @60 Guest List.xlsx
+++ b/public/data/Mr Tunde Martins AKande @60 Guest List.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="719">
   <si>
     <t>Guest List</t>
   </si>
@@ -636,7 +636,7 @@
     <t>MR. JIMMY OLUSOLA</t>
   </si>
   <si>
-    <t>SENATOR GBENGA ASHAFA (Senator of the Fedral Rep of Nigeria</t>
+    <t>SENATOR GBENGA ASHAFA (Senator of the Fedral Rep of Nigeria)</t>
   </si>
   <si>
     <t>H.E BABATUNDE FASHOLA (Former Governor Lagos State)</t>
@@ -738,7 +738,7 @@
     <t>WCS</t>
   </si>
   <si>
-    <t xml:space="preserve">Boye Etchie </t>
+    <t xml:space="preserve">Mr Boye Etchie </t>
   </si>
   <si>
     <t>750659-7109</t>
@@ -774,7 +774,7 @@
     <t>YABATECH</t>
   </si>
   <si>
-    <t>Mrs Abayomi Nash</t>
+    <t>Mrs Gloria Rhodes-Nash</t>
   </si>
   <si>
     <t>Madam Maureen Nme Ani</t>
@@ -1029,7 +1029,7 @@
     <t xml:space="preserve"> Mrs Kunle Olusemade</t>
   </si>
   <si>
-    <t>Pastor &amp; Mrs Akinrelure Joshua</t>
+    <t>Pastor Akinrelure Joshua</t>
   </si>
   <si>
     <t>Mrs Akinrelure Joshua</t>
@@ -1149,7 +1149,7 @@
     <t>Mrs Felix Olorunda</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Tunde Adebayo</t>
+    <t>Mr Tunde Adebayo</t>
   </si>
   <si>
     <t>Mrs Tunde Adebayo</t>
@@ -1266,7 +1266,7 @@
     <t>Sola Abuja</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Wale Omolola Shoyoola</t>
+    <t>Mr Wale Omolola Shoyoola</t>
   </si>
   <si>
     <t>In-law</t>
@@ -1290,7 +1290,7 @@
     <t>Mrs Akande Foluke Christiana</t>
   </si>
   <si>
-    <t>Mis Oreoluwa Akande</t>
+    <t>Miss Oreoluwa Akande</t>
   </si>
   <si>
     <t>Miss Esther Akande</t>
@@ -1626,7 +1626,7 @@
     <t>Bukky Akinola</t>
   </si>
   <si>
-    <t>Peju Lawal</t>
+    <t>Femi Lawal</t>
   </si>
   <si>
     <t xml:space="preserve"> Peju Lawal</t>
@@ -1668,7 +1668,7 @@
     <t>Table 44  (Heritage Philharmonic)</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Opabiyi</t>
+    <t>Mr Opabiyi</t>
   </si>
   <si>
     <t>Mrs Opabiyi</t>
@@ -1842,7 +1842,7 @@
     <t>Mrs Dapo Olaiya</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Deji Akinlofa Maryland USA</t>
+    <t>Mr Deji Akinlofa Maryland USA</t>
   </si>
   <si>
     <t>4443629-2628</t>
@@ -1869,13 +1869,13 @@
     <t>Mrs Dolapo Olikuntuyi</t>
   </si>
   <si>
-    <t>Engr &amp; Mrs Wale Oni</t>
+    <t>Engr Wale Oni</t>
   </si>
   <si>
     <t>Mrs Wale Oni</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Ernest Akinlola</t>
+    <t>Mr Ernest Akinlola</t>
   </si>
   <si>
     <t>Mrs Ernest Akinlola</t>
@@ -1950,7 +1950,7 @@
     <t>Mr Gani Adeshina</t>
   </si>
   <si>
-    <t>Mr &amp; Mrs Adelanke Olabisi IPU Ikaram</t>
+    <t>Mr Adelanke Olabisi IPU Ikaram</t>
   </si>
   <si>
     <t xml:space="preserve"> Mrs Adelanke Olabisi IPU Ikaram</t>
@@ -2115,6 +2115,9 @@
     <t xml:space="preserve">Table 6 ( Realty Royalty) </t>
   </si>
   <si>
+    <t xml:space="preserve">Boye Etchie </t>
+  </si>
+  <si>
     <t>Mrs Adeola Olusodo (ED LSDPC)</t>
   </si>
   <si>
@@ -2133,27 +2136,51 @@
     <t>Table 16 (Island View)</t>
   </si>
   <si>
+    <t>SENATOR GBENGA ASHAFA (Senator of the Fedral Rep of Nigeria</t>
+  </si>
+  <si>
     <t>Table 17 (Lagos Skyline)</t>
   </si>
   <si>
     <t>Table 18 (Coastview Circle)</t>
   </si>
   <si>
+    <t>Mrs Abayomi Nash</t>
+  </si>
+  <si>
+    <t>Pastor &amp; Mrs Akinrelure Joshua</t>
+  </si>
+  <si>
     <t>Pastor &amp; Mrs Felix Olorunda</t>
   </si>
   <si>
+    <t>Mr &amp; Mrs Tunde Adebayo</t>
+  </si>
+  <si>
     <t>Rev &amp; Mrs Okey Ikeri</t>
   </si>
   <si>
     <t>Mr Seun &amp; Mrs Adenike Peters</t>
   </si>
   <si>
+    <t>Mr &amp; Mrs Wale Omolola Shoyoola</t>
+  </si>
+  <si>
+    <t>Mis Oreoluwa Akande</t>
+  </si>
+  <si>
     <t>Tabke 37 ( Golden Groove)</t>
   </si>
   <si>
     <t>Ttable 40 (Disco Inferno)</t>
   </si>
   <si>
+    <t>Peju Lawal</t>
+  </si>
+  <si>
+    <t>Mr &amp; Mrs Opabiyi</t>
+  </si>
+  <si>
     <t>Mr &amp; Mrs Momoh Amoseola</t>
   </si>
   <si>
@@ -2163,13 +2190,25 @@
     <t>Mr &amp; Mrs Dapo Olaiya</t>
   </si>
   <si>
+    <t>Mr &amp; Mrs Deji Akinlofa Maryland USA</t>
+  </si>
+  <si>
     <t>Mr &amp; Mrs Dipo Fakorede</t>
   </si>
   <si>
     <t>Mr &amp; Mrs Dolapo Olikuntuyi</t>
   </si>
   <si>
+    <t>Engr &amp; Mrs Wale Oni</t>
+  </si>
+  <si>
+    <t>Mr &amp; Mrs Ernest Akinlola</t>
+  </si>
+  <si>
     <t>Mr &amp; Mrs Kemi OJO Stanbic IBTC</t>
+  </si>
+  <si>
+    <t>Mr &amp; Mrs Adelanke Olabisi IPU Ikaram</t>
   </si>
   <si>
     <t>Mr Adeshina Oluwaseun</t>
@@ -10434,13 +10473,11 @@
       <c r="K323" s="5"/>
     </row>
     <row r="324">
-      <c r="A324" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="B324" s="25"/>
-      <c r="C324" s="26"/>
-      <c r="D324" s="26"/>
-      <c r="E324" s="26"/>
+      <c r="A324" s="9"/>
+      <c r="B324" s="10"/>
+      <c r="C324" s="14"/>
+      <c r="D324" s="14"/>
+      <c r="E324" s="14"/>
       <c r="F324" s="5"/>
       <c r="G324" s="5"/>
       <c r="H324" s="5"/>
@@ -10449,21 +10486,13 @@
       <c r="K324" s="5"/>
     </row>
     <row r="325">
-      <c r="A325" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="B325" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C325" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="D325" s="14">
-        <v>8.033251726E9</v>
-      </c>
-      <c r="E325" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A325" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B325" s="25"/>
+      <c r="C325" s="26"/>
+      <c r="D325" s="26"/>
+      <c r="E325" s="26"/>
       <c r="F325" s="5"/>
       <c r="G325" s="5"/>
       <c r="H325" s="5"/>
@@ -10473,7 +10502,7 @@
     </row>
     <row r="326">
       <c r="A326" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B326" s="13">
         <v>1.0</v>
@@ -10496,7 +10525,7 @@
     </row>
     <row r="327">
       <c r="A327" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B327" s="13">
         <v>1.0</v>
@@ -10505,7 +10534,7 @@
         <v>352</v>
       </c>
       <c r="D327" s="14">
-        <v>8.075744557E9</v>
+        <v>8.033251726E9</v>
       </c>
       <c r="E327" s="14">
         <v>234.0</v>
@@ -10519,16 +10548,16 @@
     </row>
     <row r="328">
       <c r="A328" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B328" s="13">
         <v>1.0</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D328" s="14">
-        <v>8.0254998E9</v>
+        <v>8.075744557E9</v>
       </c>
       <c r="E328" s="14">
         <v>234.0</v>
@@ -10542,16 +10571,16 @@
     </row>
     <row r="329">
       <c r="A329" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B329" s="13">
         <v>1.0</v>
       </c>
       <c r="C329" s="14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D329" s="14">
-        <v>8.034183929E9</v>
+        <v>8.0254998E9</v>
       </c>
       <c r="E329" s="14">
         <v>234.0</v>
@@ -10562,36 +10591,21 @@
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
       <c r="K329" s="5"/>
-      <c r="L329" s="27"/>
-      <c r="M329" s="27"/>
-      <c r="N329" s="27"/>
-      <c r="O329" s="27"/>
-      <c r="P329" s="27"/>
-      <c r="Q329" s="27"/>
-      <c r="R329" s="27"/>
-      <c r="S329" s="27"/>
-      <c r="T329" s="27"/>
-      <c r="U329" s="27"/>
-      <c r="V329" s="27"/>
-      <c r="W329" s="27"/>
-      <c r="X329" s="27"/>
-      <c r="Y329" s="27"/>
-      <c r="Z329" s="27"/>
     </row>
     <row r="330">
-      <c r="A330" s="36" t="s">
-        <v>359</v>
-      </c>
-      <c r="B330" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="C330" s="13" t="s">
-        <v>179</v>
+      <c r="A330" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B330" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C330" s="14" t="s">
+        <v>358</v>
       </c>
       <c r="D330" s="14">
-        <v>8.023202611E9</v>
-      </c>
-      <c r="E330" s="13">
+        <v>8.034183929E9</v>
+      </c>
+      <c r="E330" s="14">
         <v>234.0</v>
       </c>
       <c r="F330" s="5"/>
@@ -10600,22 +10614,37 @@
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
       <c r="K330" s="5"/>
+      <c r="L330" s="27"/>
+      <c r="M330" s="27"/>
+      <c r="N330" s="27"/>
+      <c r="O330" s="27"/>
+      <c r="P330" s="27"/>
+      <c r="Q330" s="27"/>
+      <c r="R330" s="27"/>
+      <c r="S330" s="27"/>
+      <c r="T330" s="27"/>
+      <c r="U330" s="27"/>
+      <c r="V330" s="27"/>
+      <c r="W330" s="27"/>
+      <c r="X330" s="27"/>
+      <c r="Y330" s="27"/>
+      <c r="Z330" s="27"/>
     </row>
     <row r="331">
       <c r="A331" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B331" s="51">
         <v>1.0</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="D331" s="14" t="s">
-        <v>362</v>
+        <v>179</v>
+      </c>
+      <c r="D331" s="14">
+        <v>8.023202611E9</v>
       </c>
       <c r="E331" s="13">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F331" s="5"/>
       <c r="G331" s="5"/>
@@ -10625,20 +10654,20 @@
       <c r="K331" s="5"/>
     </row>
     <row r="332">
-      <c r="A332" s="29" t="s">
-        <v>315</v>
-      </c>
-      <c r="B332" s="13">
+      <c r="A332" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="B332" s="51">
         <v>1.0</v>
       </c>
       <c r="C332" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D332" s="14">
-        <v>8.171622577E9</v>
-      </c>
-      <c r="E332" s="14">
-        <v>234.0</v>
+        <v>361</v>
+      </c>
+      <c r="D332" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E332" s="13">
+        <v>44.0</v>
       </c>
       <c r="F332" s="5"/>
       <c r="G332" s="5"/>
@@ -10648,17 +10677,17 @@
       <c r="K332" s="5"/>
     </row>
     <row r="333">
-      <c r="A333" s="12" t="s">
-        <v>363</v>
+      <c r="A333" s="29" t="s">
+        <v>315</v>
       </c>
       <c r="B333" s="13">
         <v>1.0</v>
       </c>
-      <c r="C333" s="14" t="s">
-        <v>328</v>
+      <c r="C333" s="13" t="s">
+        <v>179</v>
       </c>
       <c r="D333" s="14">
-        <v>8.068156852E9</v>
+        <v>8.171622577E9</v>
       </c>
       <c r="E333" s="14">
         <v>234.0</v>
@@ -10671,17 +10700,17 @@
       <c r="K333" s="5"/>
     </row>
     <row r="334">
-      <c r="A334" s="36" t="s">
-        <v>364</v>
-      </c>
-      <c r="B334" s="37">
-        <v>1.0</v>
-      </c>
-      <c r="C334" s="13" t="s">
-        <v>179</v>
+      <c r="A334" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B334" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C334" s="14" t="s">
+        <v>328</v>
       </c>
       <c r="D334" s="14">
-        <v>9.0200263E9</v>
+        <v>8.068156852E9</v>
       </c>
       <c r="E334" s="14">
         <v>234.0</v>
@@ -10694,11 +10723,21 @@
       <c r="K334" s="5"/>
     </row>
     <row r="335">
-      <c r="A335" s="36"/>
-      <c r="B335" s="37"/>
-      <c r="C335" s="13"/>
-      <c r="D335" s="14"/>
-      <c r="E335" s="14"/>
+      <c r="A335" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="B335" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="C335" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D335" s="14">
+        <v>9.0200263E9</v>
+      </c>
+      <c r="E335" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F335" s="5"/>
       <c r="G335" s="5"/>
       <c r="H335" s="5"/>
@@ -10707,13 +10746,11 @@
       <c r="K335" s="5"/>
     </row>
     <row r="336">
-      <c r="A336" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="B336" s="25"/>
-      <c r="C336" s="26"/>
-      <c r="D336" s="26"/>
-      <c r="E336" s="26"/>
+      <c r="A336" s="36"/>
+      <c r="B336" s="37"/>
+      <c r="C336" s="13"/>
+      <c r="D336" s="14"/>
+      <c r="E336" s="14"/>
       <c r="F336" s="5"/>
       <c r="G336" s="5"/>
       <c r="H336" s="5"/>
@@ -10722,21 +10759,13 @@
       <c r="K336" s="5"/>
     </row>
     <row r="337">
-      <c r="A337" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B337" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C337" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D337" s="14">
-        <v>8.034942134E9</v>
-      </c>
-      <c r="E337" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A337" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="B337" s="25"/>
+      <c r="C337" s="26"/>
+      <c r="D337" s="26"/>
+      <c r="E337" s="26"/>
       <c r="F337" s="5"/>
       <c r="G337" s="5"/>
       <c r="H337" s="5"/>
@@ -10746,7 +10775,7 @@
     </row>
     <row r="338">
       <c r="A338" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B338" s="13">
         <v>1.0</v>
@@ -10755,7 +10784,7 @@
         <v>346</v>
       </c>
       <c r="D338" s="14">
-        <v>8.033022835E9</v>
+        <v>8.034942134E9</v>
       </c>
       <c r="E338" s="14">
         <v>234.0</v>
@@ -10769,7 +10798,7 @@
     </row>
     <row r="339">
       <c r="A339" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B339" s="13">
         <v>1.0</v>
@@ -10778,7 +10807,7 @@
         <v>346</v>
       </c>
       <c r="D339" s="14">
-        <v>8.033057313E9</v>
+        <v>8.033022835E9</v>
       </c>
       <c r="E339" s="14">
         <v>234.0</v>
@@ -10792,7 +10821,7 @@
     </row>
     <row r="340">
       <c r="A340" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B340" s="13">
         <v>1.0</v>
@@ -10815,7 +10844,7 @@
     </row>
     <row r="341">
       <c r="A341" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B341" s="13">
         <v>1.0</v>
@@ -10824,7 +10853,7 @@
         <v>346</v>
       </c>
       <c r="D341" s="14">
-        <v>8.032259294E9</v>
+        <v>8.033057313E9</v>
       </c>
       <c r="E341" s="14">
         <v>234.0</v>
@@ -10838,7 +10867,7 @@
     </row>
     <row r="342">
       <c r="A342" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B342" s="13">
         <v>1.0</v>
@@ -10861,7 +10890,7 @@
     </row>
     <row r="343">
       <c r="A343" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B343" s="13">
         <v>1.0</v>
@@ -10870,7 +10899,7 @@
         <v>346</v>
       </c>
       <c r="D343" s="14">
-        <v>8.03350573E9</v>
+        <v>8.032259294E9</v>
       </c>
       <c r="E343" s="14">
         <v>234.0</v>
@@ -10881,25 +10910,10 @@
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
       <c r="K343" s="5"/>
-      <c r="L343" s="27"/>
-      <c r="M343" s="27"/>
-      <c r="N343" s="27"/>
-      <c r="O343" s="27"/>
-      <c r="P343" s="27"/>
-      <c r="Q343" s="27"/>
-      <c r="R343" s="27"/>
-      <c r="S343" s="27"/>
-      <c r="T343" s="27"/>
-      <c r="U343" s="27"/>
-      <c r="V343" s="27"/>
-      <c r="W343" s="27"/>
-      <c r="X343" s="27"/>
-      <c r="Y343" s="27"/>
-      <c r="Z343" s="27"/>
     </row>
     <row r="344">
       <c r="A344" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B344" s="13">
         <v>1.0</v>
@@ -10937,16 +10951,16 @@
     </row>
     <row r="345">
       <c r="A345" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B345" s="13">
         <v>1.0</v>
       </c>
       <c r="C345" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D345" s="13">
-        <v>8.023166383E9</v>
+        <v>346</v>
+      </c>
+      <c r="D345" s="14">
+        <v>8.03350573E9</v>
       </c>
       <c r="E345" s="14">
         <v>234.0</v>
@@ -10957,10 +10971,25 @@
       <c r="I345" s="5"/>
       <c r="J345" s="5"/>
       <c r="K345" s="5"/>
+      <c r="L345" s="27"/>
+      <c r="M345" s="27"/>
+      <c r="N345" s="27"/>
+      <c r="O345" s="27"/>
+      <c r="P345" s="27"/>
+      <c r="Q345" s="27"/>
+      <c r="R345" s="27"/>
+      <c r="S345" s="27"/>
+      <c r="T345" s="27"/>
+      <c r="U345" s="27"/>
+      <c r="V345" s="27"/>
+      <c r="W345" s="27"/>
+      <c r="X345" s="27"/>
+      <c r="Y345" s="27"/>
+      <c r="Z345" s="27"/>
     </row>
     <row r="346">
-      <c r="A346" s="29" t="s">
-        <v>376</v>
+      <c r="A346" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="B346" s="13">
         <v>1.0</v>
@@ -10982,11 +11011,21 @@
       <c r="K346" s="5"/>
     </row>
     <row r="347">
-      <c r="A347" s="29"/>
-      <c r="B347" s="13"/>
-      <c r="C347" s="14"/>
-      <c r="D347" s="13"/>
-      <c r="E347" s="14"/>
+      <c r="A347" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="B347" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C347" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D347" s="13">
+        <v>8.023166383E9</v>
+      </c>
+      <c r="E347" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F347" s="5"/>
       <c r="G347" s="5"/>
       <c r="H347" s="5"/>
@@ -10995,61 +11034,51 @@
       <c r="K347" s="5"/>
     </row>
     <row r="348">
-      <c r="A348" s="47" t="s">
+      <c r="A348" s="29"/>
+      <c r="B348" s="13"/>
+      <c r="C348" s="14"/>
+      <c r="D348" s="13"/>
+      <c r="E348" s="14"/>
+      <c r="F348" s="5"/>
+      <c r="G348" s="5"/>
+      <c r="H348" s="5"/>
+      <c r="I348" s="5"/>
+      <c r="J348" s="5"/>
+      <c r="K348" s="5"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="47" t="s">
         <v>377</v>
       </c>
-      <c r="B348" s="48"/>
-      <c r="C348" s="48"/>
-      <c r="D348" s="48"/>
-      <c r="E348" s="48"/>
-      <c r="F348" s="27"/>
-      <c r="G348" s="27"/>
-      <c r="H348" s="27"/>
-      <c r="I348" s="27"/>
-      <c r="J348" s="27"/>
-      <c r="K348" s="27"/>
-      <c r="L348" s="27"/>
-      <c r="M348" s="27"/>
-      <c r="N348" s="27"/>
-      <c r="O348" s="27"/>
-      <c r="P348" s="27"/>
-      <c r="Q348" s="27"/>
-      <c r="R348" s="27"/>
-      <c r="S348" s="27"/>
-      <c r="T348" s="27"/>
-      <c r="U348" s="27"/>
-      <c r="V348" s="27"/>
-      <c r="W348" s="27"/>
-      <c r="X348" s="27"/>
-      <c r="Y348" s="27"/>
-      <c r="Z348" s="27"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="B349" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C349" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D349" s="14">
-        <v>7.065512125E9</v>
-      </c>
-      <c r="E349" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F349" s="5"/>
-      <c r="G349" s="5"/>
-      <c r="H349" s="5"/>
-      <c r="I349" s="5"/>
-      <c r="J349" s="5"/>
-      <c r="K349" s="5"/>
+      <c r="B349" s="48"/>
+      <c r="C349" s="48"/>
+      <c r="D349" s="48"/>
+      <c r="E349" s="48"/>
+      <c r="F349" s="27"/>
+      <c r="G349" s="27"/>
+      <c r="H349" s="27"/>
+      <c r="I349" s="27"/>
+      <c r="J349" s="27"/>
+      <c r="K349" s="27"/>
+      <c r="L349" s="27"/>
+      <c r="M349" s="27"/>
+      <c r="N349" s="27"/>
+      <c r="O349" s="27"/>
+      <c r="P349" s="27"/>
+      <c r="Q349" s="27"/>
+      <c r="R349" s="27"/>
+      <c r="S349" s="27"/>
+      <c r="T349" s="27"/>
+      <c r="U349" s="27"/>
+      <c r="V349" s="27"/>
+      <c r="W349" s="27"/>
+      <c r="X349" s="27"/>
+      <c r="Y349" s="27"/>
+      <c r="Z349" s="27"/>
     </row>
     <row r="350">
       <c r="A350" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B350" s="13">
         <v>1.0</v>
@@ -11058,7 +11087,7 @@
         <v>375</v>
       </c>
       <c r="D350" s="14">
-        <v>9.081192203E9</v>
+        <v>7.065512125E9</v>
       </c>
       <c r="E350" s="14">
         <v>234.0</v>
@@ -11072,7 +11101,7 @@
     </row>
     <row r="351">
       <c r="A351" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B351" s="13">
         <v>1.0</v>
@@ -11081,7 +11110,7 @@
         <v>375</v>
       </c>
       <c r="D351" s="14">
-        <v>8.054091505E9</v>
+        <v>9.081192203E9</v>
       </c>
       <c r="E351" s="14">
         <v>234.0</v>
@@ -11095,7 +11124,7 @@
     </row>
     <row r="352">
       <c r="A352" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B352" s="13">
         <v>1.0</v>
@@ -11104,10 +11133,10 @@
         <v>375</v>
       </c>
       <c r="D352" s="14">
-        <v>7.956311081E9</v>
+        <v>8.054091505E9</v>
       </c>
       <c r="E352" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F352" s="5"/>
       <c r="G352" s="5"/>
@@ -11118,7 +11147,7 @@
     </row>
     <row r="353">
       <c r="A353" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B353" s="13">
         <v>1.0</v>
@@ -11127,10 +11156,10 @@
         <v>375</v>
       </c>
       <c r="D353" s="14">
-        <v>8.023070734E9</v>
+        <v>7.956311081E9</v>
       </c>
       <c r="E353" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F353" s="5"/>
       <c r="G353" s="5"/>
@@ -11138,25 +11167,10 @@
       <c r="I353" s="5"/>
       <c r="J353" s="5"/>
       <c r="K353" s="5"/>
-      <c r="L353" s="27"/>
-      <c r="M353" s="27"/>
-      <c r="N353" s="27"/>
-      <c r="O353" s="27"/>
-      <c r="P353" s="27"/>
-      <c r="Q353" s="27"/>
-      <c r="R353" s="27"/>
-      <c r="S353" s="27"/>
-      <c r="T353" s="27"/>
-      <c r="U353" s="27"/>
-      <c r="V353" s="27"/>
-      <c r="W353" s="27"/>
-      <c r="X353" s="27"/>
-      <c r="Y353" s="27"/>
-      <c r="Z353" s="27"/>
     </row>
     <row r="354">
       <c r="A354" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B354" s="13">
         <v>1.0</v>
@@ -11165,7 +11179,7 @@
         <v>375</v>
       </c>
       <c r="D354" s="14">
-        <v>8.023309846E9</v>
+        <v>8.023070734E9</v>
       </c>
       <c r="E354" s="14">
         <v>234.0</v>
@@ -11176,10 +11190,25 @@
       <c r="I354" s="5"/>
       <c r="J354" s="5"/>
       <c r="K354" s="5"/>
+      <c r="L354" s="27"/>
+      <c r="M354" s="27"/>
+      <c r="N354" s="27"/>
+      <c r="O354" s="27"/>
+      <c r="P354" s="27"/>
+      <c r="Q354" s="27"/>
+      <c r="R354" s="27"/>
+      <c r="S354" s="27"/>
+      <c r="T354" s="27"/>
+      <c r="U354" s="27"/>
+      <c r="V354" s="27"/>
+      <c r="W354" s="27"/>
+      <c r="X354" s="27"/>
+      <c r="Y354" s="27"/>
+      <c r="Z354" s="27"/>
     </row>
     <row r="355">
       <c r="A355" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B355" s="13">
         <v>1.0</v>
@@ -11201,8 +11230,8 @@
       <c r="K355" s="5"/>
     </row>
     <row r="356">
-      <c r="A356" s="23" t="s">
-        <v>385</v>
+      <c r="A356" s="12" t="s">
+        <v>384</v>
       </c>
       <c r="B356" s="13">
         <v>1.0</v>
@@ -11211,7 +11240,7 @@
         <v>375</v>
       </c>
       <c r="D356" s="14">
-        <v>8.023405394E9</v>
+        <v>8.023309846E9</v>
       </c>
       <c r="E356" s="14">
         <v>234.0</v>
@@ -11225,7 +11254,7 @@
     </row>
     <row r="357">
       <c r="A357" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B357" s="13">
         <v>1.0</v>
@@ -11247,17 +11276,17 @@
       <c r="K357" s="5"/>
     </row>
     <row r="358">
-      <c r="A358" s="29" t="s">
-        <v>387</v>
+      <c r="A358" s="23" t="s">
+        <v>386</v>
       </c>
       <c r="B358" s="13">
         <v>1.0</v>
       </c>
       <c r="C358" s="14" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D358" s="14">
-        <v>8.075048968E9</v>
+        <v>8.023405394E9</v>
       </c>
       <c r="E358" s="14">
         <v>234.0</v>
@@ -11270,11 +11299,21 @@
       <c r="K358" s="5"/>
     </row>
     <row r="359">
-      <c r="A359" s="29"/>
-      <c r="B359" s="13"/>
-      <c r="C359" s="14"/>
-      <c r="D359" s="14"/>
-      <c r="E359" s="14"/>
+      <c r="A359" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B359" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C359" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D359" s="14">
+        <v>8.075048968E9</v>
+      </c>
+      <c r="E359" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F359" s="5"/>
       <c r="G359" s="5"/>
       <c r="H359" s="5"/>
@@ -11283,13 +11322,11 @@
       <c r="K359" s="5"/>
     </row>
     <row r="360">
-      <c r="A360" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="B360" s="25"/>
-      <c r="C360" s="26"/>
-      <c r="D360" s="26"/>
-      <c r="E360" s="26"/>
+      <c r="A360" s="29"/>
+      <c r="B360" s="13"/>
+      <c r="C360" s="14"/>
+      <c r="D360" s="14"/>
+      <c r="E360" s="14"/>
       <c r="F360" s="5"/>
       <c r="G360" s="5"/>
       <c r="H360" s="5"/>
@@ -11298,21 +11335,13 @@
       <c r="K360" s="5"/>
     </row>
     <row r="361">
-      <c r="A361" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="B361" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C361" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="D361" s="14">
-        <v>7.033311706E9</v>
-      </c>
-      <c r="E361" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A361" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="B361" s="25"/>
+      <c r="C361" s="26"/>
+      <c r="D361" s="26"/>
+      <c r="E361" s="26"/>
       <c r="F361" s="5"/>
       <c r="G361" s="5"/>
       <c r="H361" s="5"/>
@@ -11322,7 +11351,7 @@
     </row>
     <row r="362">
       <c r="A362" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B362" s="13">
         <v>1.0</v>
@@ -11345,7 +11374,7 @@
     </row>
     <row r="363">
       <c r="A363" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B363" s="13">
         <v>1.0</v>
@@ -11354,7 +11383,7 @@
         <v>391</v>
       </c>
       <c r="D363" s="14">
-        <v>8.032196962E9</v>
+        <v>7.033311706E9</v>
       </c>
       <c r="E363" s="14">
         <v>234.0</v>
@@ -11368,7 +11397,7 @@
     </row>
     <row r="364">
       <c r="A364" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B364" s="13">
         <v>1.0</v>
@@ -11377,7 +11406,7 @@
         <v>391</v>
       </c>
       <c r="D364" s="14">
-        <v>8.038269145E9</v>
+        <v>8.032196962E9</v>
       </c>
       <c r="E364" s="14">
         <v>234.0</v>
@@ -11391,7 +11420,7 @@
     </row>
     <row r="365">
       <c r="A365" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B365" s="13">
         <v>1.0</v>
@@ -11400,7 +11429,7 @@
         <v>391</v>
       </c>
       <c r="D365" s="14">
-        <v>8.037632224E9</v>
+        <v>8.038269145E9</v>
       </c>
       <c r="E365" s="14">
         <v>234.0</v>
@@ -11411,25 +11440,10 @@
       <c r="I365" s="5"/>
       <c r="J365" s="5"/>
       <c r="K365" s="5"/>
-      <c r="L365" s="27"/>
-      <c r="M365" s="27"/>
-      <c r="N365" s="27"/>
-      <c r="O365" s="27"/>
-      <c r="P365" s="27"/>
-      <c r="Q365" s="27"/>
-      <c r="R365" s="27"/>
-      <c r="S365" s="27"/>
-      <c r="T365" s="27"/>
-      <c r="U365" s="27"/>
-      <c r="V365" s="27"/>
-      <c r="W365" s="27"/>
-      <c r="X365" s="27"/>
-      <c r="Y365" s="27"/>
-      <c r="Z365" s="27"/>
     </row>
     <row r="366">
       <c r="A366" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B366" s="13">
         <v>1.0</v>
@@ -11438,7 +11452,7 @@
         <v>391</v>
       </c>
       <c r="D366" s="14">
-        <v>8.029108265E9</v>
+        <v>8.037632224E9</v>
       </c>
       <c r="E366" s="14">
         <v>234.0</v>
@@ -11449,10 +11463,25 @@
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
       <c r="K366" s="5"/>
+      <c r="L366" s="27"/>
+      <c r="M366" s="27"/>
+      <c r="N366" s="27"/>
+      <c r="O366" s="27"/>
+      <c r="P366" s="27"/>
+      <c r="Q366" s="27"/>
+      <c r="R366" s="27"/>
+      <c r="S366" s="27"/>
+      <c r="T366" s="27"/>
+      <c r="U366" s="27"/>
+      <c r="V366" s="27"/>
+      <c r="W366" s="27"/>
+      <c r="X366" s="27"/>
+      <c r="Y366" s="27"/>
+      <c r="Z366" s="27"/>
     </row>
     <row r="367">
       <c r="A367" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B367" s="13">
         <v>1.0</v>
@@ -11461,7 +11490,7 @@
         <v>391</v>
       </c>
       <c r="D367" s="14">
-        <v>9.159868421E9</v>
+        <v>8.029108265E9</v>
       </c>
       <c r="E367" s="14">
         <v>234.0</v>
@@ -11475,7 +11504,7 @@
     </row>
     <row r="368">
       <c r="A368" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B368" s="13">
         <v>1.0</v>
@@ -11498,7 +11527,7 @@
     </row>
     <row r="369">
       <c r="A369" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B369" s="13">
         <v>1.0</v>
@@ -11507,7 +11536,7 @@
         <v>391</v>
       </c>
       <c r="D369" s="14">
-        <v>7.036281456E9</v>
+        <v>9.159868421E9</v>
       </c>
       <c r="E369" s="14">
         <v>234.0</v>
@@ -11521,7 +11550,7 @@
     </row>
     <row r="370">
       <c r="A370" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B370" s="13">
         <v>1.0</v>
@@ -11543,11 +11572,21 @@
       <c r="K370" s="5"/>
     </row>
     <row r="371">
-      <c r="A371" s="12"/>
-      <c r="B371" s="13"/>
-      <c r="C371" s="14"/>
-      <c r="D371" s="14"/>
-      <c r="E371" s="14"/>
+      <c r="A371" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B371" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C371" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D371" s="14">
+        <v>7.036281456E9</v>
+      </c>
+      <c r="E371" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F371" s="5"/>
       <c r="G371" s="5"/>
       <c r="H371" s="5"/>
@@ -11556,13 +11595,11 @@
       <c r="K371" s="5"/>
     </row>
     <row r="372">
-      <c r="A372" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="B372" s="25"/>
-      <c r="C372" s="26"/>
-      <c r="D372" s="26"/>
-      <c r="E372" s="26"/>
+      <c r="A372" s="12"/>
+      <c r="B372" s="13"/>
+      <c r="C372" s="14"/>
+      <c r="D372" s="14"/>
+      <c r="E372" s="14"/>
       <c r="F372" s="5"/>
       <c r="G372" s="5"/>
       <c r="H372" s="5"/>
@@ -11571,21 +11608,13 @@
       <c r="K372" s="5"/>
     </row>
     <row r="373">
-      <c r="A373" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="B373" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C373" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="D373" s="14">
-        <v>8.036120862E9</v>
-      </c>
-      <c r="E373" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A373" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="B373" s="25"/>
+      <c r="C373" s="26"/>
+      <c r="D373" s="26"/>
+      <c r="E373" s="26"/>
       <c r="F373" s="5"/>
       <c r="G373" s="5"/>
       <c r="H373" s="5"/>
@@ -11595,7 +11624,7 @@
     </row>
     <row r="374">
       <c r="A374" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B374" s="13">
         <v>1.0</v>
@@ -11618,7 +11647,7 @@
     </row>
     <row r="375">
       <c r="A375" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B375" s="13">
         <v>1.0</v>
@@ -11627,7 +11656,7 @@
         <v>391</v>
       </c>
       <c r="D375" s="14">
-        <v>9.019404989E9</v>
+        <v>8.036120862E9</v>
       </c>
       <c r="E375" s="14">
         <v>234.0</v>
@@ -11641,7 +11670,7 @@
     </row>
     <row r="376">
       <c r="A376" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B376" s="13">
         <v>1.0</v>
@@ -11650,7 +11679,7 @@
         <v>391</v>
       </c>
       <c r="D376" s="14">
-        <v>8.034040437E9</v>
+        <v>9.019404989E9</v>
       </c>
       <c r="E376" s="14">
         <v>234.0</v>
@@ -11664,7 +11693,7 @@
     </row>
     <row r="377">
       <c r="A377" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B377" s="13">
         <v>1.0</v>
@@ -11687,7 +11716,7 @@
     </row>
     <row r="378">
       <c r="A378" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B378" s="13">
         <v>1.0</v>
@@ -11696,7 +11725,7 @@
         <v>391</v>
       </c>
       <c r="D378" s="14">
-        <v>9.095607784E9</v>
+        <v>8.034040437E9</v>
       </c>
       <c r="E378" s="14">
         <v>234.0</v>
@@ -11710,7 +11739,7 @@
     </row>
     <row r="379">
       <c r="A379" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B379" s="13">
         <v>1.0</v>
@@ -11718,8 +11747,8 @@
       <c r="C379" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D379" s="13">
-        <v>7.031890883E9</v>
+      <c r="D379" s="14">
+        <v>9.095607784E9</v>
       </c>
       <c r="E379" s="14">
         <v>234.0</v>
@@ -11733,16 +11762,16 @@
     </row>
     <row r="380">
       <c r="A380" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B380" s="13">
         <v>1.0</v>
       </c>
       <c r="C380" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="D380" s="14">
-        <v>8.02224805E8</v>
+        <v>391</v>
+      </c>
+      <c r="D380" s="13">
+        <v>7.031890883E9</v>
       </c>
       <c r="E380" s="14">
         <v>234.0</v>
@@ -11753,25 +11782,10 @@
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
       <c r="K380" s="5"/>
-      <c r="L380" s="27"/>
-      <c r="M380" s="27"/>
-      <c r="N380" s="27"/>
-      <c r="O380" s="27"/>
-      <c r="P380" s="27"/>
-      <c r="Q380" s="27"/>
-      <c r="R380" s="27"/>
-      <c r="S380" s="27"/>
-      <c r="T380" s="27"/>
-      <c r="U380" s="27"/>
-      <c r="V380" s="27"/>
-      <c r="W380" s="27"/>
-      <c r="X380" s="27"/>
-      <c r="Y380" s="27"/>
-      <c r="Z380" s="27"/>
     </row>
     <row r="381">
       <c r="A381" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B381" s="13">
         <v>1.0</v>
@@ -11809,16 +11823,16 @@
     </row>
     <row r="382">
       <c r="A382" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B382" s="13">
         <v>1.0</v>
       </c>
       <c r="C382" s="14" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="D382" s="14">
-        <v>8.038190491E9</v>
+        <v>8.02224805E8</v>
       </c>
       <c r="E382" s="14">
         <v>234.0</v>
@@ -11829,13 +11843,38 @@
       <c r="I382" s="5"/>
       <c r="J382" s="5"/>
       <c r="K382" s="5"/>
+      <c r="L382" s="27"/>
+      <c r="M382" s="27"/>
+      <c r="N382" s="27"/>
+      <c r="O382" s="27"/>
+      <c r="P382" s="27"/>
+      <c r="Q382" s="27"/>
+      <c r="R382" s="27"/>
+      <c r="S382" s="27"/>
+      <c r="T382" s="27"/>
+      <c r="U382" s="27"/>
+      <c r="V382" s="27"/>
+      <c r="W382" s="27"/>
+      <c r="X382" s="27"/>
+      <c r="Y382" s="27"/>
+      <c r="Z382" s="27"/>
     </row>
     <row r="383">
-      <c r="A383" s="12"/>
-      <c r="B383" s="13"/>
-      <c r="C383" s="14"/>
-      <c r="D383" s="13"/>
-      <c r="E383" s="14"/>
+      <c r="A383" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B383" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C383" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D383" s="14">
+        <v>8.038190491E9</v>
+      </c>
+      <c r="E383" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F383" s="5"/>
       <c r="G383" s="5"/>
       <c r="H383" s="5"/>
@@ -11844,13 +11883,11 @@
       <c r="K383" s="5"/>
     </row>
     <row r="384">
-      <c r="A384" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="B384" s="25"/>
-      <c r="C384" s="26"/>
-      <c r="D384" s="26"/>
-      <c r="E384" s="28"/>
+      <c r="A384" s="12"/>
+      <c r="B384" s="13"/>
+      <c r="C384" s="14"/>
+      <c r="D384" s="13"/>
+      <c r="E384" s="14"/>
       <c r="F384" s="5"/>
       <c r="G384" s="5"/>
       <c r="H384" s="5"/>
@@ -11859,21 +11896,13 @@
       <c r="K384" s="5"/>
     </row>
     <row r="385">
-      <c r="A385" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="B385" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C385" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="D385" s="14">
-        <v>8.038096396E9</v>
-      </c>
-      <c r="E385" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A385" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="B385" s="25"/>
+      <c r="C385" s="26"/>
+      <c r="D385" s="26"/>
+      <c r="E385" s="28"/>
       <c r="F385" s="5"/>
       <c r="G385" s="5"/>
       <c r="H385" s="5"/>
@@ -11883,7 +11912,7 @@
     </row>
     <row r="386">
       <c r="A386" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B386" s="13">
         <v>1.0</v>
@@ -11906,7 +11935,7 @@
     </row>
     <row r="387">
       <c r="A387" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B387" s="13">
         <v>1.0</v>
@@ -11914,8 +11943,8 @@
       <c r="C387" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D387" s="13">
-        <v>8.033162339E9</v>
+      <c r="D387" s="14">
+        <v>8.038096396E9</v>
       </c>
       <c r="E387" s="14">
         <v>234.0</v>
@@ -11929,7 +11958,7 @@
     </row>
     <row r="388">
       <c r="A388" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B388" s="13">
         <v>1.0</v>
@@ -11952,7 +11981,7 @@
     </row>
     <row r="389">
       <c r="A389" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B389" s="13">
         <v>1.0</v>
@@ -11960,7 +11989,7 @@
       <c r="C389" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D389" s="14">
+      <c r="D389" s="13">
         <v>8.033162339E9</v>
       </c>
       <c r="E389" s="14">
@@ -11975,7 +12004,7 @@
     </row>
     <row r="390">
       <c r="A390" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B390" s="13">
         <v>1.0</v>
@@ -11984,7 +12013,7 @@
         <v>391</v>
       </c>
       <c r="D390" s="14">
-        <v>8.035023802E9</v>
+        <v>8.033162339E9</v>
       </c>
       <c r="E390" s="14">
         <v>234.0</v>
@@ -11998,7 +12027,7 @@
     </row>
     <row r="391">
       <c r="A391" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B391" s="13">
         <v>1.0</v>
@@ -12007,7 +12036,7 @@
         <v>391</v>
       </c>
       <c r="D391" s="14">
-        <v>7.060844005E9</v>
+        <v>8.035023802E9</v>
       </c>
       <c r="E391" s="14">
         <v>234.0</v>
@@ -12021,7 +12050,7 @@
     </row>
     <row r="392">
       <c r="A392" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B392" s="13">
         <v>1.0</v>
@@ -12044,7 +12073,7 @@
     </row>
     <row r="393">
       <c r="A393" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B393" s="13">
         <v>1.0</v>
@@ -12053,7 +12082,7 @@
         <v>391</v>
       </c>
       <c r="D393" s="14">
-        <v>8.027733439E9</v>
+        <v>7.060844005E9</v>
       </c>
       <c r="E393" s="14">
         <v>234.0</v>
@@ -12064,25 +12093,10 @@
       <c r="I393" s="5"/>
       <c r="J393" s="5"/>
       <c r="K393" s="5"/>
-      <c r="L393" s="27"/>
-      <c r="M393" s="27"/>
-      <c r="N393" s="27"/>
-      <c r="O393" s="27"/>
-      <c r="P393" s="27"/>
-      <c r="Q393" s="27"/>
-      <c r="R393" s="27"/>
-      <c r="S393" s="27"/>
-      <c r="T393" s="27"/>
-      <c r="U393" s="27"/>
-      <c r="V393" s="27"/>
-      <c r="W393" s="27"/>
-      <c r="X393" s="27"/>
-      <c r="Y393" s="27"/>
-      <c r="Z393" s="27"/>
     </row>
     <row r="394">
       <c r="A394" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B394" s="13">
         <v>1.0</v>
@@ -12102,13 +12116,38 @@
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
       <c r="K394" s="5"/>
+      <c r="L394" s="27"/>
+      <c r="M394" s="27"/>
+      <c r="N394" s="27"/>
+      <c r="O394" s="27"/>
+      <c r="P394" s="27"/>
+      <c r="Q394" s="27"/>
+      <c r="R394" s="27"/>
+      <c r="S394" s="27"/>
+      <c r="T394" s="27"/>
+      <c r="U394" s="27"/>
+      <c r="V394" s="27"/>
+      <c r="W394" s="27"/>
+      <c r="X394" s="27"/>
+      <c r="Y394" s="27"/>
+      <c r="Z394" s="27"/>
     </row>
     <row r="395">
-      <c r="A395" s="12"/>
-      <c r="B395" s="13"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="14"/>
+      <c r="A395" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B395" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C395" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D395" s="14">
+        <v>8.027733439E9</v>
+      </c>
+      <c r="E395" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F395" s="5"/>
       <c r="G395" s="5"/>
       <c r="H395" s="5"/>
@@ -12117,36 +12156,28 @@
       <c r="K395" s="5"/>
     </row>
     <row r="396">
-      <c r="A396" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="B396" s="25"/>
-      <c r="C396" s="26"/>
-      <c r="D396" s="26"/>
-      <c r="E396" s="28"/>
-      <c r="F396" s="27"/>
-      <c r="G396" s="27"/>
+      <c r="A396" s="12"/>
+      <c r="B396" s="13"/>
+      <c r="C396" s="14"/>
+      <c r="D396" s="14"/>
+      <c r="E396" s="14"/>
+      <c r="F396" s="5"/>
+      <c r="G396" s="5"/>
       <c r="H396" s="5"/>
       <c r="I396" s="5"/>
       <c r="J396" s="5"/>
       <c r="K396" s="5"/>
     </row>
     <row r="397">
-      <c r="A397" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="B397" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C397" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="D397" s="14">
-        <v>8.033210754E9</v>
-      </c>
-      <c r="E397" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A397" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="B397" s="25"/>
+      <c r="C397" s="26"/>
+      <c r="D397" s="26"/>
+      <c r="E397" s="28"/>
+      <c r="F397" s="27"/>
+      <c r="G397" s="27"/>
       <c r="H397" s="5"/>
       <c r="I397" s="5"/>
       <c r="J397" s="5"/>
@@ -12154,7 +12185,7 @@
     </row>
     <row r="398">
       <c r="A398" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B398" s="13">
         <v>1.0</v>
@@ -12162,8 +12193,8 @@
       <c r="C398" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D398" s="13">
-        <v>8.039462242E9</v>
+      <c r="D398" s="14">
+        <v>8.033210754E9</v>
       </c>
       <c r="E398" s="14">
         <v>234.0</v>
@@ -12175,7 +12206,7 @@
     </row>
     <row r="399">
       <c r="A399" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B399" s="13">
         <v>1.0</v>
@@ -12184,7 +12215,7 @@
         <v>426</v>
       </c>
       <c r="D399" s="13">
-        <v>8.033670457E9</v>
+        <v>8.039462242E9</v>
       </c>
       <c r="E399" s="14">
         <v>234.0</v>
@@ -12196,7 +12227,7 @@
     </row>
     <row r="400">
       <c r="A400" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B400" s="13">
         <v>1.0</v>
@@ -12205,7 +12236,7 @@
         <v>426</v>
       </c>
       <c r="D400" s="13">
-        <v>8.066484528E9</v>
+        <v>8.033670457E9</v>
       </c>
       <c r="E400" s="14">
         <v>234.0</v>
@@ -12217,7 +12248,7 @@
     </row>
     <row r="401">
       <c r="A401" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B401" s="13">
         <v>1.0</v>
@@ -12226,7 +12257,7 @@
         <v>426</v>
       </c>
       <c r="D401" s="13">
-        <v>8.139314127E9</v>
+        <v>8.066484528E9</v>
       </c>
       <c r="E401" s="14">
         <v>234.0</v>
@@ -12238,7 +12269,7 @@
     </row>
     <row r="402">
       <c r="A402" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B402" s="13">
         <v>1.0</v>
@@ -12247,7 +12278,7 @@
         <v>426</v>
       </c>
       <c r="D402" s="13">
-        <v>8.022755703E9</v>
+        <v>8.139314127E9</v>
       </c>
       <c r="E402" s="14">
         <v>234.0</v>
@@ -12259,16 +12290,16 @@
     </row>
     <row r="403">
       <c r="A403" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B403" s="13">
         <v>1.0</v>
       </c>
       <c r="C403" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="D403" s="14">
-        <v>9.024198439E9</v>
+        <v>426</v>
+      </c>
+      <c r="D403" s="13">
+        <v>8.022755703E9</v>
       </c>
       <c r="E403" s="14">
         <v>234.0</v>
@@ -12277,34 +12308,19 @@
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
       <c r="K403" s="5"/>
-      <c r="L403" s="27"/>
-      <c r="M403" s="27"/>
-      <c r="N403" s="27"/>
-      <c r="O403" s="27"/>
-      <c r="P403" s="27"/>
-      <c r="Q403" s="27"/>
-      <c r="R403" s="27"/>
-      <c r="S403" s="27"/>
-      <c r="T403" s="27"/>
-      <c r="U403" s="27"/>
-      <c r="V403" s="27"/>
-      <c r="W403" s="27"/>
-      <c r="X403" s="27"/>
-      <c r="Y403" s="27"/>
-      <c r="Z403" s="27"/>
     </row>
     <row r="404">
       <c r="A404" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B404" s="13">
         <v>1.0</v>
       </c>
       <c r="C404" s="14" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D404" s="14">
-        <v>8.0358886E9</v>
+        <v>9.024198439E9</v>
       </c>
       <c r="E404" s="14">
         <v>234.0</v>
@@ -12313,10 +12329,25 @@
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
       <c r="K404" s="5"/>
+      <c r="L404" s="27"/>
+      <c r="M404" s="27"/>
+      <c r="N404" s="27"/>
+      <c r="O404" s="27"/>
+      <c r="P404" s="27"/>
+      <c r="Q404" s="27"/>
+      <c r="R404" s="27"/>
+      <c r="S404" s="27"/>
+      <c r="T404" s="27"/>
+      <c r="U404" s="27"/>
+      <c r="V404" s="27"/>
+      <c r="W404" s="27"/>
+      <c r="X404" s="27"/>
+      <c r="Y404" s="27"/>
+      <c r="Z404" s="27"/>
     </row>
     <row r="405">
       <c r="A405" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B405" s="13">
         <v>1.0</v>
@@ -12325,7 +12356,7 @@
         <v>426</v>
       </c>
       <c r="D405" s="14">
-        <v>8.022637076E9</v>
+        <v>8.0358886E9</v>
       </c>
       <c r="E405" s="14">
         <v>234.0</v>
@@ -12337,7 +12368,7 @@
     </row>
     <row r="406">
       <c r="A406" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B406" s="13">
         <v>1.0</v>
@@ -12346,7 +12377,7 @@
         <v>426</v>
       </c>
       <c r="D406" s="14">
-        <v>8.037865897E9</v>
+        <v>8.022637076E9</v>
       </c>
       <c r="E406" s="14">
         <v>234.0</v>
@@ -12357,47 +12388,47 @@
       <c r="K406" s="5"/>
     </row>
     <row r="407">
-      <c r="A407" s="12"/>
-      <c r="B407" s="13"/>
-      <c r="C407" s="14"/>
-      <c r="D407" s="14"/>
-      <c r="E407" s="14"/>
+      <c r="A407" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B407" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C407" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D407" s="14">
+        <v>8.037865897E9</v>
+      </c>
+      <c r="E407" s="14">
+        <v>234.0</v>
+      </c>
       <c r="H407" s="5"/>
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
       <c r="K407" s="5"/>
     </row>
     <row r="408">
-      <c r="A408" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="B408" s="25"/>
-      <c r="C408" s="26"/>
-      <c r="D408" s="26"/>
-      <c r="E408" s="26"/>
-      <c r="F408" s="27"/>
-      <c r="G408" s="27"/>
+      <c r="A408" s="12"/>
+      <c r="B408" s="13"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
       <c r="H408" s="5"/>
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
       <c r="K408" s="5"/>
     </row>
     <row r="409">
-      <c r="A409" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="B409" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C409" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="D409" s="14">
-        <v>7.068629985E9</v>
-      </c>
-      <c r="E409" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A409" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="B409" s="25"/>
+      <c r="C409" s="26"/>
+      <c r="D409" s="26"/>
+      <c r="E409" s="26"/>
+      <c r="F409" s="27"/>
+      <c r="G409" s="27"/>
       <c r="H409" s="5"/>
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
@@ -12405,7 +12436,7 @@
     </row>
     <row r="410">
       <c r="A410" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B410" s="13">
         <v>1.0</v>
@@ -12426,7 +12457,7 @@
     </row>
     <row r="411">
       <c r="A411" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B411" s="13">
         <v>1.0</v>
@@ -12435,7 +12466,7 @@
         <v>426</v>
       </c>
       <c r="D411" s="14">
-        <v>8.03315128E9</v>
+        <v>7.068629985E9</v>
       </c>
       <c r="E411" s="14">
         <v>234.0</v>
@@ -12447,7 +12478,7 @@
     </row>
     <row r="412">
       <c r="A412" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B412" s="13">
         <v>1.0</v>
@@ -12468,7 +12499,7 @@
     </row>
     <row r="413">
       <c r="A413" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B413" s="13">
         <v>1.0</v>
@@ -12477,7 +12508,7 @@
         <v>426</v>
       </c>
       <c r="D413" s="14">
-        <v>8.026359933E9</v>
+        <v>8.03315128E9</v>
       </c>
       <c r="E413" s="14">
         <v>234.0</v>
@@ -12489,7 +12520,7 @@
     </row>
     <row r="414">
       <c r="A414" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B414" s="13">
         <v>1.0</v>
@@ -12498,7 +12529,7 @@
         <v>426</v>
       </c>
       <c r="D414" s="14">
-        <v>8.064681335E9</v>
+        <v>8.026359933E9</v>
       </c>
       <c r="E414" s="14">
         <v>234.0</v>
@@ -12510,7 +12541,7 @@
     </row>
     <row r="415">
       <c r="A415" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B415" s="13">
         <v>1.0</v>
@@ -12519,7 +12550,7 @@
         <v>426</v>
       </c>
       <c r="D415" s="14">
-        <v>8.033321482E9</v>
+        <v>8.064681335E9</v>
       </c>
       <c r="E415" s="14">
         <v>234.0</v>
@@ -12531,7 +12562,7 @@
     </row>
     <row r="416">
       <c r="A416" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B416" s="13">
         <v>1.0</v>
@@ -12552,7 +12583,7 @@
     </row>
     <row r="417">
       <c r="A417" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B417" s="13">
         <v>1.0</v>
@@ -12561,7 +12592,7 @@
         <v>426</v>
       </c>
       <c r="D417" s="14">
-        <v>8.038171859E9</v>
+        <v>8.033321482E9</v>
       </c>
       <c r="E417" s="14">
         <v>234.0</v>
@@ -12573,7 +12604,7 @@
     </row>
     <row r="418">
       <c r="A418" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B418" s="13">
         <v>1.0</v>
@@ -12582,7 +12613,7 @@
         <v>426</v>
       </c>
       <c r="D418" s="14">
-        <v>9.058642558E9</v>
+        <v>8.038171859E9</v>
       </c>
       <c r="E418" s="14">
         <v>234.0</v>
@@ -12591,63 +12622,61 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
       <c r="K418" s="5"/>
-      <c r="L418" s="27"/>
-      <c r="M418" s="27"/>
-      <c r="N418" s="27"/>
-      <c r="O418" s="27"/>
-      <c r="P418" s="27"/>
-      <c r="Q418" s="27"/>
-      <c r="R418" s="27"/>
-      <c r="S418" s="27"/>
-      <c r="T418" s="27"/>
-      <c r="U418" s="27"/>
-      <c r="V418" s="27"/>
-      <c r="W418" s="27"/>
-      <c r="X418" s="27"/>
-      <c r="Y418" s="27"/>
-      <c r="Z418" s="27"/>
     </row>
     <row r="419">
-      <c r="B419" s="13"/>
-      <c r="C419" s="14"/>
-      <c r="D419" s="14"/>
-      <c r="E419" s="14"/>
+      <c r="A419" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B419" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C419" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D419" s="14">
+        <v>9.058642558E9</v>
+      </c>
+      <c r="E419" s="14">
+        <v>234.0</v>
+      </c>
       <c r="H419" s="5"/>
       <c r="I419" s="5"/>
       <c r="J419" s="5"/>
       <c r="K419" s="5"/>
+      <c r="L419" s="27"/>
+      <c r="M419" s="27"/>
+      <c r="N419" s="27"/>
+      <c r="O419" s="27"/>
+      <c r="P419" s="27"/>
+      <c r="Q419" s="27"/>
+      <c r="R419" s="27"/>
+      <c r="S419" s="27"/>
+      <c r="T419" s="27"/>
+      <c r="U419" s="27"/>
+      <c r="V419" s="27"/>
+      <c r="W419" s="27"/>
+      <c r="X419" s="27"/>
+      <c r="Y419" s="27"/>
+      <c r="Z419" s="27"/>
     </row>
     <row r="420">
-      <c r="A420" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="B420" s="25"/>
-      <c r="C420" s="26"/>
-      <c r="D420" s="26"/>
-      <c r="E420" s="26"/>
-      <c r="F420" s="5"/>
-      <c r="G420" s="5"/>
+      <c r="B420" s="13"/>
+      <c r="C420" s="14"/>
+      <c r="D420" s="14"/>
+      <c r="E420" s="14"/>
       <c r="H420" s="5"/>
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
       <c r="K420" s="5"/>
     </row>
     <row r="421">
-      <c r="A421" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="B421" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C421" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="D421" s="14">
-        <v>8.034841114E9</v>
-      </c>
-      <c r="E421" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A421" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="B421" s="25"/>
+      <c r="C421" s="26"/>
+      <c r="D421" s="26"/>
+      <c r="E421" s="26"/>
       <c r="F421" s="5"/>
       <c r="G421" s="5"/>
       <c r="H421" s="5"/>
@@ -12657,7 +12686,7 @@
     </row>
     <row r="422">
       <c r="A422" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B422" s="13">
         <v>1.0</v>
@@ -12666,7 +12695,7 @@
         <v>426</v>
       </c>
       <c r="D422" s="14">
-        <v>8.058524769E9</v>
+        <v>8.034841114E9</v>
       </c>
       <c r="E422" s="14">
         <v>234.0</v>
@@ -12680,7 +12709,7 @@
     </row>
     <row r="423">
       <c r="A423" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B423" s="13">
         <v>1.0</v>
@@ -12689,7 +12718,7 @@
         <v>426</v>
       </c>
       <c r="D423" s="14">
-        <v>9.037960582E9</v>
+        <v>8.058524769E9</v>
       </c>
       <c r="E423" s="14">
         <v>234.0</v>
@@ -12703,16 +12732,16 @@
     </row>
     <row r="424">
       <c r="A424" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B424" s="13">
         <v>1.0</v>
       </c>
       <c r="C424" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D424" s="13">
-        <v>8.032002285E9</v>
+        <v>426</v>
+      </c>
+      <c r="D424" s="14">
+        <v>9.037960582E9</v>
       </c>
       <c r="E424" s="14">
         <v>234.0</v>
@@ -12726,7 +12755,7 @@
     </row>
     <row r="425">
       <c r="A425" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B425" s="13">
         <v>1.0</v>
@@ -12734,8 +12763,8 @@
       <c r="C425" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D425" s="14">
-        <v>8.023032371E9</v>
+      <c r="D425" s="13">
+        <v>8.032002285E9</v>
       </c>
       <c r="E425" s="14">
         <v>234.0</v>
@@ -12749,7 +12778,7 @@
     </row>
     <row r="426">
       <c r="A426" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B426" s="13">
         <v>1.0</v>
@@ -12757,8 +12786,8 @@
       <c r="C426" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D426" s="52">
-        <v>8.023136932E9</v>
+      <c r="D426" s="14">
+        <v>8.023032371E9</v>
       </c>
       <c r="E426" s="14">
         <v>234.0</v>
@@ -12772,7 +12801,7 @@
     </row>
     <row r="427">
       <c r="A427" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B427" s="13">
         <v>1.0</v>
@@ -12780,8 +12809,8 @@
       <c r="C427" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D427" s="13">
-        <v>8.034360992E9</v>
+      <c r="D427" s="52">
+        <v>8.023136932E9</v>
       </c>
       <c r="E427" s="14">
         <v>234.0</v>
@@ -12795,7 +12824,7 @@
     </row>
     <row r="428">
       <c r="A428" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B428" s="13">
         <v>1.0</v>
@@ -12804,7 +12833,7 @@
         <v>375</v>
       </c>
       <c r="D428" s="13">
-        <v>8.023358954E9</v>
+        <v>8.034360992E9</v>
       </c>
       <c r="E428" s="14">
         <v>234.0</v>
@@ -12815,25 +12844,10 @@
       <c r="I428" s="5"/>
       <c r="J428" s="5"/>
       <c r="K428" s="5"/>
-      <c r="L428" s="27"/>
-      <c r="M428" s="27"/>
-      <c r="N428" s="27"/>
-      <c r="O428" s="27"/>
-      <c r="P428" s="27"/>
-      <c r="Q428" s="27"/>
-      <c r="R428" s="27"/>
-      <c r="S428" s="27"/>
-      <c r="T428" s="27"/>
-      <c r="U428" s="27"/>
-      <c r="V428" s="27"/>
-      <c r="W428" s="27"/>
-      <c r="X428" s="27"/>
-      <c r="Y428" s="27"/>
-      <c r="Z428" s="27"/>
     </row>
     <row r="429">
       <c r="A429" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B429" s="13">
         <v>1.0</v>
@@ -12842,7 +12856,7 @@
         <v>375</v>
       </c>
       <c r="D429" s="13">
-        <v>8.023056347E9</v>
+        <v>8.023358954E9</v>
       </c>
       <c r="E429" s="14">
         <v>234.0</v>
@@ -12853,10 +12867,25 @@
       <c r="I429" s="5"/>
       <c r="J429" s="5"/>
       <c r="K429" s="5"/>
+      <c r="L429" s="27"/>
+      <c r="M429" s="27"/>
+      <c r="N429" s="27"/>
+      <c r="O429" s="27"/>
+      <c r="P429" s="27"/>
+      <c r="Q429" s="27"/>
+      <c r="R429" s="27"/>
+      <c r="S429" s="27"/>
+      <c r="T429" s="27"/>
+      <c r="U429" s="27"/>
+      <c r="V429" s="27"/>
+      <c r="W429" s="27"/>
+      <c r="X429" s="27"/>
+      <c r="Y429" s="27"/>
+      <c r="Z429" s="27"/>
     </row>
     <row r="430">
       <c r="A430" s="12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B430" s="13">
         <v>1.0</v>
@@ -12865,10 +12894,10 @@
         <v>375</v>
       </c>
       <c r="D430" s="13">
-        <v>6.22041817E8</v>
+        <v>8.023056347E9</v>
       </c>
       <c r="E430" s="14">
-        <v>31.0</v>
+        <v>234.0</v>
       </c>
       <c r="F430" s="5"/>
       <c r="G430" s="5"/>
@@ -12878,11 +12907,21 @@
       <c r="K430" s="5"/>
     </row>
     <row r="431">
-      <c r="A431" s="12"/>
-      <c r="B431" s="13"/>
-      <c r="C431" s="14"/>
-      <c r="D431" s="13"/>
-      <c r="E431" s="14"/>
+      <c r="A431" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B431" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C431" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D431" s="13">
+        <v>6.22041817E8</v>
+      </c>
+      <c r="E431" s="14">
+        <v>31.0</v>
+      </c>
       <c r="F431" s="5"/>
       <c r="G431" s="5"/>
       <c r="H431" s="5"/>
@@ -12891,13 +12930,11 @@
       <c r="K431" s="5"/>
     </row>
     <row r="432">
-      <c r="A432" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="B432" s="25"/>
-      <c r="C432" s="26"/>
-      <c r="D432" s="26"/>
-      <c r="E432" s="28"/>
+      <c r="A432" s="12"/>
+      <c r="B432" s="13"/>
+      <c r="C432" s="14"/>
+      <c r="D432" s="13"/>
+      <c r="E432" s="14"/>
       <c r="F432" s="5"/>
       <c r="G432" s="5"/>
       <c r="H432" s="5"/>
@@ -12906,21 +12943,13 @@
       <c r="K432" s="5"/>
     </row>
     <row r="433">
-      <c r="A433" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="B433" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C433" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D433" s="14">
-        <v>7.086669911E9</v>
-      </c>
-      <c r="E433" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A433" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="B433" s="25"/>
+      <c r="C433" s="26"/>
+      <c r="D433" s="26"/>
+      <c r="E433" s="28"/>
       <c r="F433" s="5"/>
       <c r="G433" s="5"/>
       <c r="H433" s="5"/>
@@ -12930,7 +12959,7 @@
     </row>
     <row r="434">
       <c r="A434" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B434" s="13">
         <v>1.0</v>
@@ -12938,8 +12967,8 @@
       <c r="C434" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D434" s="13">
-        <v>8.022228967E9</v>
+      <c r="D434" s="14">
+        <v>7.086669911E9</v>
       </c>
       <c r="E434" s="14">
         <v>234.0</v>
@@ -12953,7 +12982,7 @@
     </row>
     <row r="435">
       <c r="A435" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B435" s="13">
         <v>1.0</v>
@@ -12961,8 +12990,8 @@
       <c r="C435" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D435" s="14">
-        <v>8.06302025E9</v>
+      <c r="D435" s="13">
+        <v>8.022228967E9</v>
       </c>
       <c r="E435" s="14">
         <v>234.0</v>
@@ -12976,7 +13005,7 @@
     </row>
     <row r="436">
       <c r="A436" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B436" s="13">
         <v>1.0</v>
@@ -12999,7 +13028,7 @@
     </row>
     <row r="437">
       <c r="A437" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B437" s="13">
         <v>1.0</v>
@@ -13008,7 +13037,7 @@
         <v>375</v>
       </c>
       <c r="D437" s="14">
-        <v>8.023529768E9</v>
+        <v>8.06302025E9</v>
       </c>
       <c r="E437" s="14">
         <v>234.0</v>
@@ -13022,7 +13051,7 @@
     </row>
     <row r="438">
       <c r="A438" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B438" s="13">
         <v>1.0</v>
@@ -13031,7 +13060,7 @@
         <v>375</v>
       </c>
       <c r="D438" s="14">
-        <v>7.082866677E9</v>
+        <v>8.023529768E9</v>
       </c>
       <c r="E438" s="14">
         <v>234.0</v>
@@ -13045,7 +13074,7 @@
     </row>
     <row r="439">
       <c r="A439" s="12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B439" s="13">
         <v>1.0</v>
@@ -13068,7 +13097,7 @@
     </row>
     <row r="440">
       <c r="A440" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B440" s="13">
         <v>1.0</v>
@@ -13077,7 +13106,7 @@
         <v>375</v>
       </c>
       <c r="D440" s="14">
-        <v>7.035681401E9</v>
+        <v>7.082866677E9</v>
       </c>
       <c r="E440" s="14">
         <v>234.0</v>
@@ -13091,7 +13120,7 @@
     </row>
     <row r="441">
       <c r="A441" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B441" s="13">
         <v>1.0</v>
@@ -13100,7 +13129,7 @@
         <v>375</v>
       </c>
       <c r="D441" s="14">
-        <v>8.055527946E9</v>
+        <v>7.035681401E9</v>
       </c>
       <c r="E441" s="14">
         <v>234.0</v>
@@ -13111,25 +13140,10 @@
       <c r="I441" s="5"/>
       <c r="J441" s="5"/>
       <c r="K441" s="5"/>
-      <c r="L441" s="27"/>
-      <c r="M441" s="27"/>
-      <c r="N441" s="27"/>
-      <c r="O441" s="27"/>
-      <c r="P441" s="27"/>
-      <c r="Q441" s="27"/>
-      <c r="R441" s="27"/>
-      <c r="S441" s="27"/>
-      <c r="T441" s="27"/>
-      <c r="U441" s="27"/>
-      <c r="V441" s="27"/>
-      <c r="W441" s="27"/>
-      <c r="X441" s="27"/>
-      <c r="Y441" s="27"/>
-      <c r="Z441" s="27"/>
     </row>
     <row r="442">
       <c r="A442" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B442" s="13">
         <v>1.0</v>
@@ -13138,7 +13152,7 @@
         <v>375</v>
       </c>
       <c r="D442" s="14">
-        <v>8.023194301E9</v>
+        <v>8.055527946E9</v>
       </c>
       <c r="E442" s="14">
         <v>234.0</v>
@@ -13149,13 +13163,38 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
       <c r="K442" s="5"/>
+      <c r="L442" s="27"/>
+      <c r="M442" s="27"/>
+      <c r="N442" s="27"/>
+      <c r="O442" s="27"/>
+      <c r="P442" s="27"/>
+      <c r="Q442" s="27"/>
+      <c r="R442" s="27"/>
+      <c r="S442" s="27"/>
+      <c r="T442" s="27"/>
+      <c r="U442" s="27"/>
+      <c r="V442" s="27"/>
+      <c r="W442" s="27"/>
+      <c r="X442" s="27"/>
+      <c r="Y442" s="27"/>
+      <c r="Z442" s="27"/>
     </row>
     <row r="443">
-      <c r="A443" s="12"/>
-      <c r="B443" s="13"/>
-      <c r="C443" s="14"/>
-      <c r="D443" s="14"/>
-      <c r="E443" s="14"/>
+      <c r="A443" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B443" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C443" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D443" s="14">
+        <v>8.023194301E9</v>
+      </c>
+      <c r="E443" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F443" s="5"/>
       <c r="G443" s="5"/>
       <c r="H443" s="5"/>
@@ -13164,13 +13203,11 @@
       <c r="K443" s="5"/>
     </row>
     <row r="444">
-      <c r="A444" s="39" t="s">
-        <v>470</v>
-      </c>
-      <c r="B444" s="25"/>
-      <c r="C444" s="25"/>
-      <c r="D444" s="25"/>
-      <c r="E444" s="25"/>
+      <c r="A444" s="12"/>
+      <c r="B444" s="13"/>
+      <c r="C444" s="14"/>
+      <c r="D444" s="14"/>
+      <c r="E444" s="14"/>
       <c r="F444" s="5"/>
       <c r="G444" s="5"/>
       <c r="H444" s="5"/>
@@ -13179,21 +13216,13 @@
       <c r="K444" s="5"/>
     </row>
     <row r="445">
-      <c r="A445" s="29" t="s">
-        <v>471</v>
-      </c>
-      <c r="B445" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C445" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="D445" s="13">
-        <v>7.956338229E9</v>
-      </c>
-      <c r="E445" s="13">
-        <v>44.0</v>
-      </c>
+      <c r="A445" s="39" t="s">
+        <v>470</v>
+      </c>
+      <c r="B445" s="25"/>
+      <c r="C445" s="25"/>
+      <c r="D445" s="25"/>
+      <c r="E445" s="25"/>
       <c r="F445" s="5"/>
       <c r="G445" s="5"/>
       <c r="H445" s="5"/>
@@ -13203,7 +13232,7 @@
     </row>
     <row r="446">
       <c r="A446" s="29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B446" s="13">
         <v>1.0</v>
@@ -13226,7 +13255,7 @@
     </row>
     <row r="447">
       <c r="A447" s="29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B447" s="13">
         <v>1.0</v>
@@ -13235,7 +13264,7 @@
         <v>472</v>
       </c>
       <c r="D447" s="13">
-        <v>7.956132912E9</v>
+        <v>7.956338229E9</v>
       </c>
       <c r="E447" s="13">
         <v>44.0</v>
@@ -13249,7 +13278,7 @@
     </row>
     <row r="448">
       <c r="A448" s="29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B448" s="13">
         <v>1.0</v>
@@ -13272,7 +13301,7 @@
     </row>
     <row r="449">
       <c r="A449" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B449" s="13">
         <v>1.0</v>
@@ -13281,7 +13310,7 @@
         <v>472</v>
       </c>
       <c r="D449" s="13">
-        <v>7.95613193E9</v>
+        <v>7.956132912E9</v>
       </c>
       <c r="E449" s="13">
         <v>44.0</v>
@@ -13295,7 +13324,7 @@
     </row>
     <row r="450">
       <c r="A450" s="29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B450" s="13">
         <v>1.0</v>
@@ -13318,7 +13347,7 @@
     </row>
     <row r="451">
       <c r="A451" s="29" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B451" s="13">
         <v>1.0</v>
@@ -13327,7 +13356,7 @@
         <v>472</v>
       </c>
       <c r="D451" s="13">
-        <v>7.939988528E9</v>
+        <v>7.95613193E9</v>
       </c>
       <c r="E451" s="13">
         <v>44.0</v>
@@ -13341,7 +13370,7 @@
     </row>
     <row r="452">
       <c r="A452" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B452" s="13">
         <v>1.0</v>
@@ -13364,7 +13393,7 @@
     </row>
     <row r="453">
       <c r="A453" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B453" s="13">
         <v>1.0</v>
@@ -13373,10 +13402,10 @@
         <v>472</v>
       </c>
       <c r="D453" s="13">
-        <v>9.090403655E9</v>
+        <v>7.939988528E9</v>
       </c>
       <c r="E453" s="13">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F453" s="5"/>
       <c r="G453" s="5"/>
@@ -13387,7 +13416,7 @@
     </row>
     <row r="454">
       <c r="A454" s="29" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B454" s="13">
         <v>1.0</v>
@@ -13409,13 +13438,21 @@
       <c r="K454" s="5"/>
     </row>
     <row r="455">
-      <c r="A455" s="39" t="s">
-        <v>482</v>
-      </c>
-      <c r="B455" s="25"/>
-      <c r="C455" s="25"/>
-      <c r="D455" s="25"/>
-      <c r="E455" s="25"/>
+      <c r="A455" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B455" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C455" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="D455" s="13">
+        <v>9.090403655E9</v>
+      </c>
+      <c r="E455" s="13">
+        <v>234.0</v>
+      </c>
       <c r="F455" s="5"/>
       <c r="G455" s="5"/>
       <c r="H455" s="5"/>
@@ -13424,46 +13461,23 @@
       <c r="K455" s="5"/>
     </row>
     <row r="456">
-      <c r="A456" s="29" t="s">
-        <v>483</v>
-      </c>
-      <c r="B456" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C456" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="D456" s="13">
-        <v>7.95689006E9</v>
-      </c>
-      <c r="E456" s="13">
-        <v>44.0</v>
-      </c>
+      <c r="A456" s="39" t="s">
+        <v>482</v>
+      </c>
+      <c r="B456" s="25"/>
+      <c r="C456" s="25"/>
+      <c r="D456" s="25"/>
+      <c r="E456" s="25"/>
       <c r="F456" s="5"/>
       <c r="G456" s="5"/>
       <c r="H456" s="5"/>
       <c r="I456" s="5"/>
       <c r="J456" s="5"/>
       <c r="K456" s="5"/>
-      <c r="L456" s="27"/>
-      <c r="M456" s="27"/>
-      <c r="N456" s="27"/>
-      <c r="O456" s="27"/>
-      <c r="P456" s="27"/>
-      <c r="Q456" s="27"/>
-      <c r="R456" s="27"/>
-      <c r="S456" s="27"/>
-      <c r="T456" s="27"/>
-      <c r="U456" s="27"/>
-      <c r="V456" s="27"/>
-      <c r="W456" s="27"/>
-      <c r="X456" s="27"/>
-      <c r="Y456" s="27"/>
-      <c r="Z456" s="27"/>
     </row>
     <row r="457">
       <c r="A457" s="29" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B457" s="13">
         <v>1.0</v>
@@ -13501,7 +13515,7 @@
     </row>
     <row r="458">
       <c r="A458" s="29" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B458" s="13">
         <v>1.0</v>
@@ -13510,7 +13524,7 @@
         <v>472</v>
       </c>
       <c r="D458" s="13">
-        <v>7.956132912E9</v>
+        <v>7.95689006E9</v>
       </c>
       <c r="E458" s="13">
         <v>44.0</v>
@@ -13521,10 +13535,25 @@
       <c r="I458" s="5"/>
       <c r="J458" s="5"/>
       <c r="K458" s="5"/>
+      <c r="L458" s="27"/>
+      <c r="M458" s="27"/>
+      <c r="N458" s="27"/>
+      <c r="O458" s="27"/>
+      <c r="P458" s="27"/>
+      <c r="Q458" s="27"/>
+      <c r="R458" s="27"/>
+      <c r="S458" s="27"/>
+      <c r="T458" s="27"/>
+      <c r="U458" s="27"/>
+      <c r="V458" s="27"/>
+      <c r="W458" s="27"/>
+      <c r="X458" s="27"/>
+      <c r="Y458" s="27"/>
+      <c r="Z458" s="27"/>
     </row>
     <row r="459">
       <c r="A459" s="29" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B459" s="13">
         <v>1.0</v>
@@ -13533,10 +13562,10 @@
         <v>472</v>
       </c>
       <c r="D459" s="13">
-        <v>9.022163076E9</v>
+        <v>7.956132912E9</v>
       </c>
       <c r="E459" s="13">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F459" s="5"/>
       <c r="G459" s="5"/>
@@ -13547,7 +13576,7 @@
     </row>
     <row r="460">
       <c r="A460" s="29" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B460" s="13">
         <v>1.0</v>
@@ -13556,10 +13585,10 @@
         <v>472</v>
       </c>
       <c r="D460" s="13">
-        <v>7.940255254E9</v>
+        <v>9.022163076E9</v>
       </c>
       <c r="E460" s="13">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F460" s="5"/>
       <c r="G460" s="5"/>
@@ -13570,7 +13599,7 @@
     </row>
     <row r="461">
       <c r="A461" s="29" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B461" s="13">
         <v>1.0</v>
@@ -13579,10 +13608,10 @@
         <v>472</v>
       </c>
       <c r="D461" s="13">
-        <v>7.834352811E9</v>
+        <v>7.940255254E9</v>
       </c>
       <c r="E461" s="13">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F461" s="5"/>
       <c r="G461" s="5"/>
@@ -13593,7 +13622,7 @@
     </row>
     <row r="462">
       <c r="A462" s="29" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B462" s="13">
         <v>1.0</v>
@@ -13616,7 +13645,7 @@
     </row>
     <row r="463">
       <c r="A463" s="29" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B463" s="13">
         <v>1.0</v>
@@ -13639,7 +13668,7 @@
     </row>
     <row r="464">
       <c r="A464" s="29" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B464" s="13">
         <v>1.0</v>
@@ -13648,7 +13677,7 @@
         <v>472</v>
       </c>
       <c r="D464" s="13">
-        <v>7.753673669E9</v>
+        <v>7.834352811E9</v>
       </c>
       <c r="E464" s="13">
         <v>234.0</v>
@@ -13661,20 +13690,20 @@
       <c r="K464" s="5"/>
     </row>
     <row r="465">
-      <c r="A465" s="12" t="s">
-        <v>492</v>
+      <c r="A465" s="29" t="s">
+        <v>491</v>
       </c>
       <c r="B465" s="13">
         <v>1.0</v>
       </c>
-      <c r="C465" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D465" s="14">
-        <v>7.961485817E9</v>
-      </c>
-      <c r="E465" s="14">
-        <v>44.0</v>
+      <c r="C465" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="D465" s="13">
+        <v>7.753673669E9</v>
+      </c>
+      <c r="E465" s="13">
+        <v>234.0</v>
       </c>
       <c r="F465" s="5"/>
       <c r="G465" s="5"/>
@@ -13682,43 +13711,51 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
       <c r="K465" s="5"/>
-      <c r="L465" s="27"/>
-      <c r="M465" s="27"/>
-      <c r="N465" s="27"/>
-      <c r="O465" s="27"/>
-      <c r="P465" s="27"/>
-      <c r="Q465" s="27"/>
-      <c r="R465" s="27"/>
-      <c r="S465" s="27"/>
-      <c r="T465" s="27"/>
-      <c r="U465" s="27"/>
-      <c r="V465" s="27"/>
-      <c r="W465" s="27"/>
-      <c r="X465" s="27"/>
-      <c r="Y465" s="27"/>
-      <c r="Z465" s="27"/>
     </row>
     <row r="466">
-      <c r="A466" s="12"/>
-      <c r="B466" s="13"/>
-      <c r="C466" s="14"/>
-      <c r="D466" s="14"/>
-      <c r="E466" s="14"/>
+      <c r="A466" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B466" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C466" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="D466" s="14">
+        <v>7.961485817E9</v>
+      </c>
+      <c r="E466" s="14">
+        <v>44.0</v>
+      </c>
       <c r="F466" s="5"/>
       <c r="G466" s="5"/>
       <c r="H466" s="5"/>
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
       <c r="K466" s="5"/>
+      <c r="L466" s="27"/>
+      <c r="M466" s="27"/>
+      <c r="N466" s="27"/>
+      <c r="O466" s="27"/>
+      <c r="P466" s="27"/>
+      <c r="Q466" s="27"/>
+      <c r="R466" s="27"/>
+      <c r="S466" s="27"/>
+      <c r="T466" s="27"/>
+      <c r="U466" s="27"/>
+      <c r="V466" s="27"/>
+      <c r="W466" s="27"/>
+      <c r="X466" s="27"/>
+      <c r="Y466" s="27"/>
+      <c r="Z466" s="27"/>
     </row>
     <row r="467">
-      <c r="A467" s="39" t="s">
-        <v>494</v>
-      </c>
-      <c r="B467" s="25"/>
-      <c r="C467" s="25"/>
-      <c r="D467" s="25"/>
-      <c r="E467" s="25"/>
+      <c r="A467" s="12"/>
+      <c r="B467" s="13"/>
+      <c r="C467" s="14"/>
+      <c r="D467" s="14"/>
+      <c r="E467" s="14"/>
       <c r="F467" s="5"/>
       <c r="G467" s="5"/>
       <c r="H467" s="5"/>
@@ -13727,21 +13764,13 @@
       <c r="K467" s="5"/>
     </row>
     <row r="468">
-      <c r="A468" s="29" t="s">
-        <v>495</v>
-      </c>
-      <c r="B468" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C468" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D468" s="13">
-        <v>7.807493779E9</v>
-      </c>
-      <c r="E468" s="13">
-        <v>44.0</v>
-      </c>
+      <c r="A468" s="39" t="s">
+        <v>494</v>
+      </c>
+      <c r="B468" s="25"/>
+      <c r="C468" s="25"/>
+      <c r="D468" s="25"/>
+      <c r="E468" s="25"/>
       <c r="F468" s="5"/>
       <c r="G468" s="5"/>
       <c r="H468" s="5"/>
@@ -13751,7 +13780,7 @@
     </row>
     <row r="469">
       <c r="A469" s="29" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B469" s="13">
         <v>1.0</v>
@@ -13774,7 +13803,7 @@
     </row>
     <row r="470">
       <c r="A470" s="29" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B470" s="13">
         <v>1.0</v>
@@ -13783,7 +13812,7 @@
         <v>496</v>
       </c>
       <c r="D470" s="13">
-        <v>7.424791947E9</v>
+        <v>7.807493779E9</v>
       </c>
       <c r="E470" s="13">
         <v>44.0</v>
@@ -13797,7 +13826,7 @@
     </row>
     <row r="471">
       <c r="A471" s="29" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B471" s="13">
         <v>1.0</v>
@@ -13806,7 +13835,7 @@
         <v>496</v>
       </c>
       <c r="D471" s="13">
-        <v>7.807493779E9</v>
+        <v>7.424791947E9</v>
       </c>
       <c r="E471" s="13">
         <v>44.0</v>
@@ -13820,7 +13849,7 @@
     </row>
     <row r="472">
       <c r="A472" s="29" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B472" s="13">
         <v>1.0</v>
@@ -13829,7 +13858,7 @@
         <v>496</v>
       </c>
       <c r="D472" s="13">
-        <v>7.424791947E9</v>
+        <v>7.807493779E9</v>
       </c>
       <c r="E472" s="13">
         <v>44.0</v>
@@ -13840,25 +13869,10 @@
       <c r="I472" s="5"/>
       <c r="J472" s="5"/>
       <c r="K472" s="5"/>
-      <c r="L472" s="27"/>
-      <c r="M472" s="27"/>
-      <c r="N472" s="27"/>
-      <c r="O472" s="27"/>
-      <c r="P472" s="27"/>
-      <c r="Q472" s="27"/>
-      <c r="R472" s="27"/>
-      <c r="S472" s="27"/>
-      <c r="T472" s="27"/>
-      <c r="U472" s="27"/>
-      <c r="V472" s="27"/>
-      <c r="W472" s="27"/>
-      <c r="X472" s="27"/>
-      <c r="Y472" s="27"/>
-      <c r="Z472" s="27"/>
     </row>
     <row r="473">
       <c r="A473" s="29" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B473" s="13">
         <v>1.0</v>
@@ -13867,7 +13881,7 @@
         <v>496</v>
       </c>
       <c r="D473" s="13">
-        <v>7.807493779E9</v>
+        <v>7.424791947E9</v>
       </c>
       <c r="E473" s="13">
         <v>44.0</v>
@@ -13878,10 +13892,25 @@
       <c r="I473" s="5"/>
       <c r="J473" s="5"/>
       <c r="K473" s="5"/>
+      <c r="L473" s="27"/>
+      <c r="M473" s="27"/>
+      <c r="N473" s="27"/>
+      <c r="O473" s="27"/>
+      <c r="P473" s="27"/>
+      <c r="Q473" s="27"/>
+      <c r="R473" s="27"/>
+      <c r="S473" s="27"/>
+      <c r="T473" s="27"/>
+      <c r="U473" s="27"/>
+      <c r="V473" s="27"/>
+      <c r="W473" s="27"/>
+      <c r="X473" s="27"/>
+      <c r="Y473" s="27"/>
+      <c r="Z473" s="27"/>
     </row>
     <row r="474">
       <c r="A474" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B474" s="13">
         <v>1.0</v>
@@ -13889,11 +13918,11 @@
       <c r="C474" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="D474" s="13" t="s">
-        <v>503</v>
+      <c r="D474" s="13">
+        <v>7.807493779E9</v>
       </c>
       <c r="E474" s="13">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="F474" s="5"/>
       <c r="G474" s="5"/>
@@ -13904,7 +13933,7 @@
     </row>
     <row r="475">
       <c r="A475" s="29" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B475" s="13">
         <v>1.0</v>
@@ -13912,11 +13941,11 @@
       <c r="C475" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="D475" s="13">
-        <v>7.807493779E9</v>
+      <c r="D475" s="13" t="s">
+        <v>503</v>
       </c>
       <c r="E475" s="13">
-        <v>44.0</v>
+        <v>1.0</v>
       </c>
       <c r="F475" s="5"/>
       <c r="G475" s="5"/>
@@ -13927,7 +13956,7 @@
     </row>
     <row r="476">
       <c r="A476" s="29" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B476" s="13">
         <v>1.0</v>
@@ -13950,7 +13979,7 @@
     </row>
     <row r="477">
       <c r="A477" s="29" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B477" s="13">
         <v>1.0</v>
@@ -13958,11 +13987,11 @@
       <c r="C477" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="D477" s="13" t="s">
-        <v>503</v>
+      <c r="D477" s="13">
+        <v>7.807493779E9</v>
       </c>
       <c r="E477" s="13">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="F477" s="5"/>
       <c r="G477" s="5"/>
@@ -13972,11 +14001,21 @@
       <c r="K477" s="5"/>
     </row>
     <row r="478">
-      <c r="A478" s="29"/>
-      <c r="B478" s="13"/>
-      <c r="C478" s="13"/>
-      <c r="D478" s="13"/>
-      <c r="E478" s="13"/>
+      <c r="A478" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="B478" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C478" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="D478" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="E478" s="13">
+        <v>1.0</v>
+      </c>
       <c r="F478" s="5"/>
       <c r="G478" s="5"/>
       <c r="H478" s="5"/>
@@ -13985,13 +14024,11 @@
       <c r="K478" s="5"/>
     </row>
     <row r="479">
-      <c r="A479" s="39" t="s">
-        <v>507</v>
-      </c>
-      <c r="B479" s="25"/>
-      <c r="C479" s="25"/>
-      <c r="D479" s="25"/>
-      <c r="E479" s="25"/>
+      <c r="A479" s="29"/>
+      <c r="B479" s="13"/>
+      <c r="C479" s="13"/>
+      <c r="D479" s="13"/>
+      <c r="E479" s="13"/>
       <c r="F479" s="5"/>
       <c r="G479" s="5"/>
       <c r="H479" s="5"/>
@@ -14000,21 +14037,13 @@
       <c r="K479" s="5"/>
     </row>
     <row r="480">
-      <c r="A480" s="29" t="s">
-        <v>508</v>
-      </c>
-      <c r="B480" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C480" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D480" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="E480" s="13">
-        <v>1.0</v>
-      </c>
+      <c r="A480" s="39" t="s">
+        <v>507</v>
+      </c>
+      <c r="B480" s="25"/>
+      <c r="C480" s="25"/>
+      <c r="D480" s="25"/>
+      <c r="E480" s="25"/>
       <c r="F480" s="5"/>
       <c r="G480" s="5"/>
       <c r="H480" s="5"/>
@@ -14024,7 +14053,7 @@
     </row>
     <row r="481">
       <c r="A481" s="29" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B481" s="13">
         <v>1.0</v>
@@ -14033,7 +14062,7 @@
         <v>496</v>
       </c>
       <c r="D481" s="13" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E481" s="13">
         <v>1.0</v>
@@ -14044,25 +14073,10 @@
       <c r="I481" s="5"/>
       <c r="J481" s="5"/>
       <c r="K481" s="5"/>
-      <c r="L481" s="27"/>
-      <c r="M481" s="27"/>
-      <c r="N481" s="27"/>
-      <c r="O481" s="27"/>
-      <c r="P481" s="27"/>
-      <c r="Q481" s="27"/>
-      <c r="R481" s="27"/>
-      <c r="S481" s="27"/>
-      <c r="T481" s="27"/>
-      <c r="U481" s="27"/>
-      <c r="V481" s="27"/>
-      <c r="W481" s="27"/>
-      <c r="X481" s="27"/>
-      <c r="Y481" s="27"/>
-      <c r="Z481" s="27"/>
     </row>
     <row r="482">
       <c r="A482" s="29" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B482" s="13">
         <v>1.0</v>
@@ -14071,10 +14085,10 @@
         <v>496</v>
       </c>
       <c r="D482" s="13" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E482" s="13">
-        <v>234.0</v>
+        <v>1.0</v>
       </c>
       <c r="F482" s="5"/>
       <c r="G482" s="5"/>
@@ -14082,10 +14096,25 @@
       <c r="I482" s="5"/>
       <c r="J482" s="5"/>
       <c r="K482" s="5"/>
+      <c r="L482" s="27"/>
+      <c r="M482" s="27"/>
+      <c r="N482" s="27"/>
+      <c r="O482" s="27"/>
+      <c r="P482" s="27"/>
+      <c r="Q482" s="27"/>
+      <c r="R482" s="27"/>
+      <c r="S482" s="27"/>
+      <c r="T482" s="27"/>
+      <c r="U482" s="27"/>
+      <c r="V482" s="27"/>
+      <c r="W482" s="27"/>
+      <c r="X482" s="27"/>
+      <c r="Y482" s="27"/>
+      <c r="Z482" s="27"/>
     </row>
     <row r="483">
       <c r="A483" s="29" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B483" s="13">
         <v>1.0</v>
@@ -14094,10 +14123,10 @@
         <v>496</v>
       </c>
       <c r="D483" s="13" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E483" s="13">
-        <v>1.0</v>
+        <v>234.0</v>
       </c>
       <c r="F483" s="5"/>
       <c r="G483" s="5"/>
@@ -14108,7 +14137,7 @@
     </row>
     <row r="484">
       <c r="A484" s="29" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B484" s="13">
         <v>1.0</v>
@@ -14117,7 +14146,7 @@
         <v>496</v>
       </c>
       <c r="D484" s="13" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E484" s="13">
         <v>1.0</v>
@@ -14130,20 +14159,20 @@
       <c r="K484" s="5"/>
     </row>
     <row r="485">
-      <c r="A485" s="12" t="s">
-        <v>515</v>
+      <c r="A485" s="29" t="s">
+        <v>514</v>
       </c>
       <c r="B485" s="13">
         <v>1.0</v>
       </c>
-      <c r="C485" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D485" s="14">
-        <v>7.807493779E9</v>
-      </c>
-      <c r="E485" s="10">
-        <v>44.0</v>
+      <c r="C485" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="D485" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="E485" s="13">
+        <v>1.0</v>
       </c>
       <c r="F485" s="5"/>
       <c r="G485" s="5"/>
@@ -14154,7 +14183,7 @@
     </row>
     <row r="486">
       <c r="A486" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B486" s="13">
         <v>1.0</v>
@@ -14165,7 +14194,7 @@
       <c r="D486" s="14">
         <v>7.807493779E9</v>
       </c>
-      <c r="E486" s="14">
+      <c r="E486" s="10">
         <v>44.0</v>
       </c>
       <c r="F486" s="5"/>
@@ -14174,25 +14203,10 @@
       <c r="I486" s="5"/>
       <c r="J486" s="5"/>
       <c r="K486" s="5"/>
-      <c r="L486" s="27"/>
-      <c r="M486" s="27"/>
-      <c r="N486" s="27"/>
-      <c r="O486" s="27"/>
-      <c r="P486" s="27"/>
-      <c r="Q486" s="27"/>
-      <c r="R486" s="27"/>
-      <c r="S486" s="27"/>
-      <c r="T486" s="27"/>
-      <c r="U486" s="27"/>
-      <c r="V486" s="27"/>
-      <c r="W486" s="27"/>
-      <c r="X486" s="27"/>
-      <c r="Y486" s="27"/>
-      <c r="Z486" s="27"/>
     </row>
     <row r="487">
       <c r="A487" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B487" s="13">
         <v>1.0</v>
@@ -14212,10 +14226,25 @@
       <c r="I487" s="5"/>
       <c r="J487" s="5"/>
       <c r="K487" s="5"/>
+      <c r="L487" s="27"/>
+      <c r="M487" s="27"/>
+      <c r="N487" s="27"/>
+      <c r="O487" s="27"/>
+      <c r="P487" s="27"/>
+      <c r="Q487" s="27"/>
+      <c r="R487" s="27"/>
+      <c r="S487" s="27"/>
+      <c r="T487" s="27"/>
+      <c r="U487" s="27"/>
+      <c r="V487" s="27"/>
+      <c r="W487" s="27"/>
+      <c r="X487" s="27"/>
+      <c r="Y487" s="27"/>
+      <c r="Z487" s="27"/>
     </row>
     <row r="488">
       <c r="A488" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B488" s="13">
         <v>1.0</v>
@@ -14224,7 +14253,7 @@
         <v>493</v>
       </c>
       <c r="D488" s="14">
-        <v>7.949394588E9</v>
+        <v>7.807493779E9</v>
       </c>
       <c r="E488" s="14">
         <v>44.0</v>
@@ -14238,7 +14267,7 @@
     </row>
     <row r="489">
       <c r="A489" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B489" s="13">
         <v>1.0</v>
@@ -14260,13 +14289,21 @@
       <c r="K489" s="5"/>
     </row>
     <row r="490">
-      <c r="A490" s="39" t="s">
-        <v>520</v>
-      </c>
-      <c r="B490" s="25"/>
-      <c r="C490" s="25"/>
-      <c r="D490" s="25"/>
-      <c r="E490" s="25"/>
+      <c r="A490" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="B490" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C490" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="D490" s="14">
+        <v>7.949394588E9</v>
+      </c>
+      <c r="E490" s="14">
+        <v>44.0</v>
+      </c>
       <c r="F490" s="5"/>
       <c r="G490" s="5"/>
       <c r="H490" s="5"/>
@@ -14275,21 +14312,13 @@
       <c r="K490" s="5"/>
     </row>
     <row r="491">
-      <c r="A491" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="B491" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C491" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="D491" s="13">
-        <v>7.055269061E9</v>
-      </c>
-      <c r="E491" s="13">
-        <v>234.0</v>
-      </c>
+      <c r="A491" s="39" t="s">
+        <v>520</v>
+      </c>
+      <c r="B491" s="25"/>
+      <c r="C491" s="25"/>
+      <c r="D491" s="25"/>
+      <c r="E491" s="25"/>
       <c r="F491" s="5"/>
       <c r="G491" s="5"/>
       <c r="H491" s="5"/>
@@ -14299,7 +14328,7 @@
     </row>
     <row r="492">
       <c r="A492" s="29" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B492" s="13">
         <v>1.0</v>
@@ -14322,7 +14351,7 @@
     </row>
     <row r="493">
       <c r="A493" s="29" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B493" s="13">
         <v>1.0</v>
@@ -14331,7 +14360,7 @@
         <v>522</v>
       </c>
       <c r="D493" s="13">
-        <v>7.035375757E9</v>
+        <v>7.055269061E9</v>
       </c>
       <c r="E493" s="13">
         <v>234.0</v>
@@ -14345,7 +14374,7 @@
     </row>
     <row r="494">
       <c r="A494" s="29" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B494" s="13">
         <v>1.0</v>
@@ -14354,7 +14383,7 @@
         <v>522</v>
       </c>
       <c r="D494" s="13">
-        <v>8.033459526E9</v>
+        <v>7.035375757E9</v>
       </c>
       <c r="E494" s="13">
         <v>234.0</v>
@@ -14368,7 +14397,7 @@
     </row>
     <row r="495">
       <c r="A495" s="29" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B495" s="13">
         <v>1.0</v>
@@ -14377,10 +14406,10 @@
         <v>522</v>
       </c>
       <c r="D495" s="13">
-        <v>7.956447698E9</v>
+        <v>8.033459526E9</v>
       </c>
       <c r="E495" s="13">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F495" s="5"/>
       <c r="G495" s="5"/>
@@ -14391,7 +14420,7 @@
     </row>
     <row r="496">
       <c r="A496" s="29" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B496" s="13">
         <v>1.0</v>
@@ -14414,7 +14443,7 @@
     </row>
     <row r="497">
       <c r="A497" s="29" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B497" s="13">
         <v>1.0</v>
@@ -14423,7 +14452,7 @@
         <v>522</v>
       </c>
       <c r="D497" s="13">
-        <v>7.957449008E9</v>
+        <v>7.956447698E9</v>
       </c>
       <c r="E497" s="13">
         <v>44.0</v>
@@ -14436,19 +14465,19 @@
       <c r="K497" s="5"/>
     </row>
     <row r="498">
-      <c r="A498" s="12" t="s">
-        <v>529</v>
+      <c r="A498" s="29" t="s">
+        <v>528</v>
       </c>
       <c r="B498" s="13">
         <v>1.0</v>
       </c>
-      <c r="C498" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D498" s="14">
-        <v>7.494285001E9</v>
-      </c>
-      <c r="E498" s="10">
+      <c r="C498" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="D498" s="13">
+        <v>7.957449008E9</v>
+      </c>
+      <c r="E498" s="13">
         <v>44.0</v>
       </c>
       <c r="F498" s="5"/>
@@ -14460,7 +14489,7 @@
     </row>
     <row r="499">
       <c r="A499" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B499" s="13">
         <v>1.0</v>
@@ -14482,14 +14511,14 @@
       <c r="K499" s="5"/>
     </row>
     <row r="500">
-      <c r="A500" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B500" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C500" s="10" t="s">
-        <v>522</v>
+      <c r="A500" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="B500" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C500" s="14" t="s">
+        <v>493</v>
       </c>
       <c r="D500" s="14">
         <v>7.494285001E9</v>
@@ -14497,28 +14526,36 @@
       <c r="E500" s="10">
         <v>44.0</v>
       </c>
+      <c r="F500" s="5"/>
+      <c r="G500" s="5"/>
+      <c r="H500" s="5"/>
+      <c r="I500" s="5"/>
+      <c r="J500" s="5"/>
+      <c r="K500" s="5"/>
     </row>
     <row r="501">
-      <c r="A501" s="29"/>
-      <c r="B501" s="13"/>
-      <c r="C501" s="13"/>
-      <c r="D501" s="13"/>
-      <c r="E501" s="13"/>
-      <c r="F501" s="5"/>
-      <c r="G501" s="5"/>
-      <c r="H501" s="5"/>
-      <c r="I501" s="5"/>
-      <c r="J501" s="5"/>
-      <c r="K501" s="5"/>
+      <c r="A501" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B501" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C501" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D501" s="14">
+        <v>7.494285001E9</v>
+      </c>
+      <c r="E501" s="10">
+        <v>44.0</v>
+      </c>
     </row>
     <row r="502">
-      <c r="A502" s="39" t="s">
-        <v>532</v>
-      </c>
-      <c r="B502" s="53"/>
-      <c r="C502" s="53"/>
-      <c r="D502" s="53"/>
-      <c r="E502" s="53"/>
+      <c r="A502" s="29"/>
+      <c r="B502" s="13"/>
+      <c r="C502" s="13"/>
+      <c r="D502" s="13"/>
+      <c r="E502" s="13"/>
       <c r="F502" s="5"/>
       <c r="G502" s="5"/>
       <c r="H502" s="5"/>
@@ -14527,21 +14564,13 @@
       <c r="K502" s="5"/>
     </row>
     <row r="503">
-      <c r="A503" s="29" t="s">
-        <v>533</v>
-      </c>
-      <c r="B503" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C503" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="D503" s="13">
-        <v>8.03359479E9</v>
-      </c>
-      <c r="E503" s="13">
-        <v>234.0</v>
-      </c>
+      <c r="A503" s="39" t="s">
+        <v>532</v>
+      </c>
+      <c r="B503" s="53"/>
+      <c r="C503" s="53"/>
+      <c r="D503" s="53"/>
+      <c r="E503" s="53"/>
       <c r="F503" s="5"/>
       <c r="G503" s="5"/>
       <c r="H503" s="5"/>
@@ -14551,7 +14580,7 @@
     </row>
     <row r="504">
       <c r="A504" s="29" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B504" s="13">
         <v>1.0</v>
@@ -14560,7 +14589,7 @@
         <v>522</v>
       </c>
       <c r="D504" s="13">
-        <v>8.033510345E9</v>
+        <v>8.03359479E9</v>
       </c>
       <c r="E504" s="13">
         <v>234.0</v>
@@ -14574,7 +14603,7 @@
     </row>
     <row r="505">
       <c r="A505" s="29" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B505" s="13">
         <v>1.0</v>
@@ -14583,7 +14612,7 @@
         <v>522</v>
       </c>
       <c r="D505" s="13">
-        <v>7.061817517E9</v>
+        <v>8.033510345E9</v>
       </c>
       <c r="E505" s="13">
         <v>234.0</v>
@@ -14597,7 +14626,7 @@
     </row>
     <row r="506">
       <c r="A506" s="29" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B506" s="13">
         <v>1.0</v>
@@ -14606,7 +14635,7 @@
         <v>522</v>
       </c>
       <c r="D506" s="13">
-        <v>8.035350809E9</v>
+        <v>7.061817517E9</v>
       </c>
       <c r="E506" s="13">
         <v>234.0</v>
@@ -14620,7 +14649,7 @@
     </row>
     <row r="507">
       <c r="A507" s="29" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B507" s="13">
         <v>1.0</v>
@@ -14629,7 +14658,7 @@
         <v>522</v>
       </c>
       <c r="D507" s="13">
-        <v>8.036156051E9</v>
+        <v>8.035350809E9</v>
       </c>
       <c r="E507" s="13">
         <v>234.0</v>
@@ -14640,25 +14669,10 @@
       <c r="I507" s="5"/>
       <c r="J507" s="5"/>
       <c r="K507" s="5"/>
-      <c r="L507" s="27"/>
-      <c r="M507" s="27"/>
-      <c r="N507" s="27"/>
-      <c r="O507" s="27"/>
-      <c r="P507" s="27"/>
-      <c r="Q507" s="27"/>
-      <c r="R507" s="27"/>
-      <c r="S507" s="27"/>
-      <c r="T507" s="27"/>
-      <c r="U507" s="27"/>
-      <c r="V507" s="27"/>
-      <c r="W507" s="27"/>
-      <c r="X507" s="27"/>
-      <c r="Y507" s="27"/>
-      <c r="Z507" s="27"/>
     </row>
     <row r="508">
       <c r="A508" s="29" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B508" s="13">
         <v>1.0</v>
@@ -14667,7 +14681,7 @@
         <v>522</v>
       </c>
       <c r="D508" s="13">
-        <v>7.060648613E9</v>
+        <v>8.036156051E9</v>
       </c>
       <c r="E508" s="13">
         <v>234.0</v>
@@ -14678,10 +14692,25 @@
       <c r="I508" s="5"/>
       <c r="J508" s="5"/>
       <c r="K508" s="5"/>
+      <c r="L508" s="27"/>
+      <c r="M508" s="27"/>
+      <c r="N508" s="27"/>
+      <c r="O508" s="27"/>
+      <c r="P508" s="27"/>
+      <c r="Q508" s="27"/>
+      <c r="R508" s="27"/>
+      <c r="S508" s="27"/>
+      <c r="T508" s="27"/>
+      <c r="U508" s="27"/>
+      <c r="V508" s="27"/>
+      <c r="W508" s="27"/>
+      <c r="X508" s="27"/>
+      <c r="Y508" s="27"/>
+      <c r="Z508" s="27"/>
     </row>
     <row r="509">
       <c r="A509" s="29" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B509" s="13">
         <v>1.0</v>
@@ -14704,7 +14733,7 @@
     </row>
     <row r="510">
       <c r="A510" s="29" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B510" s="13">
         <v>1.0</v>
@@ -14713,7 +14742,7 @@
         <v>522</v>
       </c>
       <c r="D510" s="13">
-        <v>8.027322242E9</v>
+        <v>7.060648613E9</v>
       </c>
       <c r="E510" s="13">
         <v>234.0</v>
@@ -14727,7 +14756,7 @@
     </row>
     <row r="511">
       <c r="A511" s="29" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B511" s="13">
         <v>1.0</v>
@@ -14736,10 +14765,10 @@
         <v>522</v>
       </c>
       <c r="D511" s="13">
-        <v>2.022468441E9</v>
+        <v>8.027322242E9</v>
       </c>
       <c r="E511" s="13">
-        <v>1.0</v>
+        <v>234.0</v>
       </c>
       <c r="F511" s="5"/>
       <c r="G511" s="5"/>
@@ -14750,7 +14779,7 @@
     </row>
     <row r="512">
       <c r="A512" s="29" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B512" s="13">
         <v>1.0</v>
@@ -14759,10 +14788,10 @@
         <v>522</v>
       </c>
       <c r="D512" s="13">
-        <v>8.184882788E9</v>
+        <v>2.022468441E9</v>
       </c>
       <c r="E512" s="13">
-        <v>234.0</v>
+        <v>1.0</v>
       </c>
       <c r="F512" s="5"/>
       <c r="G512" s="5"/>
@@ -14772,11 +14801,21 @@
       <c r="K512" s="5"/>
     </row>
     <row r="513">
-      <c r="A513" s="12"/>
-      <c r="B513" s="13"/>
-      <c r="C513" s="14"/>
-      <c r="D513" s="14"/>
-      <c r="E513" s="14"/>
+      <c r="A513" s="29" t="s">
+        <v>541</v>
+      </c>
+      <c r="B513" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C513" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="D513" s="13">
+        <v>8.184882788E9</v>
+      </c>
+      <c r="E513" s="13">
+        <v>234.0</v>
+      </c>
       <c r="F513" s="5"/>
       <c r="G513" s="5"/>
       <c r="H513" s="5"/>
@@ -14785,13 +14824,11 @@
       <c r="K513" s="5"/>
     </row>
     <row r="514">
-      <c r="A514" s="24" t="s">
-        <v>542</v>
-      </c>
-      <c r="B514" s="25"/>
-      <c r="C514" s="26"/>
-      <c r="D514" s="26"/>
-      <c r="E514" s="28"/>
+      <c r="A514" s="12"/>
+      <c r="B514" s="13"/>
+      <c r="C514" s="14"/>
+      <c r="D514" s="14"/>
+      <c r="E514" s="14"/>
       <c r="F514" s="5"/>
       <c r="G514" s="5"/>
       <c r="H514" s="5"/>
@@ -14800,35 +14837,27 @@
       <c r="K514" s="5"/>
     </row>
     <row r="515">
-      <c r="D515" s="11"/>
-      <c r="E515" s="11"/>
+      <c r="A515" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="B515" s="25"/>
+      <c r="C515" s="26"/>
+      <c r="D515" s="26"/>
+      <c r="E515" s="28"/>
+      <c r="F515" s="5"/>
+      <c r="G515" s="5"/>
+      <c r="H515" s="5"/>
+      <c r="I515" s="5"/>
+      <c r="J515" s="5"/>
+      <c r="K515" s="5"/>
     </row>
     <row r="516">
-      <c r="A516" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="B516" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C516" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D516" s="14">
-        <v>8.033016753E9</v>
-      </c>
-      <c r="E516" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F516" s="5"/>
-      <c r="G516" s="5"/>
-      <c r="H516" s="5"/>
-      <c r="I516" s="5"/>
-      <c r="J516" s="5"/>
-      <c r="K516" s="5"/>
+      <c r="D516" s="11"/>
+      <c r="E516" s="11"/>
     </row>
     <row r="517">
       <c r="A517" s="12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B517" s="13">
         <v>1.0</v>
@@ -14851,7 +14880,7 @@
     </row>
     <row r="518">
       <c r="A518" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B518" s="13">
         <v>1.0</v>
@@ -14860,7 +14889,7 @@
         <v>493</v>
       </c>
       <c r="D518" s="14">
-        <v>7.398843791E9</v>
+        <v>8.033016753E9</v>
       </c>
       <c r="E518" s="14">
         <v>234.0</v>
@@ -14874,7 +14903,7 @@
     </row>
     <row r="519">
       <c r="A519" s="12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B519" s="13">
         <v>1.0</v>
@@ -14883,10 +14912,10 @@
         <v>493</v>
       </c>
       <c r="D519" s="14">
-        <v>7.949394588E9</v>
+        <v>7.398843791E9</v>
       </c>
       <c r="E519" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F519" s="5"/>
       <c r="G519" s="5"/>
@@ -14894,37 +14923,22 @@
       <c r="I519" s="5"/>
       <c r="J519" s="5"/>
       <c r="K519" s="5"/>
-      <c r="L519" s="27"/>
-      <c r="M519" s="27"/>
-      <c r="N519" s="27"/>
-      <c r="O519" s="27"/>
-      <c r="P519" s="27"/>
-      <c r="Q519" s="27"/>
-      <c r="R519" s="27"/>
-      <c r="S519" s="27"/>
-      <c r="T519" s="27"/>
-      <c r="U519" s="27"/>
-      <c r="V519" s="27"/>
-      <c r="W519" s="27"/>
-      <c r="X519" s="27"/>
-      <c r="Y519" s="27"/>
-      <c r="Z519" s="27"/>
     </row>
     <row r="520">
-      <c r="A520" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="B520" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C520" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="D520" s="10">
-        <v>7.961023865E9</v>
-      </c>
-      <c r="E520" s="11">
-        <v>44</v>
+      <c r="A520" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="B520" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C520" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="D520" s="14">
+        <v>7.949394588E9</v>
+      </c>
+      <c r="E520" s="14">
+        <v>44.0</v>
       </c>
       <c r="F520" s="5"/>
       <c r="G520" s="5"/>
@@ -14932,10 +14946,25 @@
       <c r="I520" s="5"/>
       <c r="J520" s="5"/>
       <c r="K520" s="5"/>
+      <c r="L520" s="27"/>
+      <c r="M520" s="27"/>
+      <c r="N520" s="27"/>
+      <c r="O520" s="27"/>
+      <c r="P520" s="27"/>
+      <c r="Q520" s="27"/>
+      <c r="R520" s="27"/>
+      <c r="S520" s="27"/>
+      <c r="T520" s="27"/>
+      <c r="U520" s="27"/>
+      <c r="V520" s="27"/>
+      <c r="W520" s="27"/>
+      <c r="X520" s="27"/>
+      <c r="Y520" s="27"/>
+      <c r="Z520" s="27"/>
     </row>
     <row r="521">
       <c r="A521" s="9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B521" s="10">
         <v>1.0</v>
@@ -14957,20 +14986,20 @@
       <c r="K521" s="5"/>
     </row>
     <row r="522">
-      <c r="A522" s="29" t="s">
-        <v>550</v>
-      </c>
-      <c r="B522" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C522" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="D522" s="14">
-        <v>8.028996353E9</v>
-      </c>
-      <c r="E522" s="14">
-        <v>234.0</v>
+      <c r="A522" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="B522" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C522" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="D522" s="10">
+        <v>7.961023865E9</v>
+      </c>
+      <c r="E522" s="11">
+        <v>44</v>
       </c>
       <c r="F522" s="5"/>
       <c r="G522" s="5"/>
@@ -14980,20 +15009,20 @@
       <c r="K522" s="5"/>
     </row>
     <row r="523">
-      <c r="A523" s="12" t="s">
-        <v>551</v>
+      <c r="A523" s="29" t="s">
+        <v>550</v>
       </c>
       <c r="B523" s="13">
         <v>1.0</v>
       </c>
       <c r="C523" s="14" t="s">
-        <v>552</v>
+        <v>388</v>
       </c>
       <c r="D523" s="14">
-        <v>7.949394588E9</v>
-      </c>
-      <c r="E523" s="13">
-        <v>44.0</v>
+        <v>8.028996353E9</v>
+      </c>
+      <c r="E523" s="14">
+        <v>234.0</v>
       </c>
       <c r="F523" s="5"/>
       <c r="G523" s="5"/>
@@ -15004,13 +15033,13 @@
     </row>
     <row r="524">
       <c r="A524" s="12" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B524" s="13">
         <v>1.0</v>
       </c>
       <c r="C524" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D524" s="14">
         <v>7.949394588E9</v>
@@ -15024,25 +15053,10 @@
       <c r="I524" s="5"/>
       <c r="J524" s="5"/>
       <c r="K524" s="5"/>
-      <c r="L524" s="27"/>
-      <c r="M524" s="27"/>
-      <c r="N524" s="27"/>
-      <c r="O524" s="27"/>
-      <c r="P524" s="27"/>
-      <c r="Q524" s="27"/>
-      <c r="R524" s="27"/>
-      <c r="S524" s="27"/>
-      <c r="T524" s="27"/>
-      <c r="U524" s="27"/>
-      <c r="V524" s="27"/>
-      <c r="W524" s="27"/>
-      <c r="X524" s="27"/>
-      <c r="Y524" s="27"/>
-      <c r="Z524" s="27"/>
     </row>
     <row r="525">
       <c r="A525" s="12" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B525" s="13">
         <v>1.0</v>
@@ -15062,42 +15076,57 @@
       <c r="I525" s="5"/>
       <c r="J525" s="5"/>
       <c r="K525" s="5"/>
+      <c r="L525" s="27"/>
+      <c r="M525" s="27"/>
+      <c r="N525" s="27"/>
+      <c r="O525" s="27"/>
+      <c r="P525" s="27"/>
+      <c r="Q525" s="27"/>
+      <c r="R525" s="27"/>
+      <c r="S525" s="27"/>
+      <c r="T525" s="27"/>
+      <c r="U525" s="27"/>
+      <c r="V525" s="27"/>
+      <c r="W525" s="27"/>
+      <c r="X525" s="27"/>
+      <c r="Y525" s="27"/>
+      <c r="Z525" s="27"/>
     </row>
     <row r="526">
-      <c r="D526" s="11"/>
-      <c r="E526" s="11"/>
+      <c r="A526" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="B526" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C526" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="D526" s="14">
+        <v>7.949394588E9</v>
+      </c>
+      <c r="E526" s="13">
+        <v>44.0</v>
+      </c>
+      <c r="F526" s="5"/>
+      <c r="G526" s="5"/>
+      <c r="H526" s="5"/>
+      <c r="I526" s="5"/>
+      <c r="J526" s="5"/>
+      <c r="K526" s="5"/>
     </row>
     <row r="527">
-      <c r="A527" s="24" t="s">
+      <c r="D527" s="11"/>
+      <c r="E527" s="11"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="B527" s="53"/>
-      <c r="C527" s="28"/>
-      <c r="D527" s="28"/>
-      <c r="E527" s="28"/>
-      <c r="F527" s="5"/>
-      <c r="G527" s="5"/>
-      <c r="H527" s="5"/>
-      <c r="I527" s="5"/>
-      <c r="J527" s="5"/>
-      <c r="K527" s="5"/>
-    </row>
-    <row r="528">
-      <c r="A528" s="12" t="s">
-        <v>557</v>
-      </c>
-      <c r="B528" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C528" s="14" t="s">
-        <v>558</v>
-      </c>
-      <c r="D528" s="14">
-        <v>7.791874716E9</v>
-      </c>
-      <c r="E528" s="14">
-        <v>44.0</v>
-      </c>
+      <c r="B528" s="53"/>
+      <c r="C528" s="28"/>
+      <c r="D528" s="28"/>
+      <c r="E528" s="28"/>
       <c r="F528" s="5"/>
       <c r="G528" s="5"/>
       <c r="H528" s="5"/>
@@ -15107,7 +15136,7 @@
     </row>
     <row r="529">
       <c r="A529" s="12" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B529" s="13">
         <v>1.0</v>
@@ -15116,10 +15145,10 @@
         <v>558</v>
       </c>
       <c r="D529" s="14">
-        <v>8.056354495E9</v>
+        <v>7.791874716E9</v>
       </c>
       <c r="E529" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F529" s="5"/>
       <c r="G529" s="5"/>
@@ -15130,7 +15159,7 @@
     </row>
     <row r="530">
       <c r="A530" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B530" s="13">
         <v>1.0</v>
@@ -15139,10 +15168,10 @@
         <v>558</v>
       </c>
       <c r="D530" s="14">
-        <v>7.411035443E9</v>
+        <v>8.056354495E9</v>
       </c>
       <c r="E530" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F530" s="5"/>
       <c r="G530" s="5"/>
@@ -15153,7 +15182,7 @@
     </row>
     <row r="531">
       <c r="A531" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B531" s="13">
         <v>1.0</v>
@@ -15162,10 +15191,10 @@
         <v>558</v>
       </c>
       <c r="D531" s="14">
-        <v>8.165478317E9</v>
+        <v>7.411035443E9</v>
       </c>
       <c r="E531" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F531" s="5"/>
       <c r="G531" s="5"/>
@@ -15176,7 +15205,7 @@
     </row>
     <row r="532">
       <c r="A532" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B532" s="13">
         <v>1.0</v>
@@ -15185,10 +15214,10 @@
         <v>558</v>
       </c>
       <c r="D532" s="14">
-        <v>7.910836315E9</v>
+        <v>8.165478317E9</v>
       </c>
       <c r="E532" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F532" s="5"/>
       <c r="G532" s="5"/>
@@ -15196,34 +15225,19 @@
       <c r="I532" s="5"/>
       <c r="J532" s="5"/>
       <c r="K532" s="5"/>
-      <c r="L532" s="27"/>
-      <c r="M532" s="27"/>
-      <c r="N532" s="27"/>
-      <c r="O532" s="27"/>
-      <c r="P532" s="27"/>
-      <c r="Q532" s="27"/>
-      <c r="R532" s="27"/>
-      <c r="S532" s="27"/>
-      <c r="T532" s="27"/>
-      <c r="U532" s="27"/>
-      <c r="V532" s="27"/>
-      <c r="W532" s="27"/>
-      <c r="X532" s="27"/>
-      <c r="Y532" s="27"/>
-      <c r="Z532" s="27"/>
     </row>
     <row r="533">
       <c r="A533" s="12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B533" s="13">
         <v>1.0</v>
       </c>
       <c r="C533" s="14" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D533" s="14">
-        <v>7.398843791E9</v>
+        <v>7.910836315E9</v>
       </c>
       <c r="E533" s="14">
         <v>44.0</v>
@@ -15234,18 +15248,33 @@
       <c r="I533" s="5"/>
       <c r="J533" s="5"/>
       <c r="K533" s="5"/>
+      <c r="L533" s="27"/>
+      <c r="M533" s="27"/>
+      <c r="N533" s="27"/>
+      <c r="O533" s="27"/>
+      <c r="P533" s="27"/>
+      <c r="Q533" s="27"/>
+      <c r="R533" s="27"/>
+      <c r="S533" s="27"/>
+      <c r="T533" s="27"/>
+      <c r="U533" s="27"/>
+      <c r="V533" s="27"/>
+      <c r="W533" s="27"/>
+      <c r="X533" s="27"/>
+      <c r="Y533" s="27"/>
+      <c r="Z533" s="27"/>
     </row>
     <row r="534">
-      <c r="A534" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B534" s="10">
+      <c r="A534" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B534" s="13">
         <v>1.0</v>
       </c>
       <c r="C534" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="D534" s="10">
+      <c r="D534" s="14">
         <v>7.398843791E9</v>
       </c>
       <c r="E534" s="14">
@@ -15260,7 +15289,7 @@
     </row>
     <row r="535">
       <c r="A535" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B535" s="10">
         <v>1.0</v>
@@ -15283,7 +15312,7 @@
     </row>
     <row r="536">
       <c r="A536" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B536" s="10">
         <v>1.0</v>
@@ -15305,20 +15334,20 @@
       <c r="K536" s="5"/>
     </row>
     <row r="537">
-      <c r="A537" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="B537" s="13">
+      <c r="A537" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="B537" s="10">
         <v>1.0</v>
       </c>
       <c r="C537" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="D537" s="13">
-        <v>8.078753239E9</v>
+        <v>564</v>
+      </c>
+      <c r="D537" s="10">
+        <v>7.398843791E9</v>
       </c>
       <c r="E537" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F537" s="5"/>
       <c r="G537" s="5"/>
@@ -15328,11 +15357,21 @@
       <c r="K537" s="5"/>
     </row>
     <row r="538">
-      <c r="A538" s="23"/>
-      <c r="B538" s="38"/>
-      <c r="C538" s="35"/>
-      <c r="D538" s="35"/>
-      <c r="E538" s="35"/>
+      <c r="A538" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="B538" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C538" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D538" s="13">
+        <v>8.078753239E9</v>
+      </c>
+      <c r="E538" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F538" s="5"/>
       <c r="G538" s="5"/>
       <c r="H538" s="5"/>
@@ -15341,13 +15380,11 @@
       <c r="K538" s="5"/>
     </row>
     <row r="539">
-      <c r="A539" s="47" t="s">
-        <v>569</v>
-      </c>
-      <c r="B539" s="48"/>
-      <c r="C539" s="48"/>
-      <c r="D539" s="48"/>
-      <c r="E539" s="48"/>
+      <c r="A539" s="23"/>
+      <c r="B539" s="38"/>
+      <c r="C539" s="35"/>
+      <c r="D539" s="35"/>
+      <c r="E539" s="35"/>
       <c r="F539" s="5"/>
       <c r="G539" s="5"/>
       <c r="H539" s="5"/>
@@ -15356,21 +15393,13 @@
       <c r="K539" s="5"/>
     </row>
     <row r="540">
-      <c r="A540" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="B540" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C540" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D540" s="14">
-        <v>8.034044331E9</v>
-      </c>
-      <c r="E540" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A540" s="47" t="s">
+        <v>569</v>
+      </c>
+      <c r="B540" s="48"/>
+      <c r="C540" s="48"/>
+      <c r="D540" s="48"/>
+      <c r="E540" s="48"/>
       <c r="F540" s="5"/>
       <c r="G540" s="5"/>
       <c r="H540" s="5"/>
@@ -15380,7 +15409,7 @@
     </row>
     <row r="541">
       <c r="A541" s="12" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B541" s="13">
         <v>1.0</v>
@@ -15389,7 +15418,7 @@
         <v>375</v>
       </c>
       <c r="D541" s="14">
-        <v>8.024662308E9</v>
+        <v>8.034044331E9</v>
       </c>
       <c r="E541" s="14">
         <v>234.0</v>
@@ -15400,25 +15429,10 @@
       <c r="I541" s="5"/>
       <c r="J541" s="5"/>
       <c r="K541" s="5"/>
-      <c r="L541" s="27"/>
-      <c r="M541" s="27"/>
-      <c r="N541" s="27"/>
-      <c r="O541" s="27"/>
-      <c r="P541" s="27"/>
-      <c r="Q541" s="27"/>
-      <c r="R541" s="27"/>
-      <c r="S541" s="27"/>
-      <c r="T541" s="27"/>
-      <c r="U541" s="27"/>
-      <c r="V541" s="27"/>
-      <c r="W541" s="27"/>
-      <c r="X541" s="27"/>
-      <c r="Y541" s="27"/>
-      <c r="Z541" s="27"/>
     </row>
     <row r="542">
       <c r="A542" s="12" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B542" s="13">
         <v>1.0</v>
@@ -15427,7 +15441,7 @@
         <v>375</v>
       </c>
       <c r="D542" s="14">
-        <v>8.03372284E9</v>
+        <v>8.024662308E9</v>
       </c>
       <c r="E542" s="14">
         <v>234.0</v>
@@ -15456,7 +15470,7 @@
     </row>
     <row r="543">
       <c r="A543" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B543" s="13">
         <v>1.0</v>
@@ -15465,7 +15479,7 @@
         <v>375</v>
       </c>
       <c r="D543" s="14">
-        <v>8.023136659E9</v>
+        <v>8.03372284E9</v>
       </c>
       <c r="E543" s="14">
         <v>234.0</v>
@@ -15476,10 +15490,25 @@
       <c r="I543" s="5"/>
       <c r="J543" s="5"/>
       <c r="K543" s="5"/>
+      <c r="L543" s="27"/>
+      <c r="M543" s="27"/>
+      <c r="N543" s="27"/>
+      <c r="O543" s="27"/>
+      <c r="P543" s="27"/>
+      <c r="Q543" s="27"/>
+      <c r="R543" s="27"/>
+      <c r="S543" s="27"/>
+      <c r="T543" s="27"/>
+      <c r="U543" s="27"/>
+      <c r="V543" s="27"/>
+      <c r="W543" s="27"/>
+      <c r="X543" s="27"/>
+      <c r="Y543" s="27"/>
+      <c r="Z543" s="27"/>
     </row>
     <row r="544">
       <c r="A544" s="12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B544" s="13">
         <v>1.0</v>
@@ -15488,7 +15517,7 @@
         <v>375</v>
       </c>
       <c r="D544" s="14">
-        <v>8.023414386E9</v>
+        <v>8.023136659E9</v>
       </c>
       <c r="E544" s="14">
         <v>234.0</v>
@@ -15502,7 +15531,7 @@
     </row>
     <row r="545">
       <c r="A545" s="12" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B545" s="13">
         <v>1.0</v>
@@ -15511,7 +15540,7 @@
         <v>375</v>
       </c>
       <c r="D545" s="14">
-        <v>8.035715044E9</v>
+        <v>8.023414386E9</v>
       </c>
       <c r="E545" s="14">
         <v>234.0</v>
@@ -15525,7 +15554,7 @@
     </row>
     <row r="546">
       <c r="A546" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B546" s="13">
         <v>1.0</v>
@@ -15548,7 +15577,7 @@
     </row>
     <row r="547">
       <c r="A547" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B547" s="13">
         <v>1.0</v>
@@ -15557,7 +15586,7 @@
         <v>375</v>
       </c>
       <c r="D547" s="14">
-        <v>7.017822252E9</v>
+        <v>8.035715044E9</v>
       </c>
       <c r="E547" s="14">
         <v>234.0</v>
@@ -15571,7 +15600,7 @@
     </row>
     <row r="548">
       <c r="A548" s="12" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B548" s="13">
         <v>1.0</v>
@@ -15580,7 +15609,7 @@
         <v>375</v>
       </c>
       <c r="D548" s="14">
-        <v>8.033151449E9</v>
+        <v>7.017822252E9</v>
       </c>
       <c r="E548" s="14">
         <v>234.0</v>
@@ -15594,7 +15623,7 @@
     </row>
     <row r="549">
       <c r="A549" s="12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B549" s="13">
         <v>1.0</v>
@@ -15603,7 +15632,7 @@
         <v>375</v>
       </c>
       <c r="D549" s="14">
-        <v>8.03407192E9</v>
+        <v>8.033151449E9</v>
       </c>
       <c r="E549" s="14">
         <v>234.0</v>
@@ -15616,10 +15645,21 @@
       <c r="K549" s="5"/>
     </row>
     <row r="550">
-      <c r="B550" s="19"/>
-      <c r="C550" s="20"/>
-      <c r="D550" s="20"/>
-      <c r="E550" s="33"/>
+      <c r="A550" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B550" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C550" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D550" s="14">
+        <v>8.03407192E9</v>
+      </c>
+      <c r="E550" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F550" s="5"/>
       <c r="G550" s="5"/>
       <c r="H550" s="5"/>
@@ -15628,13 +15668,10 @@
       <c r="K550" s="5"/>
     </row>
     <row r="551">
-      <c r="A551" s="54" t="s">
-        <v>580</v>
-      </c>
-      <c r="B551" s="25"/>
-      <c r="C551" s="26"/>
-      <c r="D551" s="26"/>
-      <c r="E551" s="26"/>
+      <c r="B551" s="19"/>
+      <c r="C551" s="20"/>
+      <c r="D551" s="20"/>
+      <c r="E551" s="33"/>
       <c r="F551" s="5"/>
       <c r="G551" s="5"/>
       <c r="H551" s="5"/>
@@ -15643,46 +15680,23 @@
       <c r="K551" s="5"/>
     </row>
     <row r="552">
-      <c r="A552" s="55" t="s">
-        <v>581</v>
-      </c>
-      <c r="B552" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="C552" s="41" t="s">
-        <v>375</v>
-      </c>
-      <c r="D552" s="41">
-        <v>8.136664029E9</v>
-      </c>
-      <c r="E552" s="41">
-        <v>234.0</v>
-      </c>
-      <c r="F552" s="42"/>
-      <c r="G552" s="42"/>
-      <c r="H552" s="42"/>
-      <c r="I552" s="42"/>
-      <c r="J552" s="42"/>
-      <c r="K552" s="42"/>
-      <c r="L552" s="42"/>
-      <c r="M552" s="42"/>
-      <c r="N552" s="42"/>
-      <c r="O552" s="42"/>
-      <c r="P552" s="42"/>
-      <c r="Q552" s="42"/>
-      <c r="R552" s="42"/>
-      <c r="S552" s="42"/>
-      <c r="T552" s="42"/>
-      <c r="U552" s="42"/>
-      <c r="V552" s="42"/>
-      <c r="W552" s="42"/>
-      <c r="X552" s="42"/>
-      <c r="Y552" s="42"/>
-      <c r="Z552" s="42"/>
+      <c r="A552" s="54" t="s">
+        <v>580</v>
+      </c>
+      <c r="B552" s="25"/>
+      <c r="C552" s="26"/>
+      <c r="D552" s="26"/>
+      <c r="E552" s="26"/>
+      <c r="F552" s="5"/>
+      <c r="G552" s="5"/>
+      <c r="H552" s="5"/>
+      <c r="I552" s="5"/>
+      <c r="J552" s="5"/>
+      <c r="K552" s="5"/>
     </row>
     <row r="553">
       <c r="A553" s="55" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B553" s="56">
         <v>1.0</v>
@@ -15693,7 +15707,7 @@
       <c r="D553" s="41">
         <v>8.136664029E9</v>
       </c>
-      <c r="E553" s="56">
+      <c r="E553" s="41">
         <v>234.0</v>
       </c>
       <c r="F553" s="42"/>
@@ -15719,31 +15733,46 @@
       <c r="Z553" s="42"/>
     </row>
     <row r="554">
-      <c r="A554" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="B554" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C554" s="14" t="s">
+      <c r="A554" s="55" t="s">
+        <v>582</v>
+      </c>
+      <c r="B554" s="56">
+        <v>1.0</v>
+      </c>
+      <c r="C554" s="41" t="s">
         <v>375</v>
       </c>
-      <c r="D554" s="14">
-        <v>9.097029083E9</v>
-      </c>
-      <c r="E554" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F554" s="5"/>
-      <c r="G554" s="5"/>
-      <c r="H554" s="5"/>
-      <c r="I554" s="5"/>
-      <c r="J554" s="5"/>
-      <c r="K554" s="5"/>
+      <c r="D554" s="41">
+        <v>8.136664029E9</v>
+      </c>
+      <c r="E554" s="56">
+        <v>234.0</v>
+      </c>
+      <c r="F554" s="42"/>
+      <c r="G554" s="42"/>
+      <c r="H554" s="42"/>
+      <c r="I554" s="42"/>
+      <c r="J554" s="42"/>
+      <c r="K554" s="42"/>
+      <c r="L554" s="42"/>
+      <c r="M554" s="42"/>
+      <c r="N554" s="42"/>
+      <c r="O554" s="42"/>
+      <c r="P554" s="42"/>
+      <c r="Q554" s="42"/>
+      <c r="R554" s="42"/>
+      <c r="S554" s="42"/>
+      <c r="T554" s="42"/>
+      <c r="U554" s="42"/>
+      <c r="V554" s="42"/>
+      <c r="W554" s="42"/>
+      <c r="X554" s="42"/>
+      <c r="Y554" s="42"/>
+      <c r="Z554" s="42"/>
     </row>
     <row r="555">
       <c r="A555" s="12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B555" s="13">
         <v>1.0</v>
@@ -15766,7 +15795,7 @@
     </row>
     <row r="556">
       <c r="A556" s="12" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B556" s="13">
         <v>1.0</v>
@@ -15775,7 +15804,7 @@
         <v>375</v>
       </c>
       <c r="D556" s="14">
-        <v>8.023368979E9</v>
+        <v>9.097029083E9</v>
       </c>
       <c r="E556" s="14">
         <v>234.0</v>
@@ -15789,7 +15818,7 @@
     </row>
     <row r="557">
       <c r="A557" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B557" s="13">
         <v>1.0</v>
@@ -15812,16 +15841,16 @@
     </row>
     <row r="558">
       <c r="A558" s="12" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B558" s="13">
         <v>1.0</v>
       </c>
       <c r="C558" s="14" t="s">
-        <v>588</v>
+        <v>375</v>
       </c>
       <c r="D558" s="14">
-        <v>8.033168467E9</v>
+        <v>8.023368979E9</v>
       </c>
       <c r="E558" s="14">
         <v>234.0</v>
@@ -15835,7 +15864,7 @@
     </row>
     <row r="559">
       <c r="A559" s="12" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B559" s="13">
         <v>1.0</v>
@@ -15858,16 +15887,16 @@
     </row>
     <row r="560">
       <c r="A560" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B560" s="13">
         <v>1.0</v>
       </c>
       <c r="C560" s="14" t="s">
-        <v>388</v>
+        <v>588</v>
       </c>
       <c r="D560" s="14">
-        <v>8.033263138E9</v>
+        <v>8.033168467E9</v>
       </c>
       <c r="E560" s="14">
         <v>234.0</v>
@@ -15880,8 +15909,8 @@
       <c r="K560" s="5"/>
     </row>
     <row r="561">
-      <c r="A561" s="29" t="s">
-        <v>591</v>
+      <c r="A561" s="12" t="s">
+        <v>590</v>
       </c>
       <c r="B561" s="13">
         <v>1.0</v>
@@ -15890,7 +15919,7 @@
         <v>388</v>
       </c>
       <c r="D561" s="14">
-        <v>8.028996353E9</v>
+        <v>8.033263138E9</v>
       </c>
       <c r="E561" s="14">
         <v>234.0</v>
@@ -15903,11 +15932,21 @@
       <c r="K561" s="5"/>
     </row>
     <row r="562">
-      <c r="A562" s="29"/>
-      <c r="B562" s="13"/>
-      <c r="C562" s="14"/>
-      <c r="D562" s="14"/>
-      <c r="E562" s="14"/>
+      <c r="A562" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="B562" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C562" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D562" s="14">
+        <v>8.028996353E9</v>
+      </c>
+      <c r="E562" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F562" s="5"/>
       <c r="G562" s="5"/>
       <c r="H562" s="5"/>
@@ -15916,13 +15955,11 @@
       <c r="K562" s="5"/>
     </row>
     <row r="563">
-      <c r="A563" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="B563" s="25"/>
-      <c r="C563" s="26"/>
-      <c r="D563" s="26"/>
-      <c r="E563" s="28"/>
+      <c r="A563" s="29"/>
+      <c r="B563" s="13"/>
+      <c r="C563" s="14"/>
+      <c r="D563" s="14"/>
+      <c r="E563" s="14"/>
       <c r="F563" s="5"/>
       <c r="G563" s="5"/>
       <c r="H563" s="5"/>
@@ -15931,21 +15968,13 @@
       <c r="K563" s="5"/>
     </row>
     <row r="564">
-      <c r="A564" s="12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B564" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C564" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D564" s="9">
-        <v>8.033269954E9</v>
-      </c>
-      <c r="E564" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A564" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="B564" s="25"/>
+      <c r="C564" s="26"/>
+      <c r="D564" s="26"/>
+      <c r="E564" s="28"/>
       <c r="F564" s="5"/>
       <c r="G564" s="5"/>
       <c r="H564" s="5"/>
@@ -15955,7 +15984,7 @@
     </row>
     <row r="565">
       <c r="A565" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B565" s="13">
         <v>1.0</v>
@@ -15963,8 +15992,8 @@
       <c r="C565" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D565" s="14">
-        <v>8.023154013E9</v>
+      <c r="D565" s="9">
+        <v>8.033269954E9</v>
       </c>
       <c r="E565" s="14">
         <v>234.0</v>
@@ -15978,7 +16007,7 @@
     </row>
     <row r="566">
       <c r="A566" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B566" s="13">
         <v>1.0</v>
@@ -15987,7 +16016,7 @@
         <v>375</v>
       </c>
       <c r="D566" s="14">
-        <v>8.033047088E9</v>
+        <v>8.023154013E9</v>
       </c>
       <c r="E566" s="14">
         <v>234.0</v>
@@ -16001,7 +16030,7 @@
     </row>
     <row r="567">
       <c r="A567" s="12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B567" s="13">
         <v>1.0</v>
@@ -16024,7 +16053,7 @@
     </row>
     <row r="568">
       <c r="A568" s="12" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B568" s="13">
         <v>1.0</v>
@@ -16033,7 +16062,7 @@
         <v>375</v>
       </c>
       <c r="D568" s="14">
-        <v>8.023221192E9</v>
+        <v>8.033047088E9</v>
       </c>
       <c r="E568" s="14">
         <v>234.0</v>
@@ -16047,7 +16076,7 @@
     </row>
     <row r="569">
       <c r="A569" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B569" s="13">
         <v>1.0</v>
@@ -16056,7 +16085,7 @@
         <v>375</v>
       </c>
       <c r="D569" s="14">
-        <v>8.0330693389E10</v>
+        <v>8.023221192E9</v>
       </c>
       <c r="E569" s="14">
         <v>234.0</v>
@@ -16070,7 +16099,7 @@
     </row>
     <row r="570">
       <c r="A570" s="12" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B570" s="13">
         <v>1.0</v>
@@ -16079,7 +16108,7 @@
         <v>375</v>
       </c>
       <c r="D570" s="14">
-        <v>8.037404128E9</v>
+        <v>8.0330693389E10</v>
       </c>
       <c r="E570" s="14">
         <v>234.0</v>
@@ -16093,7 +16122,7 @@
     </row>
     <row r="571">
       <c r="A571" s="12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B571" s="13">
         <v>1.0</v>
@@ -16116,7 +16145,7 @@
     </row>
     <row r="572">
       <c r="A572" s="12" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B572" s="13">
         <v>1.0</v>
@@ -16124,11 +16153,11 @@
       <c r="C572" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D572" s="14" t="s">
-        <v>602</v>
+      <c r="D572" s="14">
+        <v>8.037404128E9</v>
       </c>
       <c r="E572" s="14">
-        <v>1.0</v>
+        <v>234.0</v>
       </c>
       <c r="F572" s="5"/>
       <c r="G572" s="5"/>
@@ -16139,7 +16168,7 @@
     </row>
     <row r="573">
       <c r="A573" s="12" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B573" s="13">
         <v>1.0</v>
@@ -16148,7 +16177,7 @@
         <v>375</v>
       </c>
       <c r="D573" s="14" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E573" s="14">
         <v>1.0</v>
@@ -16161,11 +16190,21 @@
       <c r="K573" s="5"/>
     </row>
     <row r="574">
-      <c r="A574" s="12"/>
-      <c r="B574" s="13"/>
-      <c r="C574" s="14"/>
-      <c r="D574" s="14"/>
-      <c r="E574" s="14"/>
+      <c r="A574" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="B574" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C574" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D574" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="E574" s="14">
+        <v>1.0</v>
+      </c>
       <c r="F574" s="5"/>
       <c r="G574" s="5"/>
       <c r="H574" s="5"/>
@@ -16174,13 +16213,11 @@
       <c r="K574" s="5"/>
     </row>
     <row r="575">
-      <c r="A575" s="24" t="s">
-        <v>605</v>
-      </c>
-      <c r="B575" s="25"/>
-      <c r="C575" s="26"/>
-      <c r="D575" s="26"/>
-      <c r="E575" s="28"/>
+      <c r="A575" s="12"/>
+      <c r="B575" s="13"/>
+      <c r="C575" s="14"/>
+      <c r="D575" s="14"/>
+      <c r="E575" s="14"/>
       <c r="F575" s="5"/>
       <c r="G575" s="5"/>
       <c r="H575" s="5"/>
@@ -16189,46 +16226,23 @@
       <c r="K575" s="5"/>
     </row>
     <row r="576">
-      <c r="A576" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="B576" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C576" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D576" s="14">
-        <v>8.023230526E9</v>
-      </c>
-      <c r="E576" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A576" s="24" t="s">
+        <v>605</v>
+      </c>
+      <c r="B576" s="25"/>
+      <c r="C576" s="26"/>
+      <c r="D576" s="26"/>
+      <c r="E576" s="28"/>
       <c r="F576" s="5"/>
       <c r="G576" s="5"/>
       <c r="H576" s="5"/>
       <c r="I576" s="5"/>
       <c r="J576" s="5"/>
       <c r="K576" s="5"/>
-      <c r="L576" s="27"/>
-      <c r="M576" s="27"/>
-      <c r="N576" s="27"/>
-      <c r="O576" s="27"/>
-      <c r="P576" s="27"/>
-      <c r="Q576" s="27"/>
-      <c r="R576" s="27"/>
-      <c r="S576" s="27"/>
-      <c r="T576" s="27"/>
-      <c r="U576" s="27"/>
-      <c r="V576" s="27"/>
-      <c r="W576" s="27"/>
-      <c r="X576" s="27"/>
-      <c r="Y576" s="27"/>
-      <c r="Z576" s="27"/>
     </row>
     <row r="577">
       <c r="A577" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B577" s="13">
         <v>1.0</v>
@@ -16266,7 +16280,7 @@
     </row>
     <row r="578">
       <c r="A578" s="12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B578" s="13">
         <v>1.0</v>
@@ -16275,7 +16289,7 @@
         <v>375</v>
       </c>
       <c r="D578" s="14">
-        <v>7.053152586E9</v>
+        <v>8.023230526E9</v>
       </c>
       <c r="E578" s="14">
         <v>234.0</v>
@@ -16286,10 +16300,25 @@
       <c r="I578" s="5"/>
       <c r="J578" s="5"/>
       <c r="K578" s="5"/>
+      <c r="L578" s="27"/>
+      <c r="M578" s="27"/>
+      <c r="N578" s="27"/>
+      <c r="O578" s="27"/>
+      <c r="P578" s="27"/>
+      <c r="Q578" s="27"/>
+      <c r="R578" s="27"/>
+      <c r="S578" s="27"/>
+      <c r="T578" s="27"/>
+      <c r="U578" s="27"/>
+      <c r="V578" s="27"/>
+      <c r="W578" s="27"/>
+      <c r="X578" s="27"/>
+      <c r="Y578" s="27"/>
+      <c r="Z578" s="27"/>
     </row>
     <row r="579">
       <c r="A579" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B579" s="13">
         <v>1.0</v>
@@ -16312,7 +16341,7 @@
     </row>
     <row r="580">
       <c r="A580" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B580" s="13">
         <v>1.0</v>
@@ -16321,7 +16350,7 @@
         <v>375</v>
       </c>
       <c r="D580" s="14">
-        <v>8.034360992E9</v>
+        <v>7.053152586E9</v>
       </c>
       <c r="E580" s="14">
         <v>234.0</v>
@@ -16335,7 +16364,7 @@
     </row>
     <row r="581">
       <c r="A581" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B581" s="13">
         <v>1.0</v>
@@ -16358,7 +16387,7 @@
     </row>
     <row r="582">
       <c r="A582" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B582" s="13">
         <v>1.0</v>
@@ -16367,7 +16396,7 @@
         <v>375</v>
       </c>
       <c r="D582" s="14">
-        <v>8.09944006E9</v>
+        <v>8.034360992E9</v>
       </c>
       <c r="E582" s="14">
         <v>234.0</v>
@@ -16381,7 +16410,7 @@
     </row>
     <row r="583">
       <c r="A583" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B583" s="13">
         <v>1.0</v>
@@ -16404,7 +16433,7 @@
     </row>
     <row r="584">
       <c r="A584" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B584" s="13">
         <v>1.0</v>
@@ -16413,7 +16442,7 @@
         <v>375</v>
       </c>
       <c r="D584" s="14">
-        <v>8.089886511E9</v>
+        <v>8.09944006E9</v>
       </c>
       <c r="E584" s="14">
         <v>234.0</v>
@@ -16427,7 +16456,7 @@
     </row>
     <row r="585">
       <c r="A585" s="12" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B585" s="13">
         <v>1.0</v>
@@ -16449,11 +16478,21 @@
       <c r="K585" s="5"/>
     </row>
     <row r="586">
-      <c r="A586" s="12"/>
-      <c r="B586" s="13"/>
-      <c r="C586" s="14"/>
-      <c r="D586" s="14"/>
-      <c r="E586" s="14"/>
+      <c r="A586" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="B586" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C586" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D586" s="14">
+        <v>8.089886511E9</v>
+      </c>
+      <c r="E586" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F586" s="5"/>
       <c r="G586" s="5"/>
       <c r="H586" s="5"/>
@@ -16462,61 +16501,51 @@
       <c r="K586" s="5"/>
     </row>
     <row r="587">
-      <c r="A587" s="24" t="s">
+      <c r="A587" s="12"/>
+      <c r="B587" s="13"/>
+      <c r="C587" s="14"/>
+      <c r="D587" s="14"/>
+      <c r="E587" s="14"/>
+      <c r="F587" s="5"/>
+      <c r="G587" s="5"/>
+      <c r="H587" s="5"/>
+      <c r="I587" s="5"/>
+      <c r="J587" s="5"/>
+      <c r="K587" s="5"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="24" t="s">
         <v>616</v>
       </c>
-      <c r="B587" s="25"/>
-      <c r="C587" s="26"/>
-      <c r="D587" s="26"/>
-      <c r="E587" s="26"/>
-      <c r="F587" s="27"/>
-      <c r="G587" s="27"/>
-      <c r="H587" s="27"/>
-      <c r="I587" s="27"/>
-      <c r="J587" s="27"/>
-      <c r="K587" s="27"/>
-      <c r="L587" s="27"/>
-      <c r="M587" s="27"/>
-      <c r="N587" s="27"/>
-      <c r="O587" s="27"/>
-      <c r="P587" s="27"/>
-      <c r="Q587" s="27"/>
-      <c r="R587" s="27"/>
-      <c r="S587" s="27"/>
-      <c r="T587" s="27"/>
-      <c r="U587" s="27"/>
-      <c r="V587" s="27"/>
-      <c r="W587" s="27"/>
-      <c r="X587" s="27"/>
-      <c r="Y587" s="27"/>
-      <c r="Z587" s="27"/>
-    </row>
-    <row r="588">
-      <c r="A588" s="12" t="s">
-        <v>617</v>
-      </c>
-      <c r="B588" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C588" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D588" s="14">
-        <v>8.092731761E9</v>
-      </c>
-      <c r="E588" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F588" s="5"/>
-      <c r="G588" s="5"/>
-      <c r="H588" s="5"/>
-      <c r="I588" s="5"/>
-      <c r="J588" s="5"/>
-      <c r="K588" s="5"/>
+      <c r="B588" s="25"/>
+      <c r="C588" s="26"/>
+      <c r="D588" s="26"/>
+      <c r="E588" s="26"/>
+      <c r="F588" s="27"/>
+      <c r="G588" s="27"/>
+      <c r="H588" s="27"/>
+      <c r="I588" s="27"/>
+      <c r="J588" s="27"/>
+      <c r="K588" s="27"/>
+      <c r="L588" s="27"/>
+      <c r="M588" s="27"/>
+      <c r="N588" s="27"/>
+      <c r="O588" s="27"/>
+      <c r="P588" s="27"/>
+      <c r="Q588" s="27"/>
+      <c r="R588" s="27"/>
+      <c r="S588" s="27"/>
+      <c r="T588" s="27"/>
+      <c r="U588" s="27"/>
+      <c r="V588" s="27"/>
+      <c r="W588" s="27"/>
+      <c r="X588" s="27"/>
+      <c r="Y588" s="27"/>
+      <c r="Z588" s="27"/>
     </row>
     <row r="589">
       <c r="A589" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B589" s="13">
         <v>1.0</v>
@@ -16525,7 +16554,7 @@
         <v>375</v>
       </c>
       <c r="D589" s="14">
-        <v>8.033329207E9</v>
+        <v>8.092731761E9</v>
       </c>
       <c r="E589" s="14">
         <v>234.0</v>
@@ -16539,7 +16568,7 @@
     </row>
     <row r="590">
       <c r="A590" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B590" s="13">
         <v>1.0</v>
@@ -16548,7 +16577,7 @@
         <v>375</v>
       </c>
       <c r="D590" s="14">
-        <v>8.023057851E9</v>
+        <v>8.033329207E9</v>
       </c>
       <c r="E590" s="14">
         <v>234.0</v>
@@ -16562,7 +16591,7 @@
     </row>
     <row r="591">
       <c r="A591" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B591" s="13">
         <v>1.0</v>
@@ -16585,7 +16614,7 @@
     </row>
     <row r="592">
       <c r="A592" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B592" s="13">
         <v>1.0</v>
@@ -16594,7 +16623,7 @@
         <v>375</v>
       </c>
       <c r="D592" s="14">
-        <v>8.029726428E9</v>
+        <v>8.023057851E9</v>
       </c>
       <c r="E592" s="14">
         <v>234.0</v>
@@ -16608,7 +16637,7 @@
     </row>
     <row r="593">
       <c r="A593" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B593" s="13">
         <v>1.0</v>
@@ -16617,7 +16646,7 @@
         <v>375</v>
       </c>
       <c r="D593" s="14">
-        <v>8.092902312E9</v>
+        <v>8.029726428E9</v>
       </c>
       <c r="E593" s="14">
         <v>234.0</v>
@@ -16631,7 +16660,7 @@
     </row>
     <row r="594">
       <c r="A594" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B594" s="13">
         <v>1.0</v>
@@ -16640,7 +16669,7 @@
         <v>375</v>
       </c>
       <c r="D594" s="14">
-        <v>8.023551119E9</v>
+        <v>8.092902312E9</v>
       </c>
       <c r="E594" s="14">
         <v>234.0</v>
@@ -16654,7 +16683,7 @@
     </row>
     <row r="595">
       <c r="A595" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B595" s="13">
         <v>1.0</v>
@@ -16677,7 +16706,7 @@
     </row>
     <row r="596">
       <c r="A596" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B596" s="13">
         <v>1.0</v>
@@ -16685,8 +16714,8 @@
       <c r="C596" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D596" s="13">
-        <v>8.023012426E9</v>
+      <c r="D596" s="14">
+        <v>8.023551119E9</v>
       </c>
       <c r="E596" s="14">
         <v>234.0</v>
@@ -16700,16 +16729,16 @@
     </row>
     <row r="597">
       <c r="A597" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B597" s="13">
         <v>1.0</v>
       </c>
       <c r="C597" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="D597" s="14">
-        <v>8.023506307E9</v>
+        <v>375</v>
+      </c>
+      <c r="D597" s="13">
+        <v>8.023012426E9</v>
       </c>
       <c r="E597" s="14">
         <v>234.0</v>
@@ -16722,11 +16751,21 @@
       <c r="K597" s="5"/>
     </row>
     <row r="598">
-      <c r="A598" s="12"/>
-      <c r="B598" s="13"/>
-      <c r="C598" s="14"/>
-      <c r="D598" s="14"/>
-      <c r="E598" s="14"/>
+      <c r="A598" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B598" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C598" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="D598" s="14">
+        <v>8.023506307E9</v>
+      </c>
+      <c r="E598" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F598" s="5"/>
       <c r="G598" s="5"/>
       <c r="H598" s="5"/>
@@ -16735,61 +16774,51 @@
       <c r="K598" s="5"/>
     </row>
     <row r="599">
-      <c r="A599" s="24" t="s">
+      <c r="A599" s="12"/>
+      <c r="B599" s="13"/>
+      <c r="C599" s="14"/>
+      <c r="D599" s="14"/>
+      <c r="E599" s="14"/>
+      <c r="F599" s="5"/>
+      <c r="G599" s="5"/>
+      <c r="H599" s="5"/>
+      <c r="I599" s="5"/>
+      <c r="J599" s="5"/>
+      <c r="K599" s="5"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="24" t="s">
         <v>628</v>
       </c>
-      <c r="B599" s="25"/>
-      <c r="C599" s="26"/>
-      <c r="D599" s="25"/>
-      <c r="E599" s="26"/>
-      <c r="F599" s="27"/>
-      <c r="G599" s="27"/>
-      <c r="H599" s="27"/>
-      <c r="I599" s="27"/>
-      <c r="J599" s="27"/>
-      <c r="K599" s="27"/>
-      <c r="L599" s="27"/>
-      <c r="M599" s="27"/>
-      <c r="N599" s="27"/>
-      <c r="O599" s="27"/>
-      <c r="P599" s="27"/>
-      <c r="Q599" s="27"/>
-      <c r="R599" s="27"/>
-      <c r="S599" s="27"/>
-      <c r="T599" s="27"/>
-      <c r="U599" s="27"/>
-      <c r="V599" s="27"/>
-      <c r="W599" s="27"/>
-      <c r="X599" s="27"/>
-      <c r="Y599" s="27"/>
-      <c r="Z599" s="27"/>
-    </row>
-    <row r="600">
-      <c r="A600" s="12" t="s">
-        <v>629</v>
-      </c>
-      <c r="B600" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C600" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D600" s="13">
-        <v>8.182612222E9</v>
-      </c>
-      <c r="E600" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F600" s="5"/>
-      <c r="G600" s="5"/>
-      <c r="H600" s="5"/>
-      <c r="I600" s="5"/>
-      <c r="J600" s="5"/>
-      <c r="K600" s="5"/>
+      <c r="B600" s="25"/>
+      <c r="C600" s="26"/>
+      <c r="D600" s="25"/>
+      <c r="E600" s="26"/>
+      <c r="F600" s="27"/>
+      <c r="G600" s="27"/>
+      <c r="H600" s="27"/>
+      <c r="I600" s="27"/>
+      <c r="J600" s="27"/>
+      <c r="K600" s="27"/>
+      <c r="L600" s="27"/>
+      <c r="M600" s="27"/>
+      <c r="N600" s="27"/>
+      <c r="O600" s="27"/>
+      <c r="P600" s="27"/>
+      <c r="Q600" s="27"/>
+      <c r="R600" s="27"/>
+      <c r="S600" s="27"/>
+      <c r="T600" s="27"/>
+      <c r="U600" s="27"/>
+      <c r="V600" s="27"/>
+      <c r="W600" s="27"/>
+      <c r="X600" s="27"/>
+      <c r="Y600" s="27"/>
+      <c r="Z600" s="27"/>
     </row>
     <row r="601">
       <c r="A601" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B601" s="13">
         <v>1.0</v>
@@ -16812,7 +16841,7 @@
     </row>
     <row r="602">
       <c r="A602" s="12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B602" s="13">
         <v>1.0</v>
@@ -16821,7 +16850,7 @@
         <v>375</v>
       </c>
       <c r="D602" s="13">
-        <v>8.026656748E9</v>
+        <v>8.182612222E9</v>
       </c>
       <c r="E602" s="14">
         <v>234.0</v>
@@ -16835,7 +16864,7 @@
     </row>
     <row r="603">
       <c r="A603" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B603" s="13">
         <v>1.0</v>
@@ -16844,7 +16873,7 @@
         <v>375</v>
       </c>
       <c r="D603" s="13">
-        <v>8.023316251E9</v>
+        <v>8.026656748E9</v>
       </c>
       <c r="E603" s="14">
         <v>234.0</v>
@@ -16858,7 +16887,7 @@
     </row>
     <row r="604">
       <c r="A604" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B604" s="13">
         <v>1.0</v>
@@ -16881,7 +16910,7 @@
     </row>
     <row r="605">
       <c r="A605" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B605" s="13">
         <v>1.0</v>
@@ -16890,10 +16919,10 @@
         <v>375</v>
       </c>
       <c r="D605" s="13">
-        <v>7.467166671E9</v>
+        <v>8.023316251E9</v>
       </c>
       <c r="E605" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F605" s="5"/>
       <c r="G605" s="5"/>
@@ -16904,7 +16933,7 @@
     </row>
     <row r="606">
       <c r="A606" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B606" s="13">
         <v>1.0</v>
@@ -16927,19 +16956,19 @@
     </row>
     <row r="607">
       <c r="A607" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B607" s="13">
         <v>1.0</v>
       </c>
       <c r="C607" s="14" t="s">
-        <v>588</v>
-      </c>
-      <c r="D607" s="14">
-        <v>8.183103038E9</v>
+        <v>375</v>
+      </c>
+      <c r="D607" s="13">
+        <v>7.467166671E9</v>
       </c>
       <c r="E607" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F607" s="5"/>
       <c r="G607" s="5"/>
@@ -16950,7 +16979,7 @@
     </row>
     <row r="608">
       <c r="A608" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B608" s="13">
         <v>1.0</v>
@@ -16959,7 +16988,7 @@
         <v>588</v>
       </c>
       <c r="D608" s="14">
-        <v>7.03521206E9</v>
+        <v>8.183103038E9</v>
       </c>
       <c r="E608" s="14">
         <v>234.0</v>
@@ -16973,7 +17002,7 @@
     </row>
     <row r="609">
       <c r="A609" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B609" s="13">
         <v>1.0</v>
@@ -16995,11 +17024,21 @@
       <c r="K609" s="5"/>
     </row>
     <row r="610">
-      <c r="A610" s="12"/>
-      <c r="B610" s="13"/>
-      <c r="C610" s="14"/>
-      <c r="D610" s="14"/>
-      <c r="E610" s="35"/>
+      <c r="A610" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="B610" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C610" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="D610" s="14">
+        <v>7.03521206E9</v>
+      </c>
+      <c r="E610" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F610" s="5"/>
       <c r="G610" s="5"/>
       <c r="H610" s="5"/>
@@ -17008,13 +17047,11 @@
       <c r="K610" s="5"/>
     </row>
     <row r="611">
-      <c r="A611" s="47" t="s">
-        <v>639</v>
-      </c>
-      <c r="B611" s="48"/>
-      <c r="C611" s="48"/>
-      <c r="D611" s="48"/>
-      <c r="E611" s="48"/>
+      <c r="A611" s="12"/>
+      <c r="B611" s="13"/>
+      <c r="C611" s="14"/>
+      <c r="D611" s="14"/>
+      <c r="E611" s="35"/>
       <c r="F611" s="5"/>
       <c r="G611" s="5"/>
       <c r="H611" s="5"/>
@@ -17023,21 +17060,13 @@
       <c r="K611" s="5"/>
     </row>
     <row r="612">
-      <c r="A612" s="12" t="s">
-        <v>640</v>
-      </c>
-      <c r="B612" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C612" s="14" t="s">
-        <v>641</v>
-      </c>
-      <c r="D612" s="14">
-        <v>8.023005676E9</v>
-      </c>
-      <c r="E612" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A612" s="47" t="s">
+        <v>639</v>
+      </c>
+      <c r="B612" s="48"/>
+      <c r="C612" s="48"/>
+      <c r="D612" s="48"/>
+      <c r="E612" s="48"/>
       <c r="F612" s="5"/>
       <c r="G612" s="5"/>
       <c r="H612" s="5"/>
@@ -17047,7 +17076,7 @@
     </row>
     <row r="613">
       <c r="A613" s="12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B613" s="13">
         <v>1.0</v>
@@ -17056,7 +17085,7 @@
         <v>641</v>
       </c>
       <c r="D613" s="14">
-        <v>8.0233004E9</v>
+        <v>8.023005676E9</v>
       </c>
       <c r="E613" s="14">
         <v>234.0</v>
@@ -17070,7 +17099,7 @@
     </row>
     <row r="614">
       <c r="A614" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B614" s="13">
         <v>1.0</v>
@@ -17079,7 +17108,7 @@
         <v>641</v>
       </c>
       <c r="D614" s="14">
-        <v>9.115911396E9</v>
+        <v>8.0233004E9</v>
       </c>
       <c r="E614" s="14">
         <v>234.0</v>
@@ -17093,7 +17122,7 @@
     </row>
     <row r="615">
       <c r="A615" s="12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B615" s="13">
         <v>1.0</v>
@@ -17102,7 +17131,7 @@
         <v>641</v>
       </c>
       <c r="D615" s="14">
-        <v>8.027352376E9</v>
+        <v>9.115911396E9</v>
       </c>
       <c r="E615" s="14">
         <v>234.0</v>
@@ -17116,7 +17145,7 @@
     </row>
     <row r="616">
       <c r="A616" s="12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B616" s="13">
         <v>1.0</v>
@@ -17125,7 +17154,7 @@
         <v>641</v>
       </c>
       <c r="D616" s="14">
-        <v>8.163341596E9</v>
+        <v>8.027352376E9</v>
       </c>
       <c r="E616" s="14">
         <v>234.0</v>
@@ -17136,25 +17165,10 @@
       <c r="I616" s="5"/>
       <c r="J616" s="5"/>
       <c r="K616" s="5"/>
-      <c r="L616" s="27"/>
-      <c r="M616" s="27"/>
-      <c r="N616" s="27"/>
-      <c r="O616" s="27"/>
-      <c r="P616" s="27"/>
-      <c r="Q616" s="27"/>
-      <c r="R616" s="27"/>
-      <c r="S616" s="27"/>
-      <c r="T616" s="27"/>
-      <c r="U616" s="27"/>
-      <c r="V616" s="27"/>
-      <c r="W616" s="27"/>
-      <c r="X616" s="27"/>
-      <c r="Y616" s="27"/>
-      <c r="Z616" s="27"/>
     </row>
     <row r="617">
       <c r="A617" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B617" s="13">
         <v>1.0</v>
@@ -17163,7 +17177,7 @@
         <v>641</v>
       </c>
       <c r="D617" s="14">
-        <v>8.078245569E9</v>
+        <v>8.163341596E9</v>
       </c>
       <c r="E617" s="14">
         <v>234.0</v>
@@ -17174,19 +17188,34 @@
       <c r="I617" s="5"/>
       <c r="J617" s="5"/>
       <c r="K617" s="5"/>
+      <c r="L617" s="27"/>
+      <c r="M617" s="27"/>
+      <c r="N617" s="27"/>
+      <c r="O617" s="27"/>
+      <c r="P617" s="27"/>
+      <c r="Q617" s="27"/>
+      <c r="R617" s="27"/>
+      <c r="S617" s="27"/>
+      <c r="T617" s="27"/>
+      <c r="U617" s="27"/>
+      <c r="V617" s="27"/>
+      <c r="W617" s="27"/>
+      <c r="X617" s="27"/>
+      <c r="Y617" s="27"/>
+      <c r="Z617" s="27"/>
     </row>
     <row r="618">
-      <c r="A618" s="29" t="s">
-        <v>647</v>
+      <c r="A618" s="12" t="s">
+        <v>646</v>
       </c>
       <c r="B618" s="13">
         <v>1.0</v>
       </c>
       <c r="C618" s="14" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="D618" s="14">
-        <v>8.06298339E9</v>
+        <v>8.078245569E9</v>
       </c>
       <c r="E618" s="14">
         <v>234.0</v>
@@ -17199,17 +17228,17 @@
       <c r="K618" s="5"/>
     </row>
     <row r="619">
-      <c r="A619" s="12" t="s">
-        <v>649</v>
+      <c r="A619" s="29" t="s">
+        <v>647</v>
       </c>
       <c r="B619" s="13">
         <v>1.0</v>
       </c>
       <c r="C619" s="14" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="D619" s="14">
-        <v>7.061041417E9</v>
+        <v>8.06298339E9</v>
       </c>
       <c r="E619" s="14">
         <v>234.0</v>
@@ -17223,7 +17252,7 @@
     </row>
     <row r="620">
       <c r="A620" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B620" s="13">
         <v>1.0</v>
@@ -17246,16 +17275,16 @@
     </row>
     <row r="621">
       <c r="A621" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B621" s="13">
         <v>1.0</v>
       </c>
       <c r="C621" s="14" t="s">
-        <v>375</v>
+        <v>641</v>
       </c>
       <c r="D621" s="14">
-        <v>8.062316717E9</v>
+        <v>7.061041417E9</v>
       </c>
       <c r="E621" s="14">
         <v>234.0</v>
@@ -17268,17 +17297,17 @@
       <c r="K621" s="5"/>
     </row>
     <row r="622">
-      <c r="A622" s="29" t="s">
-        <v>652</v>
+      <c r="A622" s="12" t="s">
+        <v>651</v>
       </c>
       <c r="B622" s="13">
         <v>1.0</v>
       </c>
       <c r="C622" s="14" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D622" s="14">
-        <v>8.023270405E9</v>
+        <v>8.062316717E9</v>
       </c>
       <c r="E622" s="14">
         <v>234.0</v>
@@ -17291,11 +17320,21 @@
       <c r="K622" s="5"/>
     </row>
     <row r="623">
-      <c r="A623" s="29"/>
-      <c r="B623" s="13"/>
-      <c r="C623" s="14"/>
-      <c r="D623" s="14"/>
-      <c r="E623" s="14"/>
+      <c r="A623" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="B623" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C623" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D623" s="14">
+        <v>8.023270405E9</v>
+      </c>
+      <c r="E623" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F623" s="5"/>
       <c r="G623" s="5"/>
       <c r="H623" s="5"/>
@@ -17304,61 +17343,51 @@
       <c r="K623" s="5"/>
     </row>
     <row r="624">
-      <c r="A624" s="47" t="s">
+      <c r="A624" s="29"/>
+      <c r="B624" s="13"/>
+      <c r="C624" s="14"/>
+      <c r="D624" s="14"/>
+      <c r="E624" s="14"/>
+      <c r="F624" s="5"/>
+      <c r="G624" s="5"/>
+      <c r="H624" s="5"/>
+      <c r="I624" s="5"/>
+      <c r="J624" s="5"/>
+      <c r="K624" s="5"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="B624" s="48"/>
-      <c r="C624" s="48"/>
-      <c r="D624" s="48"/>
-      <c r="E624" s="48"/>
-      <c r="F624" s="27"/>
-      <c r="G624" s="27"/>
-      <c r="H624" s="27"/>
-      <c r="I624" s="27"/>
-      <c r="J624" s="27"/>
-      <c r="K624" s="27"/>
-      <c r="L624" s="27"/>
-      <c r="M624" s="27"/>
-      <c r="N624" s="27"/>
-      <c r="O624" s="27"/>
-      <c r="P624" s="27"/>
-      <c r="Q624" s="27"/>
-      <c r="R624" s="27"/>
-      <c r="S624" s="27"/>
-      <c r="T624" s="27"/>
-      <c r="U624" s="27"/>
-      <c r="V624" s="27"/>
-      <c r="W624" s="27"/>
-      <c r="X624" s="27"/>
-      <c r="Y624" s="27"/>
-      <c r="Z624" s="27"/>
-    </row>
-    <row r="625">
-      <c r="A625" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="B625" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C625" s="13" t="s">
-        <v>655</v>
-      </c>
-      <c r="D625" s="14">
-        <v>8.038500818E9</v>
-      </c>
-      <c r="E625" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F625" s="5"/>
-      <c r="G625" s="5"/>
-      <c r="H625" s="5"/>
-      <c r="I625" s="5"/>
-      <c r="J625" s="5"/>
-      <c r="K625" s="5"/>
+      <c r="B625" s="48"/>
+      <c r="C625" s="48"/>
+      <c r="D625" s="48"/>
+      <c r="E625" s="48"/>
+      <c r="F625" s="27"/>
+      <c r="G625" s="27"/>
+      <c r="H625" s="27"/>
+      <c r="I625" s="27"/>
+      <c r="J625" s="27"/>
+      <c r="K625" s="27"/>
+      <c r="L625" s="27"/>
+      <c r="M625" s="27"/>
+      <c r="N625" s="27"/>
+      <c r="O625" s="27"/>
+      <c r="P625" s="27"/>
+      <c r="Q625" s="27"/>
+      <c r="R625" s="27"/>
+      <c r="S625" s="27"/>
+      <c r="T625" s="27"/>
+      <c r="U625" s="27"/>
+      <c r="V625" s="27"/>
+      <c r="W625" s="27"/>
+      <c r="X625" s="27"/>
+      <c r="Y625" s="27"/>
+      <c r="Z625" s="27"/>
     </row>
     <row r="626">
       <c r="A626" s="29" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B626" s="13">
         <v>1.0</v>
@@ -17367,7 +17396,7 @@
         <v>655</v>
       </c>
       <c r="D626" s="14">
-        <v>7.030260852E9</v>
+        <v>8.038500818E9</v>
       </c>
       <c r="E626" s="14">
         <v>234.0</v>
@@ -17380,17 +17409,17 @@
       <c r="K626" s="5"/>
     </row>
     <row r="627">
-      <c r="A627" s="12" t="s">
-        <v>657</v>
+      <c r="A627" s="29" t="s">
+        <v>656</v>
       </c>
       <c r="B627" s="13">
         <v>1.0</v>
       </c>
-      <c r="C627" s="14" t="s">
+      <c r="C627" s="13" t="s">
         <v>655</v>
       </c>
       <c r="D627" s="14">
-        <v>7.055444156E9</v>
+        <v>7.030260852E9</v>
       </c>
       <c r="E627" s="14">
         <v>234.0</v>
@@ -17404,7 +17433,7 @@
     </row>
     <row r="628">
       <c r="A628" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B628" s="13">
         <v>1.0</v>
@@ -17413,7 +17442,7 @@
         <v>655</v>
       </c>
       <c r="D628" s="14">
-        <v>8.032022492E9</v>
+        <v>7.055444156E9</v>
       </c>
       <c r="E628" s="14">
         <v>234.0</v>
@@ -17427,7 +17456,7 @@
     </row>
     <row r="629">
       <c r="A629" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B629" s="13">
         <v>1.0</v>
@@ -17436,7 +17465,7 @@
         <v>655</v>
       </c>
       <c r="D629" s="14">
-        <v>8.023105729E9</v>
+        <v>8.032022492E9</v>
       </c>
       <c r="E629" s="14">
         <v>234.0</v>
@@ -17450,7 +17479,7 @@
     </row>
     <row r="630">
       <c r="A630" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B630" s="13">
         <v>1.0</v>
@@ -17459,7 +17488,7 @@
         <v>655</v>
       </c>
       <c r="D630" s="14">
-        <v>9.134050297E9</v>
+        <v>8.023105729E9</v>
       </c>
       <c r="E630" s="14">
         <v>234.0</v>
@@ -17470,74 +17499,74 @@
       <c r="I630" s="5"/>
       <c r="J630" s="5"/>
       <c r="K630" s="5"/>
-      <c r="L630" s="27"/>
-      <c r="M630" s="27"/>
-      <c r="N630" s="27"/>
-      <c r="O630" s="27"/>
-      <c r="P630" s="27"/>
-      <c r="Q630" s="27"/>
-      <c r="R630" s="27"/>
-      <c r="S630" s="27"/>
-      <c r="T630" s="27"/>
-      <c r="U630" s="27"/>
-      <c r="V630" s="27"/>
-      <c r="W630" s="27"/>
-      <c r="X630" s="27"/>
-      <c r="Y630" s="27"/>
-      <c r="Z630" s="27"/>
     </row>
     <row r="631">
-      <c r="A631" s="9" t="s">
+      <c r="A631" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B631" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C631" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="D631" s="14">
+        <v>9.134050297E9</v>
+      </c>
+      <c r="E631" s="14">
+        <v>234.0</v>
+      </c>
+      <c r="F631" s="5"/>
+      <c r="G631" s="5"/>
+      <c r="H631" s="5"/>
+      <c r="I631" s="5"/>
+      <c r="J631" s="5"/>
+      <c r="K631" s="5"/>
+      <c r="L631" s="27"/>
+      <c r="M631" s="27"/>
+      <c r="N631" s="27"/>
+      <c r="O631" s="27"/>
+      <c r="P631" s="27"/>
+      <c r="Q631" s="27"/>
+      <c r="R631" s="27"/>
+      <c r="S631" s="27"/>
+      <c r="T631" s="27"/>
+      <c r="U631" s="27"/>
+      <c r="V631" s="27"/>
+      <c r="W631" s="27"/>
+      <c r="X631" s="27"/>
+      <c r="Y631" s="27"/>
+      <c r="Z631" s="27"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="B631" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C631" s="10" t="s">
+      <c r="B632" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C632" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="D631" s="10">
+      <c r="D632" s="10">
         <v>9.090140109E9</v>
       </c>
-      <c r="E631" s="10">
-        <v>234.0</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" s="29" t="s">
-        <v>662</v>
-      </c>
-      <c r="B632" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C632" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="D632" s="13">
-        <v>8.035126889E9</v>
-      </c>
-      <c r="E632" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F632" s="5"/>
-      <c r="G632" s="5"/>
-      <c r="H632" s="5"/>
-      <c r="I632" s="5"/>
-      <c r="J632" s="5"/>
-      <c r="K632" s="5"/>
+      <c r="E632" s="10">
+        <v>234.0</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="29" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B633" s="13">
         <v>1.0</v>
       </c>
       <c r="C633" s="14" t="s">
-        <v>664</v>
-      </c>
-      <c r="D633" s="14">
-        <v>8.035023802E9</v>
+        <v>388</v>
+      </c>
+      <c r="D633" s="13">
+        <v>8.035126889E9</v>
       </c>
       <c r="E633" s="14">
         <v>234.0</v>
@@ -17550,17 +17579,17 @@
       <c r="K633" s="5"/>
     </row>
     <row r="634">
-      <c r="A634" s="12" t="s">
-        <v>665</v>
+      <c r="A634" s="29" t="s">
+        <v>663</v>
       </c>
       <c r="B634" s="13">
         <v>1.0</v>
       </c>
       <c r="C634" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D634" s="13">
-        <v>8.056835983E9</v>
+        <v>664</v>
+      </c>
+      <c r="D634" s="14">
+        <v>8.035023802E9</v>
       </c>
       <c r="E634" s="14">
         <v>234.0</v>
@@ -17573,11 +17602,21 @@
       <c r="K634" s="5"/>
     </row>
     <row r="635">
-      <c r="A635" s="29"/>
-      <c r="B635" s="13"/>
-      <c r="C635" s="13"/>
-      <c r="D635" s="13"/>
-      <c r="E635" s="13"/>
+      <c r="A635" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="B635" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C635" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D635" s="13">
+        <v>8.056835983E9</v>
+      </c>
+      <c r="E635" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F635" s="5"/>
       <c r="G635" s="5"/>
       <c r="H635" s="5"/>
@@ -17586,13 +17625,11 @@
       <c r="K635" s="5"/>
     </row>
     <row r="636">
-      <c r="A636" s="24" t="s">
-        <v>666</v>
-      </c>
-      <c r="B636" s="25"/>
-      <c r="C636" s="26"/>
-      <c r="D636" s="26"/>
-      <c r="E636" s="28"/>
+      <c r="A636" s="29"/>
+      <c r="B636" s="13"/>
+      <c r="C636" s="13"/>
+      <c r="D636" s="13"/>
+      <c r="E636" s="13"/>
       <c r="F636" s="5"/>
       <c r="G636" s="5"/>
       <c r="H636" s="5"/>
@@ -17601,21 +17638,13 @@
       <c r="K636" s="5"/>
     </row>
     <row r="637">
-      <c r="A637" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="B637" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C637" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D637" s="14">
-        <v>9.081192203E9</v>
-      </c>
-      <c r="E637" s="14">
-        <v>234.0</v>
-      </c>
+      <c r="A637" s="24" t="s">
+        <v>666</v>
+      </c>
+      <c r="B637" s="25"/>
+      <c r="C637" s="26"/>
+      <c r="D637" s="26"/>
+      <c r="E637" s="28"/>
       <c r="F637" s="5"/>
       <c r="G637" s="5"/>
       <c r="H637" s="5"/>
@@ -17625,7 +17654,7 @@
     </row>
     <row r="638">
       <c r="A638" s="12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B638" s="13">
         <v>1.0</v>
@@ -17634,7 +17663,7 @@
         <v>375</v>
       </c>
       <c r="D638" s="14">
-        <v>9.15430212E9</v>
+        <v>9.081192203E9</v>
       </c>
       <c r="E638" s="14">
         <v>234.0</v>
@@ -17648,7 +17677,7 @@
     </row>
     <row r="639">
       <c r="A639" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B639" s="13">
         <v>1.0</v>
@@ -17671,7 +17700,7 @@
     </row>
     <row r="640">
       <c r="A640" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B640" s="13">
         <v>1.0</v>
@@ -17680,7 +17709,7 @@
         <v>375</v>
       </c>
       <c r="D640" s="14">
-        <v>8.023224437E9</v>
+        <v>9.15430212E9</v>
       </c>
       <c r="E640" s="14">
         <v>234.0</v>
@@ -17694,7 +17723,7 @@
     </row>
     <row r="641">
       <c r="A641" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B641" s="13">
         <v>1.0</v>
@@ -17717,7 +17746,7 @@
     </row>
     <row r="642">
       <c r="A642" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B642" s="13">
         <v>1.0</v>
@@ -17726,7 +17755,7 @@
         <v>375</v>
       </c>
       <c r="D642" s="14">
-        <v>8.056838983E9</v>
+        <v>8.023224437E9</v>
       </c>
       <c r="E642" s="14">
         <v>234.0</v>
@@ -17740,7 +17769,7 @@
     </row>
     <row r="643">
       <c r="A643" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B643" s="13">
         <v>1.0</v>
@@ -17749,7 +17778,7 @@
         <v>375</v>
       </c>
       <c r="D643" s="14">
-        <v>8.030434094E9</v>
+        <v>8.056838983E9</v>
       </c>
       <c r="E643" s="14">
         <v>234.0</v>
@@ -17763,7 +17792,7 @@
     </row>
     <row r="644">
       <c r="A644" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B644" s="13">
         <v>1.0</v>
@@ -17786,7 +17815,7 @@
     </row>
     <row r="645">
       <c r="A645" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B645" s="13">
         <v>1.0</v>
@@ -17795,7 +17824,7 @@
         <v>375</v>
       </c>
       <c r="D645" s="14">
-        <v>8.023163719E9</v>
+        <v>8.030434094E9</v>
       </c>
       <c r="E645" s="14">
         <v>234.0</v>
@@ -17809,7 +17838,7 @@
     </row>
     <row r="646">
       <c r="A646" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B646" s="13">
         <v>1.0</v>
@@ -17831,11 +17860,21 @@
       <c r="K646" s="5"/>
     </row>
     <row r="647">
-      <c r="A647" s="29"/>
-      <c r="B647" s="13"/>
-      <c r="C647" s="13"/>
-      <c r="D647" s="13"/>
-      <c r="E647" s="13"/>
+      <c r="A647" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B647" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C647" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D647" s="14">
+        <v>8.023163719E9</v>
+      </c>
+      <c r="E647" s="14">
+        <v>234.0</v>
+      </c>
       <c r="F647" s="5"/>
       <c r="G647" s="5"/>
       <c r="H647" s="5"/>
@@ -17844,90 +17883,80 @@
       <c r="K647" s="5"/>
     </row>
     <row r="648">
-      <c r="A648" s="47" t="s">
+      <c r="A648" s="29"/>
+      <c r="B648" s="13"/>
+      <c r="C648" s="13"/>
+      <c r="D648" s="13"/>
+      <c r="E648" s="13"/>
+      <c r="F648" s="5"/>
+      <c r="G648" s="5"/>
+      <c r="H648" s="5"/>
+      <c r="I648" s="5"/>
+      <c r="J648" s="5"/>
+      <c r="K648" s="5"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="47" t="s">
         <v>677</v>
       </c>
-      <c r="B648" s="48"/>
-      <c r="C648" s="48"/>
-      <c r="D648" s="48"/>
-      <c r="E648" s="48"/>
-      <c r="F648" s="27"/>
-      <c r="G648" s="27"/>
-      <c r="H648" s="27"/>
-      <c r="I648" s="27"/>
-      <c r="J648" s="27"/>
-      <c r="K648" s="27"/>
-      <c r="L648" s="27"/>
-      <c r="M648" s="27"/>
-      <c r="N648" s="27"/>
-      <c r="O648" s="27"/>
-      <c r="P648" s="27"/>
-      <c r="Q648" s="27"/>
-      <c r="R648" s="27"/>
-      <c r="S648" s="27"/>
-      <c r="T648" s="27"/>
-      <c r="U648" s="27"/>
-      <c r="V648" s="27"/>
-      <c r="W648" s="27"/>
-      <c r="X648" s="27"/>
-      <c r="Y648" s="27"/>
-      <c r="Z648" s="27"/>
-    </row>
-    <row r="649">
-      <c r="A649" s="9" t="s">
+      <c r="B649" s="48"/>
+      <c r="C649" s="48"/>
+      <c r="D649" s="48"/>
+      <c r="E649" s="48"/>
+      <c r="F649" s="27"/>
+      <c r="G649" s="27"/>
+      <c r="H649" s="27"/>
+      <c r="I649" s="27"/>
+      <c r="J649" s="27"/>
+      <c r="K649" s="27"/>
+      <c r="L649" s="27"/>
+      <c r="M649" s="27"/>
+      <c r="N649" s="27"/>
+      <c r="O649" s="27"/>
+      <c r="P649" s="27"/>
+      <c r="Q649" s="27"/>
+      <c r="R649" s="27"/>
+      <c r="S649" s="27"/>
+      <c r="T649" s="27"/>
+      <c r="U649" s="27"/>
+      <c r="V649" s="27"/>
+      <c r="W649" s="27"/>
+      <c r="X649" s="27"/>
+      <c r="Y649" s="27"/>
+      <c r="Z649" s="27"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="B649" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C649" s="10" t="s">
+      <c r="B650" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C650" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="D649" s="10">
+      <c r="D650" s="10">
         <v>8.033484174E9</v>
       </c>
-      <c r="E649" s="10">
-        <v>234.0</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" s="12" t="s">
-        <v>679</v>
-      </c>
-      <c r="B650" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C650" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="D650" s="14">
-        <v>8.06298339E9</v>
-      </c>
-      <c r="E650" s="14">
-        <v>234.0</v>
-      </c>
-      <c r="F650" s="5"/>
-      <c r="G650" s="5"/>
-      <c r="H650" s="5"/>
-      <c r="I650" s="5"/>
-      <c r="J650" s="5"/>
-      <c r="K650" s="5"/>
+      <c r="E650" s="10">
+        <v>234.0</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B651" s="13">
         <v>1.0</v>
       </c>
       <c r="C651" s="14" t="s">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="D651" s="14">
-        <v>7.904077907E9</v>
+        <v>8.06298339E9</v>
       </c>
       <c r="E651" s="14">
-        <v>44.0</v>
+        <v>234.0</v>
       </c>
       <c r="F651" s="5"/>
       <c r="G651" s="5"/>
@@ -17937,45 +17966,55 @@
       <c r="K651" s="5"/>
     </row>
     <row r="652">
-      <c r="A652" s="24"/>
-      <c r="B652" s="25"/>
-      <c r="C652" s="26"/>
-      <c r="D652" s="26"/>
-      <c r="E652" s="28"/>
+      <c r="A652" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="B652" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C652" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D652" s="14">
+        <v>7.904077907E9</v>
+      </c>
+      <c r="E652" s="14">
+        <v>44.0</v>
+      </c>
       <c r="F652" s="5"/>
       <c r="G652" s="5"/>
       <c r="H652" s="5"/>
       <c r="I652" s="5"/>
       <c r="J652" s="5"/>
       <c r="K652" s="5"/>
-      <c r="L652" s="27"/>
-      <c r="M652" s="27"/>
-      <c r="N652" s="27"/>
-      <c r="O652" s="27"/>
-      <c r="P652" s="27"/>
-      <c r="Q652" s="27"/>
-      <c r="R652" s="27"/>
-      <c r="S652" s="27"/>
-      <c r="T652" s="27"/>
-      <c r="U652" s="27"/>
-      <c r="V652" s="27"/>
-      <c r="W652" s="27"/>
-      <c r="X652" s="27"/>
-      <c r="Y652" s="27"/>
-      <c r="Z652" s="27"/>
     </row>
     <row r="653">
-      <c r="A653" s="12"/>
-      <c r="B653" s="13"/>
-      <c r="C653" s="14"/>
-      <c r="D653" s="14"/>
-      <c r="E653" s="35"/>
+      <c r="A653" s="24"/>
+      <c r="B653" s="25"/>
+      <c r="C653" s="26"/>
+      <c r="D653" s="26"/>
+      <c r="E653" s="28"/>
       <c r="F653" s="5"/>
       <c r="G653" s="5"/>
       <c r="H653" s="5"/>
       <c r="I653" s="5"/>
       <c r="J653" s="5"/>
       <c r="K653" s="5"/>
+      <c r="L653" s="27"/>
+      <c r="M653" s="27"/>
+      <c r="N653" s="27"/>
+      <c r="O653" s="27"/>
+      <c r="P653" s="27"/>
+      <c r="Q653" s="27"/>
+      <c r="R653" s="27"/>
+      <c r="S653" s="27"/>
+      <c r="T653" s="27"/>
+      <c r="U653" s="27"/>
+      <c r="V653" s="27"/>
+      <c r="W653" s="27"/>
+      <c r="X653" s="27"/>
+      <c r="Y653" s="27"/>
+      <c r="Z653" s="27"/>
     </row>
     <row r="654">
       <c r="A654" s="12"/>
@@ -17995,7 +18034,7 @@
       <c r="B655" s="13"/>
       <c r="C655" s="14"/>
       <c r="D655" s="14"/>
-      <c r="E655" s="14"/>
+      <c r="E655" s="35"/>
       <c r="F655" s="5"/>
       <c r="G655" s="5"/>
       <c r="H655" s="5"/>
@@ -18008,7 +18047,7 @@
       <c r="B656" s="13"/>
       <c r="C656" s="14"/>
       <c r="D656" s="14"/>
-      <c r="E656" s="35"/>
+      <c r="E656" s="14"/>
       <c r="F656" s="5"/>
       <c r="G656" s="5"/>
       <c r="H656" s="5"/>
@@ -18030,16 +18069,11 @@
       <c r="K657" s="5"/>
     </row>
     <row r="658">
-      <c r="A658" s="12" t="s">
-        <v>681</v>
-      </c>
-      <c r="B658" s="13">
-        <f>SUM(B3:B657)</f>
-        <v>543</v>
-      </c>
+      <c r="A658" s="12"/>
+      <c r="B658" s="13"/>
       <c r="C658" s="14"/>
       <c r="D658" s="14"/>
-      <c r="E658" s="14"/>
+      <c r="E658" s="35"/>
       <c r="F658" s="5"/>
       <c r="G658" s="5"/>
       <c r="H658" s="5"/>
@@ -18048,8 +18082,13 @@
       <c r="K658" s="5"/>
     </row>
     <row r="659">
-      <c r="A659" s="29"/>
-      <c r="B659" s="13"/>
+      <c r="A659" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="B659" s="13">
+        <f>SUM(B3:B658)</f>
+        <v>543</v>
+      </c>
       <c r="C659" s="14"/>
       <c r="D659" s="14"/>
       <c r="E659" s="14"/>
@@ -18061,11 +18100,11 @@
       <c r="K659" s="5"/>
     </row>
     <row r="660">
-      <c r="A660" s="12"/>
+      <c r="A660" s="29"/>
       <c r="B660" s="13"/>
       <c r="C660" s="14"/>
       <c r="D660" s="14"/>
-      <c r="E660" s="35"/>
+      <c r="E660" s="14"/>
       <c r="F660" s="5"/>
       <c r="G660" s="5"/>
       <c r="H660" s="5"/>
@@ -18074,45 +18113,45 @@
       <c r="K660" s="5"/>
     </row>
     <row r="661">
-      <c r="A661" s="24"/>
-      <c r="B661" s="53"/>
-      <c r="C661" s="28"/>
-      <c r="D661" s="28"/>
-      <c r="E661" s="28"/>
+      <c r="A661" s="12"/>
+      <c r="B661" s="13"/>
+      <c r="C661" s="14"/>
+      <c r="D661" s="14"/>
+      <c r="E661" s="35"/>
       <c r="F661" s="5"/>
       <c r="G661" s="5"/>
       <c r="H661" s="5"/>
       <c r="I661" s="5"/>
       <c r="J661" s="5"/>
       <c r="K661" s="5"/>
-      <c r="L661" s="27"/>
-      <c r="M661" s="27"/>
-      <c r="N661" s="27"/>
-      <c r="O661" s="27"/>
-      <c r="P661" s="27"/>
-      <c r="Q661" s="27"/>
-      <c r="R661" s="27"/>
-      <c r="S661" s="27"/>
-      <c r="T661" s="27"/>
-      <c r="U661" s="27"/>
-      <c r="V661" s="27"/>
-      <c r="W661" s="27"/>
-      <c r="X661" s="27"/>
-      <c r="Y661" s="27"/>
-      <c r="Z661" s="27"/>
     </row>
     <row r="662">
-      <c r="A662" s="12"/>
-      <c r="B662" s="13"/>
-      <c r="C662" s="14"/>
-      <c r="D662" s="14"/>
-      <c r="E662" s="14"/>
+      <c r="A662" s="24"/>
+      <c r="B662" s="53"/>
+      <c r="C662" s="28"/>
+      <c r="D662" s="28"/>
+      <c r="E662" s="28"/>
       <c r="F662" s="5"/>
       <c r="G662" s="5"/>
       <c r="H662" s="5"/>
       <c r="I662" s="5"/>
       <c r="J662" s="5"/>
       <c r="K662" s="5"/>
+      <c r="L662" s="27"/>
+      <c r="M662" s="27"/>
+      <c r="N662" s="27"/>
+      <c r="O662" s="27"/>
+      <c r="P662" s="27"/>
+      <c r="Q662" s="27"/>
+      <c r="R662" s="27"/>
+      <c r="S662" s="27"/>
+      <c r="T662" s="27"/>
+      <c r="U662" s="27"/>
+      <c r="V662" s="27"/>
+      <c r="W662" s="27"/>
+      <c r="X662" s="27"/>
+      <c r="Y662" s="27"/>
+      <c r="Z662" s="27"/>
     </row>
     <row r="663">
       <c r="A663" s="12"/>
@@ -18128,7 +18167,11 @@
       <c r="K663" s="5"/>
     </row>
     <row r="664">
-      <c r="E664" s="11"/>
+      <c r="A664" s="12"/>
+      <c r="B664" s="13"/>
+      <c r="C664" s="14"/>
+      <c r="D664" s="14"/>
+      <c r="E664" s="14"/>
       <c r="F664" s="5"/>
       <c r="G664" s="5"/>
       <c r="H664" s="5"/>
@@ -18227,9 +18270,6 @@
       <c r="K674" s="5"/>
     </row>
     <row r="675">
-      <c r="B675" s="11"/>
-      <c r="C675" s="11"/>
-      <c r="D675" s="11"/>
       <c r="E675" s="11"/>
       <c r="F675" s="5"/>
       <c r="G675" s="5"/>
@@ -18287,11 +18327,10 @@
       <c r="K679" s="5"/>
     </row>
     <row r="680">
-      <c r="A680" s="23"/>
-      <c r="B680" s="13"/>
-      <c r="C680" s="14"/>
-      <c r="D680" s="13"/>
-      <c r="E680" s="14"/>
+      <c r="B680" s="11"/>
+      <c r="C680" s="11"/>
+      <c r="D680" s="11"/>
+      <c r="E680" s="11"/>
       <c r="F680" s="5"/>
       <c r="G680" s="5"/>
       <c r="H680" s="5"/>
@@ -18300,10 +18339,11 @@
       <c r="K680" s="5"/>
     </row>
     <row r="681">
-      <c r="B681" s="11"/>
-      <c r="C681" s="11"/>
-      <c r="D681" s="11"/>
-      <c r="E681" s="11"/>
+      <c r="A681" s="23"/>
+      <c r="B681" s="13"/>
+      <c r="C681" s="14"/>
+      <c r="D681" s="13"/>
+      <c r="E681" s="14"/>
       <c r="F681" s="5"/>
       <c r="G681" s="5"/>
       <c r="H681" s="5"/>
@@ -18348,44 +18388,44 @@
       <c r="K684" s="5"/>
     </row>
     <row r="685">
-      <c r="A685" s="57"/>
-      <c r="B685" s="58"/>
-      <c r="C685" s="59"/>
-      <c r="D685" s="59"/>
-      <c r="E685" s="59"/>
-      <c r="F685" s="60"/>
-      <c r="G685" s="60"/>
-      <c r="H685" s="60"/>
-      <c r="I685" s="60"/>
-      <c r="J685" s="60"/>
-      <c r="K685" s="60"/>
-      <c r="L685" s="60"/>
-      <c r="M685" s="60"/>
-      <c r="N685" s="60"/>
-      <c r="O685" s="60"/>
-      <c r="P685" s="60"/>
-      <c r="Q685" s="60"/>
-      <c r="R685" s="60"/>
-      <c r="S685" s="60"/>
-      <c r="T685" s="60"/>
-      <c r="U685" s="60"/>
-      <c r="V685" s="60"/>
-      <c r="W685" s="60"/>
-      <c r="X685" s="60"/>
-      <c r="Y685" s="60"/>
-      <c r="Z685" s="60"/>
+      <c r="B685" s="11"/>
+      <c r="C685" s="11"/>
+      <c r="D685" s="11"/>
+      <c r="E685" s="11"/>
+      <c r="F685" s="5"/>
+      <c r="G685" s="5"/>
+      <c r="H685" s="5"/>
+      <c r="I685" s="5"/>
+      <c r="J685" s="5"/>
+      <c r="K685" s="5"/>
     </row>
     <row r="686">
-      <c r="B686" s="11"/>
-      <c r="C686" s="11"/>
-      <c r="D686" s="11"/>
-      <c r="E686" s="11"/>
-      <c r="F686" s="5"/>
-      <c r="G686" s="5"/>
-      <c r="H686" s="5"/>
-      <c r="I686" s="5"/>
-      <c r="J686" s="5"/>
-      <c r="K686" s="5"/>
+      <c r="A686" s="57"/>
+      <c r="B686" s="58"/>
+      <c r="C686" s="59"/>
+      <c r="D686" s="59"/>
+      <c r="E686" s="59"/>
+      <c r="F686" s="60"/>
+      <c r="G686" s="60"/>
+      <c r="H686" s="60"/>
+      <c r="I686" s="60"/>
+      <c r="J686" s="60"/>
+      <c r="K686" s="60"/>
+      <c r="L686" s="60"/>
+      <c r="M686" s="60"/>
+      <c r="N686" s="60"/>
+      <c r="O686" s="60"/>
+      <c r="P686" s="60"/>
+      <c r="Q686" s="60"/>
+      <c r="R686" s="60"/>
+      <c r="S686" s="60"/>
+      <c r="T686" s="60"/>
+      <c r="U686" s="60"/>
+      <c r="V686" s="60"/>
+      <c r="W686" s="60"/>
+      <c r="X686" s="60"/>
+      <c r="Y686" s="60"/>
+      <c r="Z686" s="60"/>
     </row>
     <row r="687">
       <c r="B687" s="11"/>
@@ -22778,6 +22818,18 @@
       <c r="I1052" s="5"/>
       <c r="J1052" s="5"/>
       <c r="K1052" s="5"/>
+    </row>
+    <row r="1053">
+      <c r="B1053" s="11"/>
+      <c r="C1053" s="11"/>
+      <c r="D1053" s="11"/>
+      <c r="E1053" s="11"/>
+      <c r="F1053" s="5"/>
+      <c r="G1053" s="5"/>
+      <c r="H1053" s="5"/>
+      <c r="I1053" s="5"/>
+      <c r="J1053" s="5"/>
+      <c r="K1053" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24484,7 +24536,7 @@
     </row>
     <row r="67">
       <c r="A67" s="12" t="s">
-        <v>233</v>
+        <v>684</v>
       </c>
       <c r="B67" s="13">
         <v>1.0</v>
@@ -24763,7 +24815,7 @@
     </row>
     <row r="80">
       <c r="A80" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B80" s="13">
         <v>1.0</v>
@@ -26285,7 +26337,7 @@
     </row>
     <row r="145">
       <c r="A145" s="12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B145" s="13">
         <v>1.0</v>
@@ -26308,7 +26360,7 @@
     </row>
     <row r="146">
       <c r="A146" s="12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B146" s="13">
         <v>1.0</v>
@@ -26554,7 +26606,7 @@
     </row>
     <row r="157">
       <c r="A157" s="24" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B157" s="25"/>
       <c r="C157" s="26"/>
@@ -26842,7 +26894,7 @@
     </row>
     <row r="169">
       <c r="A169" s="24" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B169" s="25"/>
       <c r="C169" s="26"/>
@@ -27130,7 +27182,7 @@
     </row>
     <row r="181">
       <c r="A181" s="39" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B181" s="25"/>
       <c r="C181" s="25"/>
@@ -27359,7 +27411,7 @@
     </row>
     <row r="190">
       <c r="A190" s="29" t="s">
-        <v>199</v>
+        <v>691</v>
       </c>
       <c r="B190" s="13">
         <v>1.0</v>
@@ -27417,7 +27469,7 @@
     </row>
     <row r="193">
       <c r="A193" s="24" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B193" s="25"/>
       <c r="C193" s="26"/>
@@ -27720,7 +27772,7 @@
     </row>
     <row r="205">
       <c r="A205" s="39" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B205" s="25"/>
       <c r="C205" s="25"/>
@@ -28124,7 +28176,7 @@
     </row>
     <row r="222">
       <c r="A222" s="29" t="s">
-        <v>245</v>
+        <v>694</v>
       </c>
       <c r="B222" s="13">
         <v>1.0</v>
@@ -30034,7 +30086,7 @@
     </row>
     <row r="304">
       <c r="A304" s="12" t="s">
-        <v>330</v>
+        <v>695</v>
       </c>
       <c r="B304" s="13">
         <v>1.0</v>
@@ -30827,7 +30879,7 @@
     </row>
     <row r="338">
       <c r="A338" s="12" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B338" s="13">
         <v>2.0</v>
@@ -30850,7 +30902,7 @@
     </row>
     <row r="339">
       <c r="A339" s="12" t="s">
-        <v>370</v>
+        <v>697</v>
       </c>
       <c r="B339" s="13">
         <v>2.0</v>
@@ -30873,7 +30925,7 @@
     </row>
     <row r="340">
       <c r="A340" s="12" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="B340" s="13">
         <v>2.0</v>
@@ -30911,7 +30963,7 @@
     </row>
     <row r="341">
       <c r="A341" s="12" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="B341" s="13">
         <v>2.0</v>
@@ -31684,7 +31736,7 @@
     </row>
     <row r="375">
       <c r="A375" s="12" t="s">
-        <v>409</v>
+        <v>700</v>
       </c>
       <c r="B375" s="13">
         <v>1.0</v>
@@ -31880,7 +31932,7 @@
     </row>
     <row r="383">
       <c r="A383" s="12" t="s">
-        <v>417</v>
+        <v>701</v>
       </c>
       <c r="B383" s="13">
         <v>1.0</v>
@@ -32843,7 +32895,7 @@
     </row>
     <row r="427">
       <c r="A427" s="24" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B427" s="25"/>
       <c r="C427" s="26"/>
@@ -33664,7 +33716,7 @@
     </row>
     <row r="462">
       <c r="A462" s="39" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B462" s="25"/>
       <c r="C462" s="25"/>
@@ -34388,7 +34440,7 @@
     </row>
     <row r="493">
       <c r="A493" s="12" t="s">
-        <v>529</v>
+        <v>704</v>
       </c>
       <c r="B493" s="13">
         <v>1.0</v>
@@ -34756,7 +34808,7 @@
     </row>
     <row r="511">
       <c r="A511" s="12" t="s">
-        <v>543</v>
+        <v>705</v>
       </c>
       <c r="B511" s="13">
         <v>1.0</v>
@@ -35763,7 +35815,7 @@
     </row>
     <row r="553">
       <c r="A553" s="12" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="B553" s="13">
         <v>1.0</v>
@@ -35916,7 +35968,7 @@
     </row>
     <row r="560">
       <c r="A560" s="12" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="B560" s="13">
         <v>2.0</v>
@@ -35985,7 +36037,7 @@
     </row>
     <row r="563">
       <c r="A563" s="12" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="B563" s="13">
         <v>2.0</v>
@@ -36008,7 +36060,7 @@
     </row>
     <row r="564">
       <c r="A564" s="12" t="s">
-        <v>601</v>
+        <v>709</v>
       </c>
       <c r="B564" s="13">
         <v>2.0</v>
@@ -36059,7 +36111,7 @@
     </row>
     <row r="567">
       <c r="A567" s="12" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="B567" s="13">
         <v>2.0</v>
@@ -36097,7 +36149,7 @@
     </row>
     <row r="568">
       <c r="A568" s="12" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="B568" s="13">
         <v>2.0</v>
@@ -36120,7 +36172,7 @@
     </row>
     <row r="569">
       <c r="A569" s="12" t="s">
-        <v>610</v>
+        <v>712</v>
       </c>
       <c r="B569" s="13">
         <v>2.0</v>
@@ -36143,7 +36195,7 @@
     </row>
     <row r="570">
       <c r="A570" s="12" t="s">
-        <v>612</v>
+        <v>713</v>
       </c>
       <c r="B570" s="13">
         <v>2.0</v>
@@ -36166,7 +36218,7 @@
     </row>
     <row r="571">
       <c r="A571" s="12" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="B571" s="13">
         <v>2.0</v>
@@ -37624,7 +37676,7 @@
     </row>
     <row r="635">
       <c r="A635" s="12" t="s">
-        <v>637</v>
+        <v>715</v>
       </c>
       <c r="B635" s="13">
         <v>1.0</v>
@@ -42549,7 +42601,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="B1" s="13">
         <v>1.0</v>
@@ -42558,7 +42610,7 @@
         <v>375</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="E1" s="35"/>
       <c r="F1" s="5"/>
@@ -42570,7 +42622,7 @@
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="B2" s="13">
         <v>1.0</v>
@@ -42579,7 +42631,7 @@
         <v>648</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="5"/>

--- a/public/data/Mr Tunde Martins AKande @60 Guest List.xlsx
+++ b/public/data/Mr Tunde Martins AKande @60 Guest List.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="719">
   <si>
     <t>Guest List</t>
   </si>
@@ -1128,6 +1128,9 @@
     <t>790825-5352</t>
   </si>
   <si>
+    <t>Mr Suleiman Shittu</t>
+  </si>
+  <si>
     <t>Mr Jide Adeleye</t>
   </si>
   <si>
@@ -2077,9 +2080,6 @@
   </si>
   <si>
     <t>Adekanye Tolulope</t>
-  </si>
-  <si>
-    <t>Mr Suleiman Shittu</t>
   </si>
   <si>
     <t>Total</t>
@@ -10677,20 +10677,20 @@
       <c r="K332" s="5"/>
     </row>
     <row r="333">
-      <c r="A333" s="29" t="s">
-        <v>315</v>
+      <c r="A333" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="B333" s="13">
         <v>1.0</v>
       </c>
-      <c r="C333" s="13" t="s">
-        <v>179</v>
+      <c r="C333" s="14" t="s">
+        <v>290</v>
       </c>
       <c r="D333" s="14">
-        <v>8.171622577E9</v>
+        <v>7.904077907E9</v>
       </c>
       <c r="E333" s="14">
-        <v>234.0</v>
+        <v>44.0</v>
       </c>
       <c r="F333" s="5"/>
       <c r="G333" s="5"/>
@@ -10701,7 +10701,7 @@
     </row>
     <row r="334">
       <c r="A334" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B334" s="13">
         <v>1.0</v>
@@ -10724,7 +10724,7 @@
     </row>
     <row r="335">
       <c r="A335" s="36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B335" s="37">
         <v>1.0</v>
@@ -10760,7 +10760,7 @@
     </row>
     <row r="337">
       <c r="A337" s="24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B337" s="25"/>
       <c r="C337" s="26"/>
@@ -10775,7 +10775,7 @@
     </row>
     <row r="338">
       <c r="A338" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B338" s="13">
         <v>1.0</v>
@@ -10798,7 +10798,7 @@
     </row>
     <row r="339">
       <c r="A339" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B339" s="13">
         <v>1.0</v>
@@ -10821,7 +10821,7 @@
     </row>
     <row r="340">
       <c r="A340" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B340" s="13">
         <v>1.0</v>
@@ -10844,7 +10844,7 @@
     </row>
     <row r="341">
       <c r="A341" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B341" s="13">
         <v>1.0</v>
@@ -10867,7 +10867,7 @@
     </row>
     <row r="342">
       <c r="A342" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B342" s="13">
         <v>1.0</v>
@@ -10890,7 +10890,7 @@
     </row>
     <row r="343">
       <c r="A343" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B343" s="13">
         <v>1.0</v>
@@ -10913,7 +10913,7 @@
     </row>
     <row r="344">
       <c r="A344" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B344" s="13">
         <v>1.0</v>
@@ -10951,7 +10951,7 @@
     </row>
     <row r="345">
       <c r="A345" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B345" s="13">
         <v>1.0</v>
@@ -10989,13 +10989,13 @@
     </row>
     <row r="346">
       <c r="A346" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B346" s="13">
         <v>1.0</v>
       </c>
       <c r="C346" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D346" s="13">
         <v>8.023166383E9</v>
@@ -11012,13 +11012,13 @@
     </row>
     <row r="347">
       <c r="A347" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B347" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C347" s="14" t="s">
         <v>376</v>
-      </c>
-      <c r="B347" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C347" s="14" t="s">
-        <v>375</v>
       </c>
       <c r="D347" s="13">
         <v>8.023166383E9</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="349">
       <c r="A349" s="47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B349" s="48"/>
       <c r="C349" s="48"/>
@@ -11078,13 +11078,13 @@
     </row>
     <row r="350">
       <c r="A350" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B350" s="13">
         <v>1.0</v>
       </c>
       <c r="C350" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D350" s="14">
         <v>7.065512125E9</v>
@@ -11101,13 +11101,13 @@
     </row>
     <row r="351">
       <c r="A351" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B351" s="13">
         <v>1.0</v>
       </c>
       <c r="C351" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D351" s="14">
         <v>9.081192203E9</v>
@@ -11124,13 +11124,13 @@
     </row>
     <row r="352">
       <c r="A352" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B352" s="13">
         <v>1.0</v>
       </c>
       <c r="C352" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D352" s="14">
         <v>8.054091505E9</v>
@@ -11147,13 +11147,13 @@
     </row>
     <row r="353">
       <c r="A353" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B353" s="13">
         <v>1.0</v>
       </c>
       <c r="C353" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D353" s="14">
         <v>7.956311081E9</v>
@@ -11170,13 +11170,13 @@
     </row>
     <row r="354">
       <c r="A354" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B354" s="13">
         <v>1.0</v>
       </c>
       <c r="C354" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D354" s="14">
         <v>8.023070734E9</v>
@@ -11208,13 +11208,13 @@
     </row>
     <row r="355">
       <c r="A355" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B355" s="13">
         <v>1.0</v>
       </c>
       <c r="C355" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D355" s="14">
         <v>8.023309846E9</v>
@@ -11231,13 +11231,13 @@
     </row>
     <row r="356">
       <c r="A356" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B356" s="13">
         <v>1.0</v>
       </c>
       <c r="C356" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D356" s="14">
         <v>8.023309846E9</v>
@@ -11254,13 +11254,13 @@
     </row>
     <row r="357">
       <c r="A357" s="23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B357" s="13">
         <v>1.0</v>
       </c>
       <c r="C357" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D357" s="14">
         <v>8.023405394E9</v>
@@ -11277,13 +11277,13 @@
     </row>
     <row r="358">
       <c r="A358" s="23" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B358" s="13">
         <v>1.0</v>
       </c>
       <c r="C358" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D358" s="14">
         <v>8.023405394E9</v>
@@ -11300,13 +11300,13 @@
     </row>
     <row r="359">
       <c r="A359" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B359" s="13">
         <v>1.0</v>
       </c>
       <c r="C359" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D359" s="14">
         <v>8.075048968E9</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="361">
       <c r="A361" s="24" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B361" s="25"/>
       <c r="C361" s="26"/>
@@ -11351,13 +11351,13 @@
     </row>
     <row r="362">
       <c r="A362" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B362" s="13">
         <v>1.0</v>
       </c>
       <c r="C362" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D362" s="14">
         <v>7.033311706E9</v>
@@ -11374,13 +11374,13 @@
     </row>
     <row r="363">
       <c r="A363" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B363" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C363" s="14" t="s">
         <v>392</v>
-      </c>
-      <c r="B363" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C363" s="14" t="s">
-        <v>391</v>
       </c>
       <c r="D363" s="14">
         <v>7.033311706E9</v>
@@ -11397,13 +11397,13 @@
     </row>
     <row r="364">
       <c r="A364" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B364" s="13">
         <v>1.0</v>
       </c>
       <c r="C364" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D364" s="14">
         <v>8.032196962E9</v>
@@ -11420,13 +11420,13 @@
     </row>
     <row r="365">
       <c r="A365" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B365" s="13">
         <v>1.0</v>
       </c>
       <c r="C365" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D365" s="14">
         <v>8.038269145E9</v>
@@ -11443,13 +11443,13 @@
     </row>
     <row r="366">
       <c r="A366" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B366" s="13">
         <v>1.0</v>
       </c>
       <c r="C366" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D366" s="14">
         <v>8.037632224E9</v>
@@ -11481,13 +11481,13 @@
     </row>
     <row r="367">
       <c r="A367" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B367" s="13">
         <v>1.0</v>
       </c>
       <c r="C367" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D367" s="14">
         <v>8.029108265E9</v>
@@ -11504,13 +11504,13 @@
     </row>
     <row r="368">
       <c r="A368" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B368" s="13">
         <v>1.0</v>
       </c>
       <c r="C368" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D368" s="14">
         <v>9.159868421E9</v>
@@ -11527,13 +11527,13 @@
     </row>
     <row r="369">
       <c r="A369" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B369" s="13">
         <v>1.0</v>
       </c>
       <c r="C369" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D369" s="14">
         <v>9.159868421E9</v>
@@ -11550,13 +11550,13 @@
     </row>
     <row r="370">
       <c r="A370" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B370" s="13">
         <v>1.0</v>
       </c>
       <c r="C370" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D370" s="14">
         <v>7.036281456E9</v>
@@ -11573,13 +11573,13 @@
     </row>
     <row r="371">
       <c r="A371" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B371" s="13">
         <v>1.0</v>
       </c>
       <c r="C371" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D371" s="14">
         <v>7.036281456E9</v>
@@ -11609,7 +11609,7 @@
     </row>
     <row r="373">
       <c r="A373" s="24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B373" s="25"/>
       <c r="C373" s="26"/>
@@ -11624,13 +11624,13 @@
     </row>
     <row r="374">
       <c r="A374" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B374" s="13">
         <v>1.0</v>
       </c>
       <c r="C374" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D374" s="14">
         <v>8.036120862E9</v>
@@ -11647,13 +11647,13 @@
     </row>
     <row r="375">
       <c r="A375" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B375" s="13">
         <v>1.0</v>
       </c>
       <c r="C375" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D375" s="14">
         <v>8.036120862E9</v>
@@ -11670,13 +11670,13 @@
     </row>
     <row r="376">
       <c r="A376" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B376" s="13">
         <v>1.0</v>
       </c>
       <c r="C376" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D376" s="14">
         <v>9.019404989E9</v>
@@ -11693,13 +11693,13 @@
     </row>
     <row r="377">
       <c r="A377" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B377" s="13">
         <v>1.0</v>
       </c>
       <c r="C377" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D377" s="14">
         <v>8.034040437E9</v>
@@ -11716,13 +11716,13 @@
     </row>
     <row r="378">
       <c r="A378" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B378" s="13">
         <v>1.0</v>
       </c>
       <c r="C378" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D378" s="14">
         <v>8.034040437E9</v>
@@ -11739,13 +11739,13 @@
     </row>
     <row r="379">
       <c r="A379" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B379" s="13">
         <v>1.0</v>
       </c>
       <c r="C379" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D379" s="14">
         <v>9.095607784E9</v>
@@ -11762,13 +11762,13 @@
     </row>
     <row r="380">
       <c r="A380" s="12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B380" s="13">
         <v>1.0</v>
       </c>
       <c r="C380" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D380" s="13">
         <v>7.031890883E9</v>
@@ -11785,13 +11785,13 @@
     </row>
     <row r="381">
       <c r="A381" s="12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B381" s="13">
         <v>1.0</v>
       </c>
       <c r="C381" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D381" s="14">
         <v>8.02224805E8</v>
@@ -11823,13 +11823,13 @@
     </row>
     <row r="382">
       <c r="A382" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B382" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C382" s="14" t="s">
         <v>411</v>
-      </c>
-      <c r="B382" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C382" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="D382" s="14">
         <v>8.02224805E8</v>
@@ -11861,13 +11861,13 @@
     </row>
     <row r="383">
       <c r="A383" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B383" s="13">
         <v>1.0</v>
       </c>
       <c r="C383" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D383" s="14">
         <v>8.038190491E9</v>
@@ -11897,7 +11897,7 @@
     </row>
     <row r="385">
       <c r="A385" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B385" s="25"/>
       <c r="C385" s="26"/>
@@ -11912,13 +11912,13 @@
     </row>
     <row r="386">
       <c r="A386" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B386" s="13">
         <v>1.0</v>
       </c>
       <c r="C386" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D386" s="14">
         <v>8.038096396E9</v>
@@ -11935,13 +11935,13 @@
     </row>
     <row r="387">
       <c r="A387" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B387" s="13">
         <v>1.0</v>
       </c>
       <c r="C387" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D387" s="14">
         <v>8.038096396E9</v>
@@ -11958,13 +11958,13 @@
     </row>
     <row r="388">
       <c r="A388" s="12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B388" s="13">
         <v>1.0</v>
       </c>
       <c r="C388" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D388" s="13">
         <v>8.033162339E9</v>
@@ -11981,13 +11981,13 @@
     </row>
     <row r="389">
       <c r="A389" s="12" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B389" s="13">
         <v>1.0</v>
       </c>
       <c r="C389" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D389" s="13">
         <v>8.033162339E9</v>
@@ -12004,13 +12004,13 @@
     </row>
     <row r="390">
       <c r="A390" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B390" s="13">
         <v>1.0</v>
       </c>
       <c r="C390" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D390" s="14">
         <v>8.033162339E9</v>
@@ -12027,13 +12027,13 @@
     </row>
     <row r="391">
       <c r="A391" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B391" s="13">
         <v>1.0</v>
       </c>
       <c r="C391" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D391" s="14">
         <v>8.035023802E9</v>
@@ -12050,13 +12050,13 @@
     </row>
     <row r="392">
       <c r="A392" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B392" s="13">
         <v>1.0</v>
       </c>
       <c r="C392" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D392" s="14">
         <v>7.060844005E9</v>
@@ -12073,13 +12073,13 @@
     </row>
     <row r="393">
       <c r="A393" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B393" s="13">
         <v>1.0</v>
       </c>
       <c r="C393" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D393" s="14">
         <v>7.060844005E9</v>
@@ -12096,13 +12096,13 @@
     </row>
     <row r="394">
       <c r="A394" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B394" s="13">
         <v>1.0</v>
       </c>
       <c r="C394" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D394" s="14">
         <v>8.027733439E9</v>
@@ -12134,13 +12134,13 @@
     </row>
     <row r="395">
       <c r="A395" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B395" s="13">
         <v>1.0</v>
       </c>
       <c r="C395" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D395" s="14">
         <v>8.027733439E9</v>
@@ -12170,7 +12170,7 @@
     </row>
     <row r="397">
       <c r="A397" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B397" s="25"/>
       <c r="C397" s="26"/>
@@ -12185,13 +12185,13 @@
     </row>
     <row r="398">
       <c r="A398" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B398" s="13">
         <v>1.0</v>
       </c>
       <c r="C398" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D398" s="14">
         <v>8.033210754E9</v>
@@ -12206,13 +12206,13 @@
     </row>
     <row r="399">
       <c r="A399" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B399" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C399" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="B399" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C399" s="14" t="s">
-        <v>426</v>
       </c>
       <c r="D399" s="13">
         <v>8.039462242E9</v>
@@ -12227,13 +12227,13 @@
     </row>
     <row r="400">
       <c r="A400" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B400" s="13">
         <v>1.0</v>
       </c>
       <c r="C400" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D400" s="13">
         <v>8.033670457E9</v>
@@ -12248,13 +12248,13 @@
     </row>
     <row r="401">
       <c r="A401" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B401" s="13">
         <v>1.0</v>
       </c>
       <c r="C401" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D401" s="13">
         <v>8.066484528E9</v>
@@ -12269,13 +12269,13 @@
     </row>
     <row r="402">
       <c r="A402" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B402" s="13">
         <v>1.0</v>
       </c>
       <c r="C402" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D402" s="13">
         <v>8.139314127E9</v>
@@ -12290,13 +12290,13 @@
     </row>
     <row r="403">
       <c r="A403" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B403" s="13">
         <v>1.0</v>
       </c>
       <c r="C403" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D403" s="13">
         <v>8.022755703E9</v>
@@ -12311,13 +12311,13 @@
     </row>
     <row r="404">
       <c r="A404" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B404" s="13">
         <v>1.0</v>
       </c>
       <c r="C404" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D404" s="14">
         <v>9.024198439E9</v>
@@ -12347,13 +12347,13 @@
     </row>
     <row r="405">
       <c r="A405" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B405" s="13">
         <v>1.0</v>
       </c>
       <c r="C405" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D405" s="14">
         <v>8.0358886E9</v>
@@ -12368,13 +12368,13 @@
     </row>
     <row r="406">
       <c r="A406" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B406" s="13">
         <v>1.0</v>
       </c>
       <c r="C406" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D406" s="14">
         <v>8.022637076E9</v>
@@ -12389,13 +12389,13 @@
     </row>
     <row r="407">
       <c r="A407" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B407" s="13">
         <v>1.0</v>
       </c>
       <c r="C407" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D407" s="14">
         <v>8.037865897E9</v>
@@ -12421,7 +12421,7 @@
     </row>
     <row r="409">
       <c r="A409" s="24" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B409" s="25"/>
       <c r="C409" s="26"/>
@@ -12436,13 +12436,13 @@
     </row>
     <row r="410">
       <c r="A410" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B410" s="13">
         <v>1.0</v>
       </c>
       <c r="C410" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D410" s="14">
         <v>7.068629985E9</v>
@@ -12457,13 +12457,13 @@
     </row>
     <row r="411">
       <c r="A411" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B411" s="13">
         <v>1.0</v>
       </c>
       <c r="C411" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D411" s="14">
         <v>7.068629985E9</v>
@@ -12478,13 +12478,13 @@
     </row>
     <row r="412">
       <c r="A412" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B412" s="13">
         <v>1.0</v>
       </c>
       <c r="C412" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D412" s="14">
         <v>8.03315128E9</v>
@@ -12499,13 +12499,13 @@
     </row>
     <row r="413">
       <c r="A413" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B413" s="13">
         <v>1.0</v>
       </c>
       <c r="C413" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D413" s="14">
         <v>8.03315128E9</v>
@@ -12520,13 +12520,13 @@
     </row>
     <row r="414">
       <c r="A414" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B414" s="13">
         <v>1.0</v>
       </c>
       <c r="C414" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D414" s="14">
         <v>8.026359933E9</v>
@@ -12541,13 +12541,13 @@
     </row>
     <row r="415">
       <c r="A415" s="12" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B415" s="13">
         <v>1.0</v>
       </c>
       <c r="C415" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D415" s="14">
         <v>8.064681335E9</v>
@@ -12562,13 +12562,13 @@
     </row>
     <row r="416">
       <c r="A416" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B416" s="13">
         <v>1.0</v>
       </c>
       <c r="C416" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D416" s="14">
         <v>8.033321482E9</v>
@@ -12583,13 +12583,13 @@
     </row>
     <row r="417">
       <c r="A417" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B417" s="13">
         <v>1.0</v>
       </c>
       <c r="C417" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D417" s="14">
         <v>8.033321482E9</v>
@@ -12604,13 +12604,13 @@
     </row>
     <row r="418">
       <c r="A418" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B418" s="13">
         <v>1.0</v>
       </c>
       <c r="C418" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D418" s="14">
         <v>8.038171859E9</v>
@@ -12625,13 +12625,13 @@
     </row>
     <row r="419">
       <c r="A419" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B419" s="13">
         <v>1.0</v>
       </c>
       <c r="C419" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D419" s="14">
         <v>9.058642558E9</v>
@@ -12671,7 +12671,7 @@
     </row>
     <row r="421">
       <c r="A421" s="24" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B421" s="25"/>
       <c r="C421" s="26"/>
@@ -12686,13 +12686,13 @@
     </row>
     <row r="422">
       <c r="A422" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B422" s="13">
         <v>1.0</v>
       </c>
       <c r="C422" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D422" s="14">
         <v>8.034841114E9</v>
@@ -12709,13 +12709,13 @@
     </row>
     <row r="423">
       <c r="A423" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B423" s="13">
         <v>1.0</v>
       </c>
       <c r="C423" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D423" s="14">
         <v>8.058524769E9</v>
@@ -12732,13 +12732,13 @@
     </row>
     <row r="424">
       <c r="A424" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B424" s="13">
         <v>1.0</v>
       </c>
       <c r="C424" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D424" s="14">
         <v>9.037960582E9</v>
@@ -12755,13 +12755,13 @@
     </row>
     <row r="425">
       <c r="A425" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B425" s="13">
         <v>1.0</v>
       </c>
       <c r="C425" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D425" s="13">
         <v>8.032002285E9</v>
@@ -12778,13 +12778,13 @@
     </row>
     <row r="426">
       <c r="A426" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B426" s="13">
         <v>1.0</v>
       </c>
       <c r="C426" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D426" s="14">
         <v>8.023032371E9</v>
@@ -12801,13 +12801,13 @@
     </row>
     <row r="427">
       <c r="A427" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B427" s="13">
         <v>1.0</v>
       </c>
       <c r="C427" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D427" s="52">
         <v>8.023136932E9</v>
@@ -12824,13 +12824,13 @@
     </row>
     <row r="428">
       <c r="A428" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B428" s="13">
         <v>1.0</v>
       </c>
       <c r="C428" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D428" s="13">
         <v>8.034360992E9</v>
@@ -12847,13 +12847,13 @@
     </row>
     <row r="429">
       <c r="A429" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B429" s="13">
         <v>1.0</v>
       </c>
       <c r="C429" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D429" s="13">
         <v>8.023358954E9</v>
@@ -12885,13 +12885,13 @@
     </row>
     <row r="430">
       <c r="A430" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B430" s="13">
         <v>1.0</v>
       </c>
       <c r="C430" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D430" s="13">
         <v>8.023056347E9</v>
@@ -12908,13 +12908,13 @@
     </row>
     <row r="431">
       <c r="A431" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B431" s="13">
         <v>1.0</v>
       </c>
       <c r="C431" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D431" s="13">
         <v>6.22041817E8</v>
@@ -12944,7 +12944,7 @@
     </row>
     <row r="433">
       <c r="A433" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B433" s="25"/>
       <c r="C433" s="26"/>
@@ -12959,13 +12959,13 @@
     </row>
     <row r="434">
       <c r="A434" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B434" s="13">
         <v>1.0</v>
       </c>
       <c r="C434" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D434" s="14">
         <v>7.086669911E9</v>
@@ -12982,13 +12982,13 @@
     </row>
     <row r="435">
       <c r="A435" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B435" s="13">
         <v>1.0</v>
       </c>
       <c r="C435" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D435" s="13">
         <v>8.022228967E9</v>
@@ -13005,13 +13005,13 @@
     </row>
     <row r="436">
       <c r="A436" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B436" s="13">
         <v>1.0</v>
       </c>
       <c r="C436" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D436" s="14">
         <v>8.06302025E9</v>
@@ -13028,13 +13028,13 @@
     </row>
     <row r="437">
       <c r="A437" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B437" s="13">
         <v>1.0</v>
       </c>
       <c r="C437" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D437" s="14">
         <v>8.06302025E9</v>
@@ -13051,13 +13051,13 @@
     </row>
     <row r="438">
       <c r="A438" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B438" s="13">
         <v>1.0</v>
       </c>
       <c r="C438" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D438" s="14">
         <v>8.023529768E9</v>
@@ -13074,13 +13074,13 @@
     </row>
     <row r="439">
       <c r="A439" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B439" s="13">
         <v>1.0</v>
       </c>
       <c r="C439" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D439" s="14">
         <v>7.082866677E9</v>
@@ -13097,13 +13097,13 @@
     </row>
     <row r="440">
       <c r="A440" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B440" s="13">
         <v>1.0</v>
       </c>
       <c r="C440" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D440" s="14">
         <v>7.082866677E9</v>
@@ -13120,13 +13120,13 @@
     </row>
     <row r="441">
       <c r="A441" s="12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B441" s="13">
         <v>1.0</v>
       </c>
       <c r="C441" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D441" s="14">
         <v>7.035681401E9</v>
@@ -13143,13 +13143,13 @@
     </row>
     <row r="442">
       <c r="A442" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B442" s="13">
         <v>1.0</v>
       </c>
       <c r="C442" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D442" s="14">
         <v>8.055527946E9</v>
@@ -13181,13 +13181,13 @@
     </row>
     <row r="443">
       <c r="A443" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B443" s="13">
         <v>1.0</v>
       </c>
       <c r="C443" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D443" s="14">
         <v>8.023194301E9</v>
@@ -13217,7 +13217,7 @@
     </row>
     <row r="445">
       <c r="A445" s="39" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B445" s="25"/>
       <c r="C445" s="25"/>
@@ -13232,13 +13232,13 @@
     </row>
     <row r="446">
       <c r="A446" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B446" s="13">
         <v>1.0</v>
       </c>
       <c r="C446" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D446" s="13">
         <v>7.956338229E9</v>
@@ -13255,13 +13255,13 @@
     </row>
     <row r="447">
       <c r="A447" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B447" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C447" s="13" t="s">
         <v>473</v>
-      </c>
-      <c r="B447" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C447" s="13" t="s">
-        <v>472</v>
       </c>
       <c r="D447" s="13">
         <v>7.956338229E9</v>
@@ -13278,13 +13278,13 @@
     </row>
     <row r="448">
       <c r="A448" s="29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B448" s="13">
         <v>1.0</v>
       </c>
       <c r="C448" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D448" s="13">
         <v>7.956132912E9</v>
@@ -13301,13 +13301,13 @@
     </row>
     <row r="449">
       <c r="A449" s="29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B449" s="13">
         <v>1.0</v>
       </c>
       <c r="C449" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D449" s="13">
         <v>7.956132912E9</v>
@@ -13324,13 +13324,13 @@
     </row>
     <row r="450">
       <c r="A450" s="29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B450" s="13">
         <v>1.0</v>
       </c>
       <c r="C450" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D450" s="13">
         <v>7.95613193E9</v>
@@ -13347,13 +13347,13 @@
     </row>
     <row r="451">
       <c r="A451" s="29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B451" s="13">
         <v>1.0</v>
       </c>
       <c r="C451" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D451" s="13">
         <v>7.95613193E9</v>
@@ -13370,13 +13370,13 @@
     </row>
     <row r="452">
       <c r="A452" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B452" s="13">
         <v>1.0</v>
       </c>
       <c r="C452" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D452" s="13">
         <v>7.939988528E9</v>
@@ -13393,13 +13393,13 @@
     </row>
     <row r="453">
       <c r="A453" s="29" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B453" s="13">
         <v>1.0</v>
       </c>
       <c r="C453" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D453" s="13">
         <v>7.939988528E9</v>
@@ -13416,13 +13416,13 @@
     </row>
     <row r="454">
       <c r="A454" s="29" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B454" s="13">
         <v>1.0</v>
       </c>
       <c r="C454" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D454" s="13">
         <v>9.090403655E9</v>
@@ -13439,13 +13439,13 @@
     </row>
     <row r="455">
       <c r="A455" s="29" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B455" s="13">
         <v>1.0</v>
       </c>
       <c r="C455" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D455" s="13">
         <v>9.090403655E9</v>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="456">
       <c r="A456" s="39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B456" s="25"/>
       <c r="C456" s="25"/>
@@ -13477,13 +13477,13 @@
     </row>
     <row r="457">
       <c r="A457" s="29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B457" s="13">
         <v>1.0</v>
       </c>
       <c r="C457" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D457" s="13">
         <v>7.95689006E9</v>
@@ -13515,13 +13515,13 @@
     </row>
     <row r="458">
       <c r="A458" s="29" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B458" s="13">
         <v>1.0</v>
       </c>
       <c r="C458" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D458" s="13">
         <v>7.95689006E9</v>
@@ -13553,13 +13553,13 @@
     </row>
     <row r="459">
       <c r="A459" s="29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B459" s="13">
         <v>1.0</v>
       </c>
       <c r="C459" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D459" s="13">
         <v>7.956132912E9</v>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="460">
       <c r="A460" s="29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B460" s="13">
         <v>1.0</v>
       </c>
       <c r="C460" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D460" s="13">
         <v>9.022163076E9</v>
@@ -13599,13 +13599,13 @@
     </row>
     <row r="461">
       <c r="A461" s="29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B461" s="13">
         <v>1.0</v>
       </c>
       <c r="C461" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D461" s="13">
         <v>7.940255254E9</v>
@@ -13622,13 +13622,13 @@
     </row>
     <row r="462">
       <c r="A462" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B462" s="13">
         <v>1.0</v>
       </c>
       <c r="C462" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D462" s="13">
         <v>7.834352811E9</v>
@@ -13645,13 +13645,13 @@
     </row>
     <row r="463">
       <c r="A463" s="29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B463" s="13">
         <v>1.0</v>
       </c>
       <c r="C463" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D463" s="13">
         <v>7.834352811E9</v>
@@ -13668,13 +13668,13 @@
     </row>
     <row r="464">
       <c r="A464" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B464" s="13">
         <v>1.0</v>
       </c>
       <c r="C464" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D464" s="13">
         <v>7.834352811E9</v>
@@ -13691,13 +13691,13 @@
     </row>
     <row r="465">
       <c r="A465" s="29" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B465" s="13">
         <v>1.0</v>
       </c>
       <c r="C465" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D465" s="13">
         <v>7.753673669E9</v>
@@ -13714,13 +13714,13 @@
     </row>
     <row r="466">
       <c r="A466" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B466" s="13">
         <v>1.0</v>
       </c>
       <c r="C466" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D466" s="14">
         <v>7.961485817E9</v>
@@ -13765,7 +13765,7 @@
     </row>
     <row r="468">
       <c r="A468" s="39" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B468" s="25"/>
       <c r="C468" s="25"/>
@@ -13780,13 +13780,13 @@
     </row>
     <row r="469">
       <c r="A469" s="29" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B469" s="13">
         <v>1.0</v>
       </c>
       <c r="C469" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D469" s="13">
         <v>7.807493779E9</v>
@@ -13803,13 +13803,13 @@
     </row>
     <row r="470">
       <c r="A470" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="B470" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C470" s="13" t="s">
         <v>497</v>
-      </c>
-      <c r="B470" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C470" s="13" t="s">
-        <v>496</v>
       </c>
       <c r="D470" s="13">
         <v>7.807493779E9</v>
@@ -13826,13 +13826,13 @@
     </row>
     <row r="471">
       <c r="A471" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B471" s="13">
         <v>1.0</v>
       </c>
       <c r="C471" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D471" s="13">
         <v>7.424791947E9</v>
@@ -13849,13 +13849,13 @@
     </row>
     <row r="472">
       <c r="A472" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B472" s="13">
         <v>1.0</v>
       </c>
       <c r="C472" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D472" s="13">
         <v>7.807493779E9</v>
@@ -13872,13 +13872,13 @@
     </row>
     <row r="473">
       <c r="A473" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B473" s="13">
         <v>1.0</v>
       </c>
       <c r="C473" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D473" s="13">
         <v>7.424791947E9</v>
@@ -13910,13 +13910,13 @@
     </row>
     <row r="474">
       <c r="A474" s="29" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B474" s="13">
         <v>1.0</v>
       </c>
       <c r="C474" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D474" s="13">
         <v>7.807493779E9</v>
@@ -13933,16 +13933,16 @@
     </row>
     <row r="475">
       <c r="A475" s="29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B475" s="13">
         <v>1.0</v>
       </c>
       <c r="C475" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D475" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E475" s="13">
         <v>1.0</v>
@@ -13956,13 +13956,13 @@
     </row>
     <row r="476">
       <c r="A476" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B476" s="13">
         <v>1.0</v>
       </c>
       <c r="C476" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D476" s="13">
         <v>7.807493779E9</v>
@@ -13979,13 +13979,13 @@
     </row>
     <row r="477">
       <c r="A477" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B477" s="13">
         <v>1.0</v>
       </c>
       <c r="C477" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D477" s="13">
         <v>7.807493779E9</v>
@@ -14002,16 +14002,16 @@
     </row>
     <row r="478">
       <c r="A478" s="29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B478" s="13">
         <v>1.0</v>
       </c>
       <c r="C478" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D478" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E478" s="13">
         <v>1.0</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="480">
       <c r="A480" s="39" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B480" s="25"/>
       <c r="C480" s="25"/>
@@ -14053,16 +14053,16 @@
     </row>
     <row r="481">
       <c r="A481" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B481" s="13">
         <v>1.0</v>
       </c>
       <c r="C481" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D481" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E481" s="13">
         <v>1.0</v>
@@ -14076,16 +14076,16 @@
     </row>
     <row r="482">
       <c r="A482" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B482" s="13">
         <v>1.0</v>
       </c>
       <c r="C482" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D482" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E482" s="13">
         <v>1.0</v>
@@ -14114,16 +14114,16 @@
     </row>
     <row r="483">
       <c r="A483" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B483" s="13">
         <v>1.0</v>
       </c>
       <c r="C483" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D483" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E483" s="13">
         <v>234.0</v>
@@ -14137,16 +14137,16 @@
     </row>
     <row r="484">
       <c r="A484" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B484" s="13">
         <v>1.0</v>
       </c>
       <c r="C484" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D484" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E484" s="13">
         <v>1.0</v>
@@ -14160,16 +14160,16 @@
     </row>
     <row r="485">
       <c r="A485" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B485" s="13">
         <v>1.0</v>
       </c>
       <c r="C485" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D485" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E485" s="13">
         <v>1.0</v>
@@ -14183,13 +14183,13 @@
     </row>
     <row r="486">
       <c r="A486" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B486" s="13">
         <v>1.0</v>
       </c>
       <c r="C486" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D486" s="14">
         <v>7.807493779E9</v>
@@ -14206,13 +14206,13 @@
     </row>
     <row r="487">
       <c r="A487" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B487" s="13">
         <v>1.0</v>
       </c>
       <c r="C487" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D487" s="14">
         <v>7.807493779E9</v>
@@ -14244,13 +14244,13 @@
     </row>
     <row r="488">
       <c r="A488" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B488" s="13">
         <v>1.0</v>
       </c>
       <c r="C488" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D488" s="14">
         <v>7.807493779E9</v>
@@ -14267,13 +14267,13 @@
     </row>
     <row r="489">
       <c r="A489" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B489" s="13">
         <v>1.0</v>
       </c>
       <c r="C489" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D489" s="14">
         <v>7.949394588E9</v>
@@ -14290,13 +14290,13 @@
     </row>
     <row r="490">
       <c r="A490" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B490" s="13">
         <v>1.0</v>
       </c>
       <c r="C490" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D490" s="14">
         <v>7.949394588E9</v>
@@ -14313,7 +14313,7 @@
     </row>
     <row r="491">
       <c r="A491" s="39" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B491" s="25"/>
       <c r="C491" s="25"/>
@@ -14328,13 +14328,13 @@
     </row>
     <row r="492">
       <c r="A492" s="29" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B492" s="13">
         <v>1.0</v>
       </c>
       <c r="C492" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D492" s="13">
         <v>7.055269061E9</v>
@@ -14351,13 +14351,13 @@
     </row>
     <row r="493">
       <c r="A493" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="B493" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C493" s="13" t="s">
         <v>523</v>
-      </c>
-      <c r="B493" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C493" s="13" t="s">
-        <v>522</v>
       </c>
       <c r="D493" s="13">
         <v>7.055269061E9</v>
@@ -14374,13 +14374,13 @@
     </row>
     <row r="494">
       <c r="A494" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B494" s="13">
         <v>1.0</v>
       </c>
       <c r="C494" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D494" s="13">
         <v>7.035375757E9</v>
@@ -14397,13 +14397,13 @@
     </row>
     <row r="495">
       <c r="A495" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B495" s="13">
         <v>1.0</v>
       </c>
       <c r="C495" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D495" s="13">
         <v>8.033459526E9</v>
@@ -14420,13 +14420,13 @@
     </row>
     <row r="496">
       <c r="A496" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B496" s="13">
         <v>1.0</v>
       </c>
       <c r="C496" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D496" s="13">
         <v>7.956447698E9</v>
@@ -14443,13 +14443,13 @@
     </row>
     <row r="497">
       <c r="A497" s="29" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B497" s="13">
         <v>1.0</v>
       </c>
       <c r="C497" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D497" s="13">
         <v>7.956447698E9</v>
@@ -14466,13 +14466,13 @@
     </row>
     <row r="498">
       <c r="A498" s="29" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B498" s="13">
         <v>1.0</v>
       </c>
       <c r="C498" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D498" s="13">
         <v>7.957449008E9</v>
@@ -14489,13 +14489,13 @@
     </row>
     <row r="499">
       <c r="A499" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B499" s="13">
         <v>1.0</v>
       </c>
       <c r="C499" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D499" s="14">
         <v>7.494285001E9</v>
@@ -14512,13 +14512,13 @@
     </row>
     <row r="500">
       <c r="A500" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B500" s="13">
         <v>1.0</v>
       </c>
       <c r="C500" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D500" s="14">
         <v>7.494285001E9</v>
@@ -14535,13 +14535,13 @@
     </row>
     <row r="501">
       <c r="A501" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B501" s="10">
         <v>1.0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D501" s="14">
         <v>7.494285001E9</v>
@@ -14565,7 +14565,7 @@
     </row>
     <row r="503">
       <c r="A503" s="39" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B503" s="53"/>
       <c r="C503" s="53"/>
@@ -14580,13 +14580,13 @@
     </row>
     <row r="504">
       <c r="A504" s="29" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B504" s="13">
         <v>1.0</v>
       </c>
       <c r="C504" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D504" s="13">
         <v>8.03359479E9</v>
@@ -14603,13 +14603,13 @@
     </row>
     <row r="505">
       <c r="A505" s="29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B505" s="13">
         <v>1.0</v>
       </c>
       <c r="C505" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D505" s="13">
         <v>8.033510345E9</v>
@@ -14626,13 +14626,13 @@
     </row>
     <row r="506">
       <c r="A506" s="29" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B506" s="13">
         <v>1.0</v>
       </c>
       <c r="C506" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D506" s="13">
         <v>7.061817517E9</v>
@@ -14649,13 +14649,13 @@
     </row>
     <row r="507">
       <c r="A507" s="29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B507" s="13">
         <v>1.0</v>
       </c>
       <c r="C507" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D507" s="13">
         <v>8.035350809E9</v>
@@ -14672,13 +14672,13 @@
     </row>
     <row r="508">
       <c r="A508" s="29" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B508" s="13">
         <v>1.0</v>
       </c>
       <c r="C508" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D508" s="13">
         <v>8.036156051E9</v>
@@ -14710,13 +14710,13 @@
     </row>
     <row r="509">
       <c r="A509" s="29" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B509" s="13">
         <v>1.0</v>
       </c>
       <c r="C509" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D509" s="13">
         <v>7.060648613E9</v>
@@ -14733,13 +14733,13 @@
     </row>
     <row r="510">
       <c r="A510" s="29" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B510" s="13">
         <v>1.0</v>
       </c>
       <c r="C510" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D510" s="13">
         <v>7.060648613E9</v>
@@ -14756,13 +14756,13 @@
     </row>
     <row r="511">
       <c r="A511" s="29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B511" s="13">
         <v>1.0</v>
       </c>
       <c r="C511" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D511" s="13">
         <v>8.027322242E9</v>
@@ -14779,13 +14779,13 @@
     </row>
     <row r="512">
       <c r="A512" s="29" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B512" s="13">
         <v>1.0</v>
       </c>
       <c r="C512" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D512" s="13">
         <v>2.022468441E9</v>
@@ -14802,13 +14802,13 @@
     </row>
     <row r="513">
       <c r="A513" s="29" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B513" s="13">
         <v>1.0</v>
       </c>
       <c r="C513" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D513" s="13">
         <v>8.184882788E9</v>
@@ -14838,7 +14838,7 @@
     </row>
     <row r="515">
       <c r="A515" s="24" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B515" s="25"/>
       <c r="C515" s="26"/>
@@ -14857,13 +14857,13 @@
     </row>
     <row r="517">
       <c r="A517" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B517" s="13">
         <v>1.0</v>
       </c>
       <c r="C517" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D517" s="14">
         <v>8.033016753E9</v>
@@ -14880,13 +14880,13 @@
     </row>
     <row r="518">
       <c r="A518" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B518" s="13">
         <v>1.0</v>
       </c>
       <c r="C518" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D518" s="14">
         <v>8.033016753E9</v>
@@ -14903,13 +14903,13 @@
     </row>
     <row r="519">
       <c r="A519" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B519" s="13">
         <v>1.0</v>
       </c>
       <c r="C519" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D519" s="14">
         <v>7.398843791E9</v>
@@ -14926,13 +14926,13 @@
     </row>
     <row r="520">
       <c r="A520" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B520" s="13">
         <v>1.0</v>
       </c>
       <c r="C520" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D520" s="14">
         <v>7.949394588E9</v>
@@ -14964,13 +14964,13 @@
     </row>
     <row r="521">
       <c r="A521" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B521" s="10">
         <v>1.0</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D521" s="10">
         <v>7.961023865E9</v>
@@ -14987,13 +14987,13 @@
     </row>
     <row r="522">
       <c r="A522" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B522" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C522" s="10" t="s">
         <v>549</v>
-      </c>
-      <c r="B522" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C522" s="10" t="s">
-        <v>548</v>
       </c>
       <c r="D522" s="10">
         <v>7.961023865E9</v>
@@ -15010,13 +15010,13 @@
     </row>
     <row r="523">
       <c r="A523" s="29" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B523" s="13">
         <v>1.0</v>
       </c>
       <c r="C523" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D523" s="14">
         <v>8.028996353E9</v>
@@ -15033,13 +15033,13 @@
     </row>
     <row r="524">
       <c r="A524" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B524" s="13">
         <v>1.0</v>
       </c>
       <c r="C524" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D524" s="14">
         <v>7.949394588E9</v>
@@ -15056,13 +15056,13 @@
     </row>
     <row r="525">
       <c r="A525" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B525" s="13">
         <v>1.0</v>
       </c>
       <c r="C525" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D525" s="14">
         <v>7.949394588E9</v>
@@ -15094,13 +15094,13 @@
     </row>
     <row r="526">
       <c r="A526" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B526" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C526" s="14" t="s">
         <v>555</v>
-      </c>
-      <c r="B526" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C526" s="14" t="s">
-        <v>554</v>
       </c>
       <c r="D526" s="14">
         <v>7.949394588E9</v>
@@ -15121,7 +15121,7 @@
     </row>
     <row r="528">
       <c r="A528" s="24" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B528" s="53"/>
       <c r="C528" s="28"/>
@@ -15136,13 +15136,13 @@
     </row>
     <row r="529">
       <c r="A529" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B529" s="13">
         <v>1.0</v>
       </c>
       <c r="C529" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D529" s="14">
         <v>7.791874716E9</v>
@@ -15159,13 +15159,13 @@
     </row>
     <row r="530">
       <c r="A530" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B530" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C530" s="14" t="s">
         <v>559</v>
-      </c>
-      <c r="B530" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C530" s="14" t="s">
-        <v>558</v>
       </c>
       <c r="D530" s="14">
         <v>8.056354495E9</v>
@@ -15182,13 +15182,13 @@
     </row>
     <row r="531">
       <c r="A531" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B531" s="13">
         <v>1.0</v>
       </c>
       <c r="C531" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D531" s="14">
         <v>7.411035443E9</v>
@@ -15205,13 +15205,13 @@
     </row>
     <row r="532">
       <c r="A532" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B532" s="13">
         <v>1.0</v>
       </c>
       <c r="C532" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D532" s="14">
         <v>8.165478317E9</v>
@@ -15228,13 +15228,13 @@
     </row>
     <row r="533">
       <c r="A533" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B533" s="13">
         <v>1.0</v>
       </c>
       <c r="C533" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D533" s="14">
         <v>7.910836315E9</v>
@@ -15266,13 +15266,13 @@
     </row>
     <row r="534">
       <c r="A534" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B534" s="13">
         <v>1.0</v>
       </c>
       <c r="C534" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D534" s="14">
         <v>7.398843791E9</v>
@@ -15289,13 +15289,13 @@
     </row>
     <row r="535">
       <c r="A535" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="B535" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C535" s="14" t="s">
         <v>565</v>
-      </c>
-      <c r="B535" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C535" s="14" t="s">
-        <v>564</v>
       </c>
       <c r="D535" s="10">
         <v>7.398843791E9</v>
@@ -15312,13 +15312,13 @@
     </row>
     <row r="536">
       <c r="A536" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B536" s="10">
         <v>1.0</v>
       </c>
       <c r="C536" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D536" s="10">
         <v>7.398843791E9</v>
@@ -15335,13 +15335,13 @@
     </row>
     <row r="537">
       <c r="A537" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B537" s="10">
         <v>1.0</v>
       </c>
       <c r="C537" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D537" s="10">
         <v>7.398843791E9</v>
@@ -15358,13 +15358,13 @@
     </row>
     <row r="538">
       <c r="A538" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B538" s="13">
         <v>1.0</v>
       </c>
       <c r="C538" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D538" s="13">
         <v>8.078753239E9</v>
@@ -15394,7 +15394,7 @@
     </row>
     <row r="540">
       <c r="A540" s="47" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B540" s="48"/>
       <c r="C540" s="48"/>
@@ -15409,13 +15409,13 @@
     </row>
     <row r="541">
       <c r="A541" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B541" s="13">
         <v>1.0</v>
       </c>
       <c r="C541" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D541" s="14">
         <v>8.034044331E9</v>
@@ -15432,13 +15432,13 @@
     </row>
     <row r="542">
       <c r="A542" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B542" s="13">
         <v>1.0</v>
       </c>
       <c r="C542" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D542" s="14">
         <v>8.024662308E9</v>
@@ -15470,13 +15470,13 @@
     </row>
     <row r="543">
       <c r="A543" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B543" s="13">
         <v>1.0</v>
       </c>
       <c r="C543" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D543" s="14">
         <v>8.03372284E9</v>
@@ -15508,13 +15508,13 @@
     </row>
     <row r="544">
       <c r="A544" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B544" s="13">
         <v>1.0</v>
       </c>
       <c r="C544" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D544" s="14">
         <v>8.023136659E9</v>
@@ -15531,13 +15531,13 @@
     </row>
     <row r="545">
       <c r="A545" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B545" s="13">
         <v>1.0</v>
       </c>
       <c r="C545" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D545" s="14">
         <v>8.023414386E9</v>
@@ -15554,13 +15554,13 @@
     </row>
     <row r="546">
       <c r="A546" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B546" s="13">
         <v>1.0</v>
       </c>
       <c r="C546" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D546" s="14">
         <v>8.035715044E9</v>
@@ -15577,13 +15577,13 @@
     </row>
     <row r="547">
       <c r="A547" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B547" s="13">
         <v>1.0</v>
       </c>
       <c r="C547" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D547" s="14">
         <v>8.035715044E9</v>
@@ -15600,13 +15600,13 @@
     </row>
     <row r="548">
       <c r="A548" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B548" s="13">
         <v>1.0</v>
       </c>
       <c r="C548" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D548" s="14">
         <v>7.017822252E9</v>
@@ -15623,13 +15623,13 @@
     </row>
     <row r="549">
       <c r="A549" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B549" s="13">
         <v>1.0</v>
       </c>
       <c r="C549" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D549" s="14">
         <v>8.033151449E9</v>
@@ -15646,13 +15646,13 @@
     </row>
     <row r="550">
       <c r="A550" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B550" s="13">
         <v>1.0</v>
       </c>
       <c r="C550" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D550" s="14">
         <v>8.03407192E9</v>
@@ -15681,7 +15681,7 @@
     </row>
     <row r="552">
       <c r="A552" s="54" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B552" s="25"/>
       <c r="C552" s="26"/>
@@ -15696,13 +15696,13 @@
     </row>
     <row r="553">
       <c r="A553" s="55" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B553" s="56">
         <v>1.0</v>
       </c>
       <c r="C553" s="41" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D553" s="41">
         <v>8.136664029E9</v>
@@ -15734,13 +15734,13 @@
     </row>
     <row r="554">
       <c r="A554" s="55" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B554" s="56">
         <v>1.0</v>
       </c>
       <c r="C554" s="41" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D554" s="41">
         <v>8.136664029E9</v>
@@ -15772,13 +15772,13 @@
     </row>
     <row r="555">
       <c r="A555" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B555" s="13">
         <v>1.0</v>
       </c>
       <c r="C555" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D555" s="14">
         <v>9.097029083E9</v>
@@ -15795,13 +15795,13 @@
     </row>
     <row r="556">
       <c r="A556" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B556" s="13">
         <v>1.0</v>
       </c>
       <c r="C556" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D556" s="14">
         <v>9.097029083E9</v>
@@ -15818,13 +15818,13 @@
     </row>
     <row r="557">
       <c r="A557" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B557" s="13">
         <v>1.0</v>
       </c>
       <c r="C557" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D557" s="14">
         <v>8.023368979E9</v>
@@ -15841,13 +15841,13 @@
     </row>
     <row r="558">
       <c r="A558" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B558" s="13">
         <v>1.0</v>
       </c>
       <c r="C558" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D558" s="14">
         <v>8.023368979E9</v>
@@ -15864,13 +15864,13 @@
     </row>
     <row r="559">
       <c r="A559" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B559" s="13">
         <v>1.0</v>
       </c>
       <c r="C559" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D559" s="14">
         <v>8.033168467E9</v>
@@ -15887,13 +15887,13 @@
     </row>
     <row r="560">
       <c r="A560" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B560" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C560" s="14" t="s">
         <v>589</v>
-      </c>
-      <c r="B560" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C560" s="14" t="s">
-        <v>588</v>
       </c>
       <c r="D560" s="14">
         <v>8.033168467E9</v>
@@ -15910,13 +15910,13 @@
     </row>
     <row r="561">
       <c r="A561" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B561" s="13">
         <v>1.0</v>
       </c>
       <c r="C561" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D561" s="14">
         <v>8.033263138E9</v>
@@ -15933,13 +15933,13 @@
     </row>
     <row r="562">
       <c r="A562" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B562" s="13">
         <v>1.0</v>
       </c>
       <c r="C562" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D562" s="14">
         <v>8.028996353E9</v>
@@ -15969,7 +15969,7 @@
     </row>
     <row r="564">
       <c r="A564" s="24" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B564" s="25"/>
       <c r="C564" s="26"/>
@@ -15984,13 +15984,13 @@
     </row>
     <row r="565">
       <c r="A565" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B565" s="13">
         <v>1.0</v>
       </c>
       <c r="C565" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D565" s="9">
         <v>8.033269954E9</v>
@@ -16007,13 +16007,13 @@
     </row>
     <row r="566">
       <c r="A566" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B566" s="13">
         <v>1.0</v>
       </c>
       <c r="C566" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D566" s="14">
         <v>8.023154013E9</v>
@@ -16030,13 +16030,13 @@
     </row>
     <row r="567">
       <c r="A567" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B567" s="13">
         <v>1.0</v>
       </c>
       <c r="C567" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D567" s="14">
         <v>8.033047088E9</v>
@@ -16053,13 +16053,13 @@
     </row>
     <row r="568">
       <c r="A568" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B568" s="13">
         <v>1.0</v>
       </c>
       <c r="C568" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D568" s="14">
         <v>8.033047088E9</v>
@@ -16076,13 +16076,13 @@
     </row>
     <row r="569">
       <c r="A569" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B569" s="13">
         <v>1.0</v>
       </c>
       <c r="C569" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D569" s="14">
         <v>8.023221192E9</v>
@@ -16099,13 +16099,13 @@
     </row>
     <row r="570">
       <c r="A570" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B570" s="13">
         <v>1.0</v>
       </c>
       <c r="C570" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D570" s="14">
         <v>8.0330693389E10</v>
@@ -16122,13 +16122,13 @@
     </row>
     <row r="571">
       <c r="A571" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B571" s="13">
         <v>1.0</v>
       </c>
       <c r="C571" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D571" s="14">
         <v>8.037404128E9</v>
@@ -16145,13 +16145,13 @@
     </row>
     <row r="572">
       <c r="A572" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B572" s="13">
         <v>1.0</v>
       </c>
       <c r="C572" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D572" s="14">
         <v>8.037404128E9</v>
@@ -16168,16 +16168,16 @@
     </row>
     <row r="573">
       <c r="A573" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B573" s="13">
         <v>1.0</v>
       </c>
       <c r="C573" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D573" s="14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E573" s="14">
         <v>1.0</v>
@@ -16191,16 +16191,16 @@
     </row>
     <row r="574">
       <c r="A574" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B574" s="13">
         <v>1.0</v>
       </c>
       <c r="C574" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D574" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E574" s="14">
         <v>1.0</v>
@@ -16227,7 +16227,7 @@
     </row>
     <row r="576">
       <c r="A576" s="24" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B576" s="25"/>
       <c r="C576" s="26"/>
@@ -16242,13 +16242,13 @@
     </row>
     <row r="577">
       <c r="A577" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B577" s="13">
         <v>1.0</v>
       </c>
       <c r="C577" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D577" s="14">
         <v>8.023230526E9</v>
@@ -16280,13 +16280,13 @@
     </row>
     <row r="578">
       <c r="A578" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B578" s="13">
         <v>1.0</v>
       </c>
       <c r="C578" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D578" s="14">
         <v>8.023230526E9</v>
@@ -16318,13 +16318,13 @@
     </row>
     <row r="579">
       <c r="A579" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B579" s="13">
         <v>1.0</v>
       </c>
       <c r="C579" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D579" s="14">
         <v>7.053152586E9</v>
@@ -16341,13 +16341,13 @@
     </row>
     <row r="580">
       <c r="A580" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B580" s="13">
         <v>1.0</v>
       </c>
       <c r="C580" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D580" s="14">
         <v>7.053152586E9</v>
@@ -16364,13 +16364,13 @@
     </row>
     <row r="581">
       <c r="A581" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B581" s="13">
         <v>1.0</v>
       </c>
       <c r="C581" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D581" s="14">
         <v>8.034360992E9</v>
@@ -16387,13 +16387,13 @@
     </row>
     <row r="582">
       <c r="A582" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B582" s="13">
         <v>1.0</v>
       </c>
       <c r="C582" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D582" s="14">
         <v>8.034360992E9</v>
@@ -16410,13 +16410,13 @@
     </row>
     <row r="583">
       <c r="A583" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B583" s="13">
         <v>1.0</v>
       </c>
       <c r="C583" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D583" s="14">
         <v>8.09944006E9</v>
@@ -16433,13 +16433,13 @@
     </row>
     <row r="584">
       <c r="A584" s="12" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B584" s="13">
         <v>1.0</v>
       </c>
       <c r="C584" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D584" s="14">
         <v>8.09944006E9</v>
@@ -16456,13 +16456,13 @@
     </row>
     <row r="585">
       <c r="A585" s="12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B585" s="13">
         <v>1.0</v>
       </c>
       <c r="C585" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D585" s="14">
         <v>8.089886511E9</v>
@@ -16479,13 +16479,13 @@
     </row>
     <row r="586">
       <c r="A586" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B586" s="13">
         <v>1.0</v>
       </c>
       <c r="C586" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D586" s="14">
         <v>8.089886511E9</v>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="588">
       <c r="A588" s="24" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B588" s="25"/>
       <c r="C588" s="26"/>
@@ -16545,13 +16545,13 @@
     </row>
     <row r="589">
       <c r="A589" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B589" s="13">
         <v>1.0</v>
       </c>
       <c r="C589" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D589" s="14">
         <v>8.092731761E9</v>
@@ -16568,13 +16568,13 @@
     </row>
     <row r="590">
       <c r="A590" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B590" s="13">
         <v>1.0</v>
       </c>
       <c r="C590" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D590" s="14">
         <v>8.033329207E9</v>
@@ -16591,13 +16591,13 @@
     </row>
     <row r="591">
       <c r="A591" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B591" s="13">
         <v>1.0</v>
       </c>
       <c r="C591" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D591" s="14">
         <v>8.023057851E9</v>
@@ -16614,13 +16614,13 @@
     </row>
     <row r="592">
       <c r="A592" s="12" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B592" s="13">
         <v>1.0</v>
       </c>
       <c r="C592" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D592" s="14">
         <v>8.023057851E9</v>
@@ -16637,13 +16637,13 @@
     </row>
     <row r="593">
       <c r="A593" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B593" s="13">
         <v>1.0</v>
       </c>
       <c r="C593" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D593" s="14">
         <v>8.029726428E9</v>
@@ -16660,13 +16660,13 @@
     </row>
     <row r="594">
       <c r="A594" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B594" s="13">
         <v>1.0</v>
       </c>
       <c r="C594" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D594" s="14">
         <v>8.092902312E9</v>
@@ -16683,13 +16683,13 @@
     </row>
     <row r="595">
       <c r="A595" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B595" s="13">
         <v>1.0</v>
       </c>
       <c r="C595" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D595" s="14">
         <v>8.023551119E9</v>
@@ -16706,13 +16706,13 @@
     </row>
     <row r="596">
       <c r="A596" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B596" s="13">
         <v>1.0</v>
       </c>
       <c r="C596" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D596" s="14">
         <v>8.023551119E9</v>
@@ -16729,13 +16729,13 @@
     </row>
     <row r="597">
       <c r="A597" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B597" s="13">
         <v>1.0</v>
       </c>
       <c r="C597" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D597" s="13">
         <v>8.023012426E9</v>
@@ -16752,13 +16752,13 @@
     </row>
     <row r="598">
       <c r="A598" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B598" s="13">
         <v>1.0</v>
       </c>
       <c r="C598" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D598" s="14">
         <v>8.023506307E9</v>
@@ -16788,7 +16788,7 @@
     </row>
     <row r="600">
       <c r="A600" s="24" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B600" s="25"/>
       <c r="C600" s="26"/>
@@ -16818,13 +16818,13 @@
     </row>
     <row r="601">
       <c r="A601" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B601" s="13">
         <v>1.0</v>
       </c>
       <c r="C601" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D601" s="13">
         <v>8.182612222E9</v>
@@ -16841,13 +16841,13 @@
     </row>
     <row r="602">
       <c r="A602" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B602" s="13">
         <v>1.0</v>
       </c>
       <c r="C602" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D602" s="13">
         <v>8.182612222E9</v>
@@ -16864,13 +16864,13 @@
     </row>
     <row r="603">
       <c r="A603" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B603" s="13">
         <v>1.0</v>
       </c>
       <c r="C603" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D603" s="13">
         <v>8.026656748E9</v>
@@ -16887,13 +16887,13 @@
     </row>
     <row r="604">
       <c r="A604" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B604" s="13">
         <v>1.0</v>
       </c>
       <c r="C604" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D604" s="13">
         <v>8.023316251E9</v>
@@ -16910,13 +16910,13 @@
     </row>
     <row r="605">
       <c r="A605" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B605" s="13">
         <v>1.0</v>
       </c>
       <c r="C605" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D605" s="13">
         <v>8.023316251E9</v>
@@ -16933,13 +16933,13 @@
     </row>
     <row r="606">
       <c r="A606" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B606" s="13">
         <v>1.0</v>
       </c>
       <c r="C606" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D606" s="13">
         <v>7.467166671E9</v>
@@ -16956,13 +16956,13 @@
     </row>
     <row r="607">
       <c r="A607" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B607" s="13">
         <v>1.0</v>
       </c>
       <c r="C607" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D607" s="13">
         <v>7.467166671E9</v>
@@ -16979,13 +16979,13 @@
     </row>
     <row r="608">
       <c r="A608" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B608" s="13">
         <v>1.0</v>
       </c>
       <c r="C608" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D608" s="14">
         <v>8.183103038E9</v>
@@ -17002,13 +17002,13 @@
     </row>
     <row r="609">
       <c r="A609" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B609" s="13">
         <v>1.0</v>
       </c>
       <c r="C609" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D609" s="14">
         <v>7.03521206E9</v>
@@ -17025,13 +17025,13 @@
     </row>
     <row r="610">
       <c r="A610" s="12" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B610" s="13">
         <v>1.0</v>
       </c>
       <c r="C610" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D610" s="14">
         <v>7.03521206E9</v>
@@ -17061,7 +17061,7 @@
     </row>
     <row r="612">
       <c r="A612" s="47" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B612" s="48"/>
       <c r="C612" s="48"/>
@@ -17076,13 +17076,13 @@
     </row>
     <row r="613">
       <c r="A613" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B613" s="13">
         <v>1.0</v>
       </c>
       <c r="C613" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D613" s="14">
         <v>8.023005676E9</v>
@@ -17099,13 +17099,13 @@
     </row>
     <row r="614">
       <c r="A614" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B614" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C614" s="14" t="s">
         <v>642</v>
-      </c>
-      <c r="B614" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C614" s="14" t="s">
-        <v>641</v>
       </c>
       <c r="D614" s="14">
         <v>8.0233004E9</v>
@@ -17122,13 +17122,13 @@
     </row>
     <row r="615">
       <c r="A615" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B615" s="13">
         <v>1.0</v>
       </c>
       <c r="C615" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D615" s="14">
         <v>9.115911396E9</v>
@@ -17145,13 +17145,13 @@
     </row>
     <row r="616">
       <c r="A616" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B616" s="13">
         <v>1.0</v>
       </c>
       <c r="C616" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D616" s="14">
         <v>8.027352376E9</v>
@@ -17168,13 +17168,13 @@
     </row>
     <row r="617">
       <c r="A617" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B617" s="13">
         <v>1.0</v>
       </c>
       <c r="C617" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D617" s="14">
         <v>8.163341596E9</v>
@@ -17206,13 +17206,13 @@
     </row>
     <row r="618">
       <c r="A618" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B618" s="13">
         <v>1.0</v>
       </c>
       <c r="C618" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D618" s="14">
         <v>8.078245569E9</v>
@@ -17229,13 +17229,13 @@
     </row>
     <row r="619">
       <c r="A619" s="29" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B619" s="13">
         <v>1.0</v>
       </c>
       <c r="C619" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D619" s="14">
         <v>8.06298339E9</v>
@@ -17252,13 +17252,13 @@
     </row>
     <row r="620">
       <c r="A620" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B620" s="13">
         <v>1.0</v>
       </c>
       <c r="C620" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D620" s="14">
         <v>7.061041417E9</v>
@@ -17275,13 +17275,13 @@
     </row>
     <row r="621">
       <c r="A621" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B621" s="13">
         <v>1.0</v>
       </c>
       <c r="C621" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D621" s="14">
         <v>7.061041417E9</v>
@@ -17298,13 +17298,13 @@
     </row>
     <row r="622">
       <c r="A622" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B622" s="13">
         <v>1.0</v>
       </c>
       <c r="C622" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D622" s="14">
         <v>8.062316717E9</v>
@@ -17321,13 +17321,13 @@
     </row>
     <row r="623">
       <c r="A623" s="29" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B623" s="13">
         <v>1.0</v>
       </c>
       <c r="C623" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D623" s="14">
         <v>8.023270405E9</v>
@@ -17357,7 +17357,7 @@
     </row>
     <row r="625">
       <c r="A625" s="47" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B625" s="48"/>
       <c r="C625" s="48"/>
@@ -17387,13 +17387,13 @@
     </row>
     <row r="626">
       <c r="A626" s="29" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B626" s="13">
         <v>1.0</v>
       </c>
       <c r="C626" s="13" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D626" s="14">
         <v>8.038500818E9</v>
@@ -17410,13 +17410,13 @@
     </row>
     <row r="627">
       <c r="A627" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="B627" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C627" s="13" t="s">
         <v>656</v>
-      </c>
-      <c r="B627" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C627" s="13" t="s">
-        <v>655</v>
       </c>
       <c r="D627" s="14">
         <v>7.030260852E9</v>
@@ -17433,13 +17433,13 @@
     </row>
     <row r="628">
       <c r="A628" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B628" s="13">
         <v>1.0</v>
       </c>
       <c r="C628" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D628" s="14">
         <v>7.055444156E9</v>
@@ -17456,13 +17456,13 @@
     </row>
     <row r="629">
       <c r="A629" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B629" s="13">
         <v>1.0</v>
       </c>
       <c r="C629" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D629" s="14">
         <v>8.032022492E9</v>
@@ -17479,13 +17479,13 @@
     </row>
     <row r="630">
       <c r="A630" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B630" s="13">
         <v>1.0</v>
       </c>
       <c r="C630" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D630" s="14">
         <v>8.023105729E9</v>
@@ -17502,13 +17502,13 @@
     </row>
     <row r="631">
       <c r="A631" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B631" s="13">
         <v>1.0</v>
       </c>
       <c r="C631" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D631" s="14">
         <v>9.134050297E9</v>
@@ -17540,13 +17540,13 @@
     </row>
     <row r="632">
       <c r="A632" s="9" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B632" s="10">
         <v>1.0</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D632" s="10">
         <v>9.090140109E9</v>
@@ -17557,13 +17557,13 @@
     </row>
     <row r="633">
       <c r="A633" s="29" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B633" s="13">
         <v>1.0</v>
       </c>
       <c r="C633" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D633" s="13">
         <v>8.035126889E9</v>
@@ -17580,13 +17580,13 @@
     </row>
     <row r="634">
       <c r="A634" s="29" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B634" s="13">
         <v>1.0</v>
       </c>
       <c r="C634" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D634" s="14">
         <v>8.035023802E9</v>
@@ -17603,13 +17603,13 @@
     </row>
     <row r="635">
       <c r="A635" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B635" s="13">
         <v>1.0</v>
       </c>
       <c r="C635" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D635" s="13">
         <v>8.056835983E9</v>
@@ -17639,7 +17639,7 @@
     </row>
     <row r="637">
       <c r="A637" s="24" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B637" s="25"/>
       <c r="C637" s="26"/>
@@ -17654,13 +17654,13 @@
     </row>
     <row r="638">
       <c r="A638" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B638" s="13">
         <v>1.0</v>
       </c>
       <c r="C638" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D638" s="14">
         <v>9.081192203E9</v>
@@ -17677,13 +17677,13 @@
     </row>
     <row r="639">
       <c r="A639" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B639" s="13">
         <v>1.0</v>
       </c>
       <c r="C639" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D639" s="14">
         <v>9.15430212E9</v>
@@ -17700,13 +17700,13 @@
     </row>
     <row r="640">
       <c r="A640" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B640" s="13">
         <v>1.0</v>
       </c>
       <c r="C640" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D640" s="14">
         <v>9.15430212E9</v>
@@ -17723,13 +17723,13 @@
     </row>
     <row r="641">
       <c r="A641" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B641" s="13">
         <v>1.0</v>
       </c>
       <c r="C641" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D641" s="14">
         <v>8.023224437E9</v>
@@ -17746,13 +17746,13 @@
     </row>
     <row r="642">
       <c r="A642" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B642" s="13">
         <v>1.0</v>
       </c>
       <c r="C642" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D642" s="14">
         <v>8.023224437E9</v>
@@ -17769,13 +17769,13 @@
     </row>
     <row r="643">
       <c r="A643" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B643" s="13">
         <v>1.0</v>
       </c>
       <c r="C643" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D643" s="14">
         <v>8.056838983E9</v>
@@ -17792,13 +17792,13 @@
     </row>
     <row r="644">
       <c r="A644" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B644" s="13">
         <v>1.0</v>
       </c>
       <c r="C644" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D644" s="14">
         <v>8.030434094E9</v>
@@ -17815,13 +17815,13 @@
     </row>
     <row r="645">
       <c r="A645" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B645" s="13">
         <v>1.0</v>
       </c>
       <c r="C645" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D645" s="14">
         <v>8.030434094E9</v>
@@ -17838,13 +17838,13 @@
     </row>
     <row r="646">
       <c r="A646" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B646" s="13">
         <v>1.0</v>
       </c>
       <c r="C646" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D646" s="14">
         <v>8.023163719E9</v>
@@ -17861,13 +17861,13 @@
     </row>
     <row r="647">
       <c r="A647" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B647" s="13">
         <v>1.0</v>
       </c>
       <c r="C647" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D647" s="14">
         <v>8.023163719E9</v>
@@ -17897,7 +17897,7 @@
     </row>
     <row r="649">
       <c r="A649" s="47" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B649" s="48"/>
       <c r="C649" s="48"/>
@@ -17927,13 +17927,13 @@
     </row>
     <row r="650">
       <c r="A650" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B650" s="10">
         <v>1.0</v>
       </c>
       <c r="C650" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D650" s="10">
         <v>8.033484174E9</v>
@@ -17944,13 +17944,13 @@
     </row>
     <row r="651">
       <c r="A651" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B651" s="13">
         <v>1.0</v>
       </c>
       <c r="C651" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D651" s="14">
         <v>8.06298339E9</v>
@@ -17964,29 +17964,6 @@
       <c r="I651" s="5"/>
       <c r="J651" s="5"/>
       <c r="K651" s="5"/>
-    </row>
-    <row r="652">
-      <c r="A652" s="12" t="s">
-        <v>680</v>
-      </c>
-      <c r="B652" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C652" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="D652" s="14">
-        <v>7.904077907E9</v>
-      </c>
-      <c r="E652" s="14">
-        <v>44.0</v>
-      </c>
-      <c r="F652" s="5"/>
-      <c r="G652" s="5"/>
-      <c r="H652" s="5"/>
-      <c r="I652" s="5"/>
-      <c r="J652" s="5"/>
-      <c r="K652" s="5"/>
     </row>
     <row r="653">
       <c r="A653" s="24"/>
@@ -18087,7 +18064,7 @@
       </c>
       <c r="B659" s="13">
         <f>SUM(B3:B658)</f>
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C659" s="14"/>
       <c r="D659" s="14"/>
@@ -28090,13 +28067,13 @@
     </row>
     <row r="218">
       <c r="A218" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B218" s="10">
         <v>1.0</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D218" s="10">
         <v>8.033484174E9</v>
@@ -29206,7 +29183,7 @@
     </row>
     <row r="266">
       <c r="A266" s="12" t="s">
-        <v>680</v>
+        <v>363</v>
       </c>
       <c r="B266" s="13">
         <v>1.0</v>
@@ -30772,7 +30749,7 @@
     </row>
     <row r="333">
       <c r="A333" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B333" s="13">
         <v>1.0</v>
@@ -30795,7 +30772,7 @@
     </row>
     <row r="334">
       <c r="A334" s="36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B334" s="37">
         <v>1.0</v>
@@ -30818,7 +30795,7 @@
     </row>
     <row r="335">
       <c r="A335" s="24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B335" s="25"/>
       <c r="C335" s="26"/>
@@ -30833,7 +30810,7 @@
     </row>
     <row r="336">
       <c r="A336" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B336" s="13">
         <v>1.0</v>
@@ -30856,7 +30833,7 @@
     </row>
     <row r="337">
       <c r="A337" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B337" s="13">
         <v>1.0</v>
@@ -30969,7 +30946,7 @@
         <v>2.0</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D341" s="13">
         <v>8.023166383E9</v>
@@ -30999,7 +30976,7 @@
     </row>
     <row r="343">
       <c r="A343" s="47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B343" s="48"/>
       <c r="C343" s="48"/>
@@ -31029,13 +31006,13 @@
     </row>
     <row r="344">
       <c r="A344" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B344" s="13">
         <v>1.0</v>
       </c>
       <c r="C344" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D344" s="14">
         <v>7.065512125E9</v>
@@ -31052,13 +31029,13 @@
     </row>
     <row r="345">
       <c r="A345" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B345" s="13">
         <v>1.0</v>
       </c>
       <c r="C345" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D345" s="14">
         <v>9.081192203E9</v>
@@ -31075,13 +31052,13 @@
     </row>
     <row r="346">
       <c r="A346" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B346" s="13">
         <v>1.0</v>
       </c>
       <c r="C346" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D346" s="14">
         <v>8.054091505E9</v>
@@ -31098,13 +31075,13 @@
     </row>
     <row r="347">
       <c r="A347" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B347" s="13">
         <v>1.0</v>
       </c>
       <c r="C347" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D347" s="14">
         <v>7.956311081E9</v>
@@ -31121,13 +31098,13 @@
     </row>
     <row r="348">
       <c r="A348" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B348" s="13">
         <v>1.0</v>
       </c>
       <c r="C348" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D348" s="14">
         <v>8.023070734E9</v>
@@ -31159,13 +31136,13 @@
     </row>
     <row r="349">
       <c r="A349" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B349" s="13">
         <v>1.0</v>
       </c>
       <c r="C349" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D349" s="14">
         <v>8.023309846E9</v>
@@ -31182,13 +31159,13 @@
     </row>
     <row r="350">
       <c r="A350" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B350" s="13">
         <v>1.0</v>
       </c>
       <c r="C350" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D350" s="14">
         <v>8.023309846E9</v>
@@ -31205,13 +31182,13 @@
     </row>
     <row r="351">
       <c r="A351" s="23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B351" s="13">
         <v>1.0</v>
       </c>
       <c r="C351" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D351" s="14">
         <v>8.023405394E9</v>
@@ -31228,13 +31205,13 @@
     </row>
     <row r="352">
       <c r="A352" s="23" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B352" s="13">
         <v>1.0</v>
       </c>
       <c r="C352" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D352" s="14">
         <v>8.023405394E9</v>
@@ -31251,13 +31228,13 @@
     </row>
     <row r="353">
       <c r="A353" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B353" s="13">
         <v>1.0</v>
       </c>
       <c r="C353" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D353" s="14">
         <v>8.075048968E9</v>
@@ -31287,7 +31264,7 @@
     </row>
     <row r="355">
       <c r="A355" s="24" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B355" s="25"/>
       <c r="C355" s="26"/>
@@ -31302,13 +31279,13 @@
     </row>
     <row r="356">
       <c r="A356" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B356" s="13">
         <v>1.0</v>
       </c>
       <c r="C356" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D356" s="14">
         <v>7.033311706E9</v>
@@ -31325,13 +31302,13 @@
     </row>
     <row r="357">
       <c r="A357" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B357" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C357" s="14" t="s">
         <v>392</v>
-      </c>
-      <c r="B357" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C357" s="14" t="s">
-        <v>391</v>
       </c>
       <c r="D357" s="14">
         <v>7.033311706E9</v>
@@ -31348,13 +31325,13 @@
     </row>
     <row r="358">
       <c r="A358" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B358" s="13">
         <v>1.0</v>
       </c>
       <c r="C358" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D358" s="14">
         <v>8.032196962E9</v>
@@ -31371,13 +31348,13 @@
     </row>
     <row r="359">
       <c r="A359" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B359" s="13">
         <v>1.0</v>
       </c>
       <c r="C359" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D359" s="14">
         <v>8.038269145E9</v>
@@ -31394,13 +31371,13 @@
     </row>
     <row r="360">
       <c r="A360" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B360" s="13">
         <v>1.0</v>
       </c>
       <c r="C360" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D360" s="14">
         <v>8.037632224E9</v>
@@ -31432,13 +31409,13 @@
     </row>
     <row r="361">
       <c r="A361" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B361" s="13">
         <v>1.0</v>
       </c>
       <c r="C361" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D361" s="14">
         <v>8.029108265E9</v>
@@ -31455,13 +31432,13 @@
     </row>
     <row r="362">
       <c r="A362" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B362" s="13">
         <v>1.0</v>
       </c>
       <c r="C362" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D362" s="14">
         <v>9.159868421E9</v>
@@ -31478,13 +31455,13 @@
     </row>
     <row r="363">
       <c r="A363" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B363" s="13">
         <v>1.0</v>
       </c>
       <c r="C363" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D363" s="14">
         <v>9.159868421E9</v>
@@ -31501,13 +31478,13 @@
     </row>
     <row r="364">
       <c r="A364" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B364" s="13">
         <v>1.0</v>
       </c>
       <c r="C364" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D364" s="14">
         <v>7.036281456E9</v>
@@ -31524,13 +31501,13 @@
     </row>
     <row r="365">
       <c r="A365" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B365" s="13">
         <v>1.0</v>
       </c>
       <c r="C365" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D365" s="14">
         <v>7.036281456E9</v>
@@ -31560,7 +31537,7 @@
     </row>
     <row r="367">
       <c r="A367" s="24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B367" s="25"/>
       <c r="C367" s="26"/>
@@ -31575,13 +31552,13 @@
     </row>
     <row r="368">
       <c r="A368" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B368" s="13">
         <v>1.0</v>
       </c>
       <c r="C368" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D368" s="14">
         <v>8.036120862E9</v>
@@ -31598,13 +31575,13 @@
     </row>
     <row r="369">
       <c r="A369" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B369" s="13">
         <v>1.0</v>
       </c>
       <c r="C369" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D369" s="14">
         <v>8.036120862E9</v>
@@ -31621,13 +31598,13 @@
     </row>
     <row r="370">
       <c r="A370" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B370" s="13">
         <v>1.0</v>
       </c>
       <c r="C370" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D370" s="14">
         <v>9.019404989E9</v>
@@ -31644,13 +31621,13 @@
     </row>
     <row r="371">
       <c r="A371" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B371" s="13">
         <v>1.0</v>
       </c>
       <c r="C371" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D371" s="14">
         <v>8.034040437E9</v>
@@ -31667,13 +31644,13 @@
     </row>
     <row r="372">
       <c r="A372" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B372" s="13">
         <v>1.0</v>
       </c>
       <c r="C372" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D372" s="14">
         <v>8.034040437E9</v>
@@ -31690,13 +31667,13 @@
     </row>
     <row r="373">
       <c r="A373" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B373" s="13">
         <v>1.0</v>
       </c>
       <c r="C373" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D373" s="14">
         <v>9.095607784E9</v>
@@ -31713,13 +31690,13 @@
     </row>
     <row r="374">
       <c r="A374" s="12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B374" s="13">
         <v>1.0</v>
       </c>
       <c r="C374" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D374" s="13">
         <v>7.031890883E9</v>
@@ -31742,7 +31719,7 @@
         <v>1.0</v>
       </c>
       <c r="C375" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D375" s="14">
         <v>8.02224805E8</v>
@@ -31774,13 +31751,13 @@
     </row>
     <row r="376">
       <c r="A376" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B376" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C376" s="14" t="s">
         <v>411</v>
-      </c>
-      <c r="B376" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C376" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="D376" s="14">
         <v>8.02224805E8</v>
@@ -31812,13 +31789,13 @@
     </row>
     <row r="377">
       <c r="A377" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B377" s="13">
         <v>1.0</v>
       </c>
       <c r="C377" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D377" s="14">
         <v>8.038190491E9</v>
@@ -31848,7 +31825,7 @@
     </row>
     <row r="379">
       <c r="A379" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B379" s="25"/>
       <c r="C379" s="26"/>
@@ -31863,13 +31840,13 @@
     </row>
     <row r="380">
       <c r="A380" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B380" s="13">
         <v>1.0</v>
       </c>
       <c r="C380" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D380" s="14">
         <v>8.038096396E9</v>
@@ -31886,13 +31863,13 @@
     </row>
     <row r="381">
       <c r="A381" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B381" s="13">
         <v>1.0</v>
       </c>
       <c r="C381" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D381" s="14">
         <v>8.038096396E9</v>
@@ -31909,13 +31886,13 @@
     </row>
     <row r="382">
       <c r="A382" s="12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B382" s="13">
         <v>1.0</v>
       </c>
       <c r="C382" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D382" s="13">
         <v>8.033162339E9</v>
@@ -31938,7 +31915,7 @@
         <v>1.0</v>
       </c>
       <c r="C383" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D383" s="13">
         <v>8.033162339E9</v>
@@ -31955,13 +31932,13 @@
     </row>
     <row r="384">
       <c r="A384" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B384" s="13">
         <v>1.0</v>
       </c>
       <c r="C384" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D384" s="14">
         <v>8.033162339E9</v>
@@ -31978,13 +31955,13 @@
     </row>
     <row r="385">
       <c r="A385" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B385" s="13">
         <v>1.0</v>
       </c>
       <c r="C385" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D385" s="14">
         <v>8.035023802E9</v>
@@ -32001,13 +31978,13 @@
     </row>
     <row r="386">
       <c r="A386" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B386" s="13">
         <v>1.0</v>
       </c>
       <c r="C386" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D386" s="14">
         <v>7.060844005E9</v>
@@ -32024,13 +32001,13 @@
     </row>
     <row r="387">
       <c r="A387" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B387" s="13">
         <v>1.0</v>
       </c>
       <c r="C387" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D387" s="14">
         <v>7.060844005E9</v>
@@ -32047,13 +32024,13 @@
     </row>
     <row r="388">
       <c r="A388" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B388" s="13">
         <v>1.0</v>
       </c>
       <c r="C388" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D388" s="14">
         <v>8.027733439E9</v>
@@ -32085,13 +32062,13 @@
     </row>
     <row r="389">
       <c r="A389" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B389" s="13">
         <v>1.0</v>
       </c>
       <c r="C389" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D389" s="14">
         <v>8.027733439E9</v>
@@ -32121,7 +32098,7 @@
     </row>
     <row r="391">
       <c r="A391" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B391" s="25"/>
       <c r="C391" s="26"/>
@@ -32136,13 +32113,13 @@
     </row>
     <row r="392">
       <c r="A392" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B392" s="13">
         <v>1.0</v>
       </c>
       <c r="C392" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D392" s="14">
         <v>8.033210754E9</v>
@@ -32157,13 +32134,13 @@
     </row>
     <row r="393">
       <c r="A393" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B393" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C393" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="B393" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C393" s="14" t="s">
-        <v>426</v>
       </c>
       <c r="D393" s="13">
         <v>8.039462242E9</v>
@@ -32178,13 +32155,13 @@
     </row>
     <row r="394">
       <c r="A394" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B394" s="13">
         <v>1.0</v>
       </c>
       <c r="C394" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D394" s="13">
         <v>8.033670457E9</v>
@@ -32199,13 +32176,13 @@
     </row>
     <row r="395">
       <c r="A395" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B395" s="13">
         <v>1.0</v>
       </c>
       <c r="C395" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D395" s="13">
         <v>8.066484528E9</v>
@@ -32220,13 +32197,13 @@
     </row>
     <row r="396">
       <c r="A396" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B396" s="13">
         <v>1.0</v>
       </c>
       <c r="C396" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D396" s="13">
         <v>8.139314127E9</v>
@@ -32241,13 +32218,13 @@
     </row>
     <row r="397">
       <c r="A397" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B397" s="13">
         <v>1.0</v>
       </c>
       <c r="C397" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D397" s="13">
         <v>8.022755703E9</v>
@@ -32262,13 +32239,13 @@
     </row>
     <row r="398">
       <c r="A398" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B398" s="13">
         <v>1.0</v>
       </c>
       <c r="C398" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D398" s="14">
         <v>9.024198439E9</v>
@@ -32298,13 +32275,13 @@
     </row>
     <row r="399">
       <c r="A399" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B399" s="13">
         <v>1.0</v>
       </c>
       <c r="C399" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D399" s="14">
         <v>8.0358886E9</v>
@@ -32319,13 +32296,13 @@
     </row>
     <row r="400">
       <c r="A400" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B400" s="13">
         <v>1.0</v>
       </c>
       <c r="C400" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D400" s="14">
         <v>8.022637076E9</v>
@@ -32340,13 +32317,13 @@
     </row>
     <row r="401">
       <c r="A401" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B401" s="13">
         <v>1.0</v>
       </c>
       <c r="C401" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D401" s="14">
         <v>8.037865897E9</v>
@@ -32372,7 +32349,7 @@
     </row>
     <row r="403">
       <c r="A403" s="24" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B403" s="25"/>
       <c r="C403" s="26"/>
@@ -32387,13 +32364,13 @@
     </row>
     <row r="404">
       <c r="A404" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B404" s="13">
         <v>1.0</v>
       </c>
       <c r="C404" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D404" s="14">
         <v>7.068629985E9</v>
@@ -32408,13 +32385,13 @@
     </row>
     <row r="405">
       <c r="A405" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B405" s="13">
         <v>1.0</v>
       </c>
       <c r="C405" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D405" s="14">
         <v>7.068629985E9</v>
@@ -32429,13 +32406,13 @@
     </row>
     <row r="406">
       <c r="A406" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B406" s="13">
         <v>1.0</v>
       </c>
       <c r="C406" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D406" s="14">
         <v>8.03315128E9</v>
@@ -32450,13 +32427,13 @@
     </row>
     <row r="407">
       <c r="A407" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B407" s="13">
         <v>1.0</v>
       </c>
       <c r="C407" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D407" s="14">
         <v>8.03315128E9</v>
@@ -32471,13 +32448,13 @@
     </row>
     <row r="408">
       <c r="A408" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B408" s="13">
         <v>1.0</v>
       </c>
       <c r="C408" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D408" s="14">
         <v>8.026359933E9</v>
@@ -32492,13 +32469,13 @@
     </row>
     <row r="409">
       <c r="A409" s="12" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B409" s="13">
         <v>1.0</v>
       </c>
       <c r="C409" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D409" s="14">
         <v>8.064681335E9</v>
@@ -32513,13 +32490,13 @@
     </row>
     <row r="410">
       <c r="A410" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B410" s="13">
         <v>1.0</v>
       </c>
       <c r="C410" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D410" s="14">
         <v>8.033321482E9</v>
@@ -32534,13 +32511,13 @@
     </row>
     <row r="411">
       <c r="A411" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B411" s="13">
         <v>1.0</v>
       </c>
       <c r="C411" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D411" s="14">
         <v>8.033321482E9</v>
@@ -32555,13 +32532,13 @@
     </row>
     <row r="412">
       <c r="A412" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B412" s="13">
         <v>1.0</v>
       </c>
       <c r="C412" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D412" s="14">
         <v>8.038171859E9</v>
@@ -32576,13 +32553,13 @@
     </row>
     <row r="413">
       <c r="A413" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B413" s="13">
         <v>1.0</v>
       </c>
       <c r="C413" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D413" s="14">
         <v>9.058642558E9</v>
@@ -32622,7 +32599,7 @@
     </row>
     <row r="415">
       <c r="A415" s="24" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B415" s="25"/>
       <c r="C415" s="26"/>
@@ -32637,13 +32614,13 @@
     </row>
     <row r="416">
       <c r="A416" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B416" s="13">
         <v>1.0</v>
       </c>
       <c r="C416" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D416" s="14">
         <v>8.034841114E9</v>
@@ -32660,13 +32637,13 @@
     </row>
     <row r="417">
       <c r="A417" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B417" s="13">
         <v>1.0</v>
       </c>
       <c r="C417" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D417" s="14">
         <v>8.058524769E9</v>
@@ -32683,13 +32660,13 @@
     </row>
     <row r="418">
       <c r="A418" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B418" s="13">
         <v>1.0</v>
       </c>
       <c r="C418" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D418" s="14">
         <v>9.037960582E9</v>
@@ -32706,13 +32683,13 @@
     </row>
     <row r="419">
       <c r="A419" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B419" s="13">
         <v>1.0</v>
       </c>
       <c r="C419" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D419" s="13">
         <v>8.032002285E9</v>
@@ -32729,13 +32706,13 @@
     </row>
     <row r="420">
       <c r="A420" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B420" s="13">
         <v>1.0</v>
       </c>
       <c r="C420" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D420" s="14">
         <v>8.023032371E9</v>
@@ -32752,13 +32729,13 @@
     </row>
     <row r="421">
       <c r="A421" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B421" s="13">
         <v>1.0</v>
       </c>
       <c r="C421" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D421" s="52">
         <v>8.023136932E9</v>
@@ -32775,13 +32752,13 @@
     </row>
     <row r="422">
       <c r="A422" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B422" s="13">
         <v>1.0</v>
       </c>
       <c r="C422" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D422" s="13">
         <v>8.034360992E9</v>
@@ -32798,13 +32775,13 @@
     </row>
     <row r="423">
       <c r="A423" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B423" s="13">
         <v>1.0</v>
       </c>
       <c r="C423" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D423" s="13">
         <v>8.023358954E9</v>
@@ -32836,13 +32813,13 @@
     </row>
     <row r="424">
       <c r="A424" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B424" s="13">
         <v>1.0</v>
       </c>
       <c r="C424" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D424" s="13">
         <v>8.023056347E9</v>
@@ -32859,13 +32836,13 @@
     </row>
     <row r="425">
       <c r="A425" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B425" s="13">
         <v>1.0</v>
       </c>
       <c r="C425" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D425" s="13">
         <v>6.22041817E8</v>
@@ -32910,13 +32887,13 @@
     </row>
     <row r="428">
       <c r="A428" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B428" s="13">
         <v>1.0</v>
       </c>
       <c r="C428" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D428" s="14">
         <v>7.086669911E9</v>
@@ -32933,13 +32910,13 @@
     </row>
     <row r="429">
       <c r="A429" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B429" s="13">
         <v>1.0</v>
       </c>
       <c r="C429" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D429" s="13">
         <v>8.022228967E9</v>
@@ -32956,13 +32933,13 @@
     </row>
     <row r="430">
       <c r="A430" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B430" s="13">
         <v>1.0</v>
       </c>
       <c r="C430" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D430" s="14">
         <v>8.06302025E9</v>
@@ -32979,13 +32956,13 @@
     </row>
     <row r="431">
       <c r="A431" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B431" s="13">
         <v>1.0</v>
       </c>
       <c r="C431" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D431" s="14">
         <v>8.06302025E9</v>
@@ -33002,13 +32979,13 @@
     </row>
     <row r="432">
       <c r="A432" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B432" s="13">
         <v>1.0</v>
       </c>
       <c r="C432" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D432" s="14">
         <v>8.023529768E9</v>
@@ -33025,13 +33002,13 @@
     </row>
     <row r="433">
       <c r="A433" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B433" s="13">
         <v>1.0</v>
       </c>
       <c r="C433" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D433" s="14">
         <v>7.082866677E9</v>
@@ -33048,13 +33025,13 @@
     </row>
     <row r="434">
       <c r="A434" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B434" s="13">
         <v>1.0</v>
       </c>
       <c r="C434" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D434" s="14">
         <v>7.082866677E9</v>
@@ -33071,13 +33048,13 @@
     </row>
     <row r="435">
       <c r="A435" s="12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B435" s="13">
         <v>1.0</v>
       </c>
       <c r="C435" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D435" s="14">
         <v>7.035681401E9</v>
@@ -33094,13 +33071,13 @@
     </row>
     <row r="436">
       <c r="A436" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B436" s="13">
         <v>1.0</v>
       </c>
       <c r="C436" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D436" s="14">
         <v>8.055527946E9</v>
@@ -33132,13 +33109,13 @@
     </row>
     <row r="437">
       <c r="A437" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B437" s="13">
         <v>1.0</v>
       </c>
       <c r="C437" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D437" s="14">
         <v>8.023194301E9</v>
@@ -33168,7 +33145,7 @@
     </row>
     <row r="439">
       <c r="A439" s="39" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B439" s="25"/>
       <c r="C439" s="25"/>
@@ -33183,13 +33160,13 @@
     </row>
     <row r="440">
       <c r="A440" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B440" s="13">
         <v>1.0</v>
       </c>
       <c r="C440" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D440" s="13">
         <v>7.956338229E9</v>
@@ -33206,13 +33183,13 @@
     </row>
     <row r="441">
       <c r="A441" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B441" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C441" s="13" t="s">
         <v>473</v>
-      </c>
-      <c r="B441" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C441" s="13" t="s">
-        <v>472</v>
       </c>
       <c r="D441" s="13">
         <v>7.956338229E9</v>
@@ -33229,13 +33206,13 @@
     </row>
     <row r="442">
       <c r="A442" s="29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B442" s="13">
         <v>1.0</v>
       </c>
       <c r="C442" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D442" s="13">
         <v>7.956132912E9</v>
@@ -33252,13 +33229,13 @@
     </row>
     <row r="443">
       <c r="A443" s="29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B443" s="13">
         <v>1.0</v>
       </c>
       <c r="C443" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D443" s="13">
         <v>7.956132912E9</v>
@@ -33275,13 +33252,13 @@
     </row>
     <row r="444">
       <c r="A444" s="29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B444" s="13">
         <v>1.0</v>
       </c>
       <c r="C444" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D444" s="13">
         <v>7.95613193E9</v>
@@ -33298,13 +33275,13 @@
     </row>
     <row r="445">
       <c r="A445" s="29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B445" s="13">
         <v>1.0</v>
       </c>
       <c r="C445" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D445" s="13">
         <v>7.95613193E9</v>
@@ -33321,13 +33298,13 @@
     </row>
     <row r="446">
       <c r="A446" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B446" s="13">
         <v>1.0</v>
       </c>
       <c r="C446" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D446" s="13">
         <v>7.939988528E9</v>
@@ -33344,13 +33321,13 @@
     </row>
     <row r="447">
       <c r="A447" s="29" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B447" s="13">
         <v>1.0</v>
       </c>
       <c r="C447" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D447" s="13">
         <v>7.939988528E9</v>
@@ -33367,13 +33344,13 @@
     </row>
     <row r="448">
       <c r="A448" s="29" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B448" s="13">
         <v>1.0</v>
       </c>
       <c r="C448" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D448" s="13">
         <v>9.090403655E9</v>
@@ -33390,13 +33367,13 @@
     </row>
     <row r="449">
       <c r="A449" s="29" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B449" s="13">
         <v>1.0</v>
       </c>
       <c r="C449" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D449" s="13">
         <v>9.090403655E9</v>
@@ -33413,7 +33390,7 @@
     </row>
     <row r="450">
       <c r="A450" s="39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B450" s="25"/>
       <c r="C450" s="25"/>
@@ -33428,13 +33405,13 @@
     </row>
     <row r="451">
       <c r="A451" s="29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B451" s="13">
         <v>1.0</v>
       </c>
       <c r="C451" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D451" s="13">
         <v>7.95689006E9</v>
@@ -33466,13 +33443,13 @@
     </row>
     <row r="452">
       <c r="A452" s="29" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B452" s="13">
         <v>1.0</v>
       </c>
       <c r="C452" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D452" s="13">
         <v>7.95689006E9</v>
@@ -33504,13 +33481,13 @@
     </row>
     <row r="453">
       <c r="A453" s="29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B453" s="13">
         <v>1.0</v>
       </c>
       <c r="C453" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D453" s="13">
         <v>7.956132912E9</v>
@@ -33527,13 +33504,13 @@
     </row>
     <row r="454">
       <c r="A454" s="29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B454" s="13">
         <v>1.0</v>
       </c>
       <c r="C454" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D454" s="13">
         <v>9.022163076E9</v>
@@ -33550,13 +33527,13 @@
     </row>
     <row r="455">
       <c r="A455" s="29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B455" s="13">
         <v>1.0</v>
       </c>
       <c r="C455" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D455" s="13">
         <v>7.940255254E9</v>
@@ -33573,13 +33550,13 @@
     </row>
     <row r="456">
       <c r="A456" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B456" s="13">
         <v>1.0</v>
       </c>
       <c r="C456" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D456" s="13">
         <v>7.834352811E9</v>
@@ -33596,13 +33573,13 @@
     </row>
     <row r="457">
       <c r="A457" s="29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B457" s="13">
         <v>1.0</v>
       </c>
       <c r="C457" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D457" s="13">
         <v>7.834352811E9</v>
@@ -33619,13 +33596,13 @@
     </row>
     <row r="458">
       <c r="A458" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B458" s="13">
         <v>1.0</v>
       </c>
       <c r="C458" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D458" s="13">
         <v>7.834352811E9</v>
@@ -33642,13 +33619,13 @@
     </row>
     <row r="459">
       <c r="A459" s="29" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B459" s="13">
         <v>1.0</v>
       </c>
       <c r="C459" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D459" s="13">
         <v>7.753673669E9</v>
@@ -33665,13 +33642,13 @@
     </row>
     <row r="460">
       <c r="A460" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B460" s="13">
         <v>1.0</v>
       </c>
       <c r="C460" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D460" s="14">
         <v>7.961485817E9</v>
@@ -33731,13 +33708,13 @@
     </row>
     <row r="463">
       <c r="A463" s="29" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B463" s="13">
         <v>1.0</v>
       </c>
       <c r="C463" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D463" s="13">
         <v>7.807493779E9</v>
@@ -33754,13 +33731,13 @@
     </row>
     <row r="464">
       <c r="A464" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="B464" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C464" s="13" t="s">
         <v>497</v>
-      </c>
-      <c r="B464" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C464" s="13" t="s">
-        <v>496</v>
       </c>
       <c r="D464" s="13">
         <v>7.807493779E9</v>
@@ -33777,13 +33754,13 @@
     </row>
     <row r="465">
       <c r="A465" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B465" s="13">
         <v>1.0</v>
       </c>
       <c r="C465" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D465" s="13">
         <v>7.424791947E9</v>
@@ -33800,13 +33777,13 @@
     </row>
     <row r="466">
       <c r="A466" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B466" s="13">
         <v>1.0</v>
       </c>
       <c r="C466" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D466" s="13">
         <v>7.807493779E9</v>
@@ -33823,13 +33800,13 @@
     </row>
     <row r="467">
       <c r="A467" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B467" s="13">
         <v>1.0</v>
       </c>
       <c r="C467" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D467" s="13">
         <v>7.424791947E9</v>
@@ -33861,13 +33838,13 @@
     </row>
     <row r="468">
       <c r="A468" s="29" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B468" s="13">
         <v>1.0</v>
       </c>
       <c r="C468" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D468" s="13">
         <v>7.807493779E9</v>
@@ -33884,16 +33861,16 @@
     </row>
     <row r="469">
       <c r="A469" s="29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B469" s="13">
         <v>1.0</v>
       </c>
       <c r="C469" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D469" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E469" s="13">
         <v>1.0</v>
@@ -33907,13 +33884,13 @@
     </row>
     <row r="470">
       <c r="A470" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B470" s="13">
         <v>1.0</v>
       </c>
       <c r="C470" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D470" s="13">
         <v>7.807493779E9</v>
@@ -33930,13 +33907,13 @@
     </row>
     <row r="471">
       <c r="A471" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B471" s="13">
         <v>1.0</v>
       </c>
       <c r="C471" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D471" s="13">
         <v>7.807493779E9</v>
@@ -33953,16 +33930,16 @@
     </row>
     <row r="472">
       <c r="A472" s="29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B472" s="13">
         <v>1.0</v>
       </c>
       <c r="C472" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D472" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E472" s="13">
         <v>1.0</v>
@@ -33989,7 +33966,7 @@
     </row>
     <row r="474">
       <c r="A474" s="39" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B474" s="25"/>
       <c r="C474" s="25"/>
@@ -34004,16 +33981,16 @@
     </row>
     <row r="475">
       <c r="A475" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B475" s="13">
         <v>1.0</v>
       </c>
       <c r="C475" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D475" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E475" s="13">
         <v>1.0</v>
@@ -34027,16 +34004,16 @@
     </row>
     <row r="476">
       <c r="A476" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B476" s="13">
         <v>1.0</v>
       </c>
       <c r="C476" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D476" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E476" s="13">
         <v>1.0</v>
@@ -34065,16 +34042,16 @@
     </row>
     <row r="477">
       <c r="A477" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B477" s="13">
         <v>1.0</v>
       </c>
       <c r="C477" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D477" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E477" s="13">
         <v>234.0</v>
@@ -34088,16 +34065,16 @@
     </row>
     <row r="478">
       <c r="A478" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B478" s="13">
         <v>1.0</v>
       </c>
       <c r="C478" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D478" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E478" s="13">
         <v>1.0</v>
@@ -34111,16 +34088,16 @@
     </row>
     <row r="479">
       <c r="A479" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B479" s="13">
         <v>1.0</v>
       </c>
       <c r="C479" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D479" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E479" s="13">
         <v>1.0</v>
@@ -34134,13 +34111,13 @@
     </row>
     <row r="480">
       <c r="A480" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B480" s="13">
         <v>1.0</v>
       </c>
       <c r="C480" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D480" s="14">
         <v>7.807493779E9</v>
@@ -34157,13 +34134,13 @@
     </row>
     <row r="481">
       <c r="A481" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B481" s="13">
         <v>1.0</v>
       </c>
       <c r="C481" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D481" s="14">
         <v>7.807493779E9</v>
@@ -34195,13 +34172,13 @@
     </row>
     <row r="482">
       <c r="A482" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B482" s="13">
         <v>1.0</v>
       </c>
       <c r="C482" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D482" s="14">
         <v>7.807493779E9</v>
@@ -34218,13 +34195,13 @@
     </row>
     <row r="483">
       <c r="A483" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B483" s="13">
         <v>1.0</v>
       </c>
       <c r="C483" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D483" s="14">
         <v>7.949394588E9</v>
@@ -34241,13 +34218,13 @@
     </row>
     <row r="484">
       <c r="A484" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B484" s="13">
         <v>1.0</v>
       </c>
       <c r="C484" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D484" s="14">
         <v>7.949394588E9</v>
@@ -34264,7 +34241,7 @@
     </row>
     <row r="485">
       <c r="A485" s="39" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B485" s="25"/>
       <c r="C485" s="25"/>
@@ -34279,13 +34256,13 @@
     </row>
     <row r="486">
       <c r="A486" s="29" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B486" s="13">
         <v>1.0</v>
       </c>
       <c r="C486" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D486" s="13">
         <v>7.055269061E9</v>
@@ -34302,13 +34279,13 @@
     </row>
     <row r="487">
       <c r="A487" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="B487" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C487" s="13" t="s">
         <v>523</v>
-      </c>
-      <c r="B487" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C487" s="13" t="s">
-        <v>522</v>
       </c>
       <c r="D487" s="13">
         <v>7.055269061E9</v>
@@ -34325,13 +34302,13 @@
     </row>
     <row r="488">
       <c r="A488" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B488" s="13">
         <v>1.0</v>
       </c>
       <c r="C488" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D488" s="13">
         <v>7.035375757E9</v>
@@ -34348,13 +34325,13 @@
     </row>
     <row r="489">
       <c r="A489" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B489" s="13">
         <v>1.0</v>
       </c>
       <c r="C489" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D489" s="13">
         <v>8.033459526E9</v>
@@ -34371,13 +34348,13 @@
     </row>
     <row r="490">
       <c r="A490" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B490" s="13">
         <v>1.0</v>
       </c>
       <c r="C490" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D490" s="13">
         <v>7.956447698E9</v>
@@ -34394,13 +34371,13 @@
     </row>
     <row r="491">
       <c r="A491" s="29" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B491" s="13">
         <v>1.0</v>
       </c>
       <c r="C491" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D491" s="13">
         <v>7.956447698E9</v>
@@ -34417,13 +34394,13 @@
     </row>
     <row r="492">
       <c r="A492" s="29" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B492" s="13">
         <v>1.0</v>
       </c>
       <c r="C492" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D492" s="13">
         <v>7.957449008E9</v>
@@ -34446,7 +34423,7 @@
         <v>1.0</v>
       </c>
       <c r="C493" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D493" s="14">
         <v>7.494285001E9</v>
@@ -34463,13 +34440,13 @@
     </row>
     <row r="494">
       <c r="A494" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B494" s="13">
         <v>1.0</v>
       </c>
       <c r="C494" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D494" s="14">
         <v>7.494285001E9</v>
@@ -34486,13 +34463,13 @@
     </row>
     <row r="495">
       <c r="A495" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B495" s="10">
         <v>1.0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D495" s="14">
         <v>7.494285001E9</v>
@@ -34516,7 +34493,7 @@
     </row>
     <row r="497">
       <c r="A497" s="39" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B497" s="53"/>
       <c r="C497" s="53"/>
@@ -34531,13 +34508,13 @@
     </row>
     <row r="498">
       <c r="A498" s="29" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B498" s="13">
         <v>1.0</v>
       </c>
       <c r="C498" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D498" s="13">
         <v>8.03359479E9</v>
@@ -34554,13 +34531,13 @@
     </row>
     <row r="499">
       <c r="A499" s="29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B499" s="13">
         <v>1.0</v>
       </c>
       <c r="C499" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D499" s="13">
         <v>8.033510345E9</v>
@@ -34577,13 +34554,13 @@
     </row>
     <row r="500">
       <c r="A500" s="29" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B500" s="13">
         <v>1.0</v>
       </c>
       <c r="C500" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D500" s="13">
         <v>7.061817517E9</v>
@@ -34600,13 +34577,13 @@
     </row>
     <row r="501">
       <c r="A501" s="29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B501" s="13">
         <v>1.0</v>
       </c>
       <c r="C501" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D501" s="13">
         <v>8.035350809E9</v>
@@ -34623,13 +34600,13 @@
     </row>
     <row r="502">
       <c r="A502" s="29" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B502" s="13">
         <v>1.0</v>
       </c>
       <c r="C502" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D502" s="13">
         <v>8.036156051E9</v>
@@ -34661,13 +34638,13 @@
     </row>
     <row r="503">
       <c r="A503" s="29" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B503" s="13">
         <v>1.0</v>
       </c>
       <c r="C503" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D503" s="13">
         <v>7.060648613E9</v>
@@ -34684,13 +34661,13 @@
     </row>
     <row r="504">
       <c r="A504" s="29" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B504" s="13">
         <v>1.0</v>
       </c>
       <c r="C504" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D504" s="13">
         <v>7.060648613E9</v>
@@ -34707,13 +34684,13 @@
     </row>
     <row r="505">
       <c r="A505" s="29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B505" s="13">
         <v>1.0</v>
       </c>
       <c r="C505" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D505" s="13">
         <v>8.027322242E9</v>
@@ -34730,13 +34707,13 @@
     </row>
     <row r="506">
       <c r="A506" s="29" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B506" s="13">
         <v>1.0</v>
       </c>
       <c r="C506" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D506" s="13">
         <v>2.022468441E9</v>
@@ -34753,13 +34730,13 @@
     </row>
     <row r="507">
       <c r="A507" s="29" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B507" s="13">
         <v>1.0</v>
       </c>
       <c r="C507" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D507" s="13">
         <v>8.184882788E9</v>
@@ -34789,7 +34766,7 @@
     </row>
     <row r="509">
       <c r="A509" s="24" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B509" s="25"/>
       <c r="C509" s="26"/>
@@ -34814,7 +34791,7 @@
         <v>1.0</v>
       </c>
       <c r="C511" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D511" s="14">
         <v>8.033016753E9</v>
@@ -34831,13 +34808,13 @@
     </row>
     <row r="512">
       <c r="A512" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B512" s="13">
         <v>1.0</v>
       </c>
       <c r="C512" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D512" s="14">
         <v>8.033016753E9</v>
@@ -34854,13 +34831,13 @@
     </row>
     <row r="513">
       <c r="A513" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B513" s="13">
         <v>1.0</v>
       </c>
       <c r="C513" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D513" s="14">
         <v>7.398843791E9</v>
@@ -34877,13 +34854,13 @@
     </row>
     <row r="514">
       <c r="A514" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B514" s="13">
         <v>1.0</v>
       </c>
       <c r="C514" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D514" s="14">
         <v>7.949394588E9</v>
@@ -34915,13 +34892,13 @@
     </row>
     <row r="515">
       <c r="A515" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B515" s="13">
         <v>1.0</v>
       </c>
       <c r="C515" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D515" s="14">
         <v>8.033263138E9</v>
@@ -34938,13 +34915,13 @@
     </row>
     <row r="516">
       <c r="A516" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B516" s="13">
         <v>1.0</v>
       </c>
       <c r="C516" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D516" s="14">
         <v>8.028996353E9</v>
@@ -34961,13 +34938,13 @@
     </row>
     <row r="517">
       <c r="A517" s="29" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B517" s="13">
         <v>1.0</v>
       </c>
       <c r="C517" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D517" s="14">
         <v>8.028996353E9</v>
@@ -34984,13 +34961,13 @@
     </row>
     <row r="518">
       <c r="A518" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B518" s="13">
         <v>1.0</v>
       </c>
       <c r="C518" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D518" s="14">
         <v>7.949394588E9</v>
@@ -35007,13 +34984,13 @@
     </row>
     <row r="519">
       <c r="A519" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B519" s="13">
         <v>1.0</v>
       </c>
       <c r="C519" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D519" s="14">
         <v>7.949394588E9</v>
@@ -35045,13 +35022,13 @@
     </row>
     <row r="520">
       <c r="A520" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B520" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C520" s="14" t="s">
         <v>555</v>
-      </c>
-      <c r="B520" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C520" s="14" t="s">
-        <v>554</v>
       </c>
       <c r="D520" s="14">
         <v>7.949394588E9</v>
@@ -35072,7 +35049,7 @@
     </row>
     <row r="522">
       <c r="A522" s="24" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B522" s="53"/>
       <c r="C522" s="28"/>
@@ -35087,13 +35064,13 @@
     </row>
     <row r="523">
       <c r="A523" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B523" s="13">
         <v>1.0</v>
       </c>
       <c r="C523" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D523" s="14">
         <v>7.791874716E9</v>
@@ -35110,13 +35087,13 @@
     </row>
     <row r="524">
       <c r="A524" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B524" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C524" s="14" t="s">
         <v>559</v>
-      </c>
-      <c r="B524" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C524" s="14" t="s">
-        <v>558</v>
       </c>
       <c r="D524" s="14">
         <v>8.056354495E9</v>
@@ -35133,13 +35110,13 @@
     </row>
     <row r="525">
       <c r="A525" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B525" s="13">
         <v>1.0</v>
       </c>
       <c r="C525" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D525" s="14">
         <v>7.411035443E9</v>
@@ -35156,13 +35133,13 @@
     </row>
     <row r="526">
       <c r="A526" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B526" s="13">
         <v>1.0</v>
       </c>
       <c r="C526" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D526" s="14">
         <v>8.165478317E9</v>
@@ -35179,13 +35156,13 @@
     </row>
     <row r="527">
       <c r="A527" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B527" s="13">
         <v>1.0</v>
       </c>
       <c r="C527" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D527" s="14">
         <v>7.910836315E9</v>
@@ -35217,13 +35194,13 @@
     </row>
     <row r="528">
       <c r="A528" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B528" s="13">
         <v>1.0</v>
       </c>
       <c r="C528" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D528" s="14">
         <v>7.398843791E9</v>
@@ -35240,13 +35217,13 @@
     </row>
     <row r="529">
       <c r="A529" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="B529" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C529" s="14" t="s">
         <v>565</v>
-      </c>
-      <c r="B529" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C529" s="14" t="s">
-        <v>564</v>
       </c>
       <c r="D529" s="10">
         <v>7.398843791E9</v>
@@ -35263,13 +35240,13 @@
     </row>
     <row r="530">
       <c r="A530" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B530" s="10">
         <v>1.0</v>
       </c>
       <c r="C530" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D530" s="10">
         <v>7.398843791E9</v>
@@ -35286,13 +35263,13 @@
     </row>
     <row r="531">
       <c r="A531" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B531" s="10">
         <v>1.0</v>
       </c>
       <c r="C531" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D531" s="10">
         <v>7.398843791E9</v>
@@ -35309,13 +35286,13 @@
     </row>
     <row r="532">
       <c r="A532" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B532" s="13">
         <v>1.0</v>
       </c>
       <c r="C532" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D532" s="13">
         <v>8.078753239E9</v>
@@ -35345,7 +35322,7 @@
     </row>
     <row r="534">
       <c r="A534" s="47" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B534" s="48"/>
       <c r="C534" s="48"/>
@@ -35360,13 +35337,13 @@
     </row>
     <row r="535">
       <c r="A535" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B535" s="13">
         <v>1.0</v>
       </c>
       <c r="C535" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D535" s="14">
         <v>8.034044331E9</v>
@@ -35383,13 +35360,13 @@
     </row>
     <row r="536">
       <c r="A536" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B536" s="13">
         <v>1.0</v>
       </c>
       <c r="C536" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D536" s="14">
         <v>8.024662308E9</v>
@@ -35421,13 +35398,13 @@
     </row>
     <row r="537">
       <c r="A537" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B537" s="13">
         <v>1.0</v>
       </c>
       <c r="C537" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D537" s="14">
         <v>8.03372284E9</v>
@@ -35459,13 +35436,13 @@
     </row>
     <row r="538">
       <c r="A538" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B538" s="13">
         <v>1.0</v>
       </c>
       <c r="C538" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D538" s="14">
         <v>8.023136659E9</v>
@@ -35482,13 +35459,13 @@
     </row>
     <row r="539">
       <c r="A539" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B539" s="13">
         <v>1.0</v>
       </c>
       <c r="C539" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D539" s="14">
         <v>8.023414386E9</v>
@@ -35505,13 +35482,13 @@
     </row>
     <row r="540">
       <c r="A540" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B540" s="13">
         <v>1.0</v>
       </c>
       <c r="C540" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D540" s="14">
         <v>8.035715044E9</v>
@@ -35528,13 +35505,13 @@
     </row>
     <row r="541">
       <c r="A541" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B541" s="13">
         <v>1.0</v>
       </c>
       <c r="C541" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D541" s="14">
         <v>8.035715044E9</v>
@@ -35551,13 +35528,13 @@
     </row>
     <row r="542">
       <c r="A542" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B542" s="13">
         <v>1.0</v>
       </c>
       <c r="C542" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D542" s="14">
         <v>7.017822252E9</v>
@@ -35574,13 +35551,13 @@
     </row>
     <row r="543">
       <c r="A543" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B543" s="13">
         <v>1.0</v>
       </c>
       <c r="C543" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D543" s="14">
         <v>8.033151449E9</v>
@@ -35597,13 +35574,13 @@
     </row>
     <row r="544">
       <c r="A544" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B544" s="13">
         <v>1.0</v>
       </c>
       <c r="C544" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D544" s="14">
         <v>8.03407192E9</v>
@@ -35632,7 +35609,7 @@
     </row>
     <row r="546">
       <c r="A546" s="54" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B546" s="25"/>
       <c r="C546" s="26"/>
@@ -35647,13 +35624,13 @@
     </row>
     <row r="547">
       <c r="A547" s="55" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B547" s="56">
         <v>1.0</v>
       </c>
       <c r="C547" s="41" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D547" s="41">
         <v>8.136664029E9</v>
@@ -35685,13 +35662,13 @@
     </row>
     <row r="548">
       <c r="A548" s="55" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B548" s="56">
         <v>1.0</v>
       </c>
       <c r="C548" s="41" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D548" s="41">
         <v>8.136664029E9</v>
@@ -35723,13 +35700,13 @@
     </row>
     <row r="549">
       <c r="A549" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B549" s="13">
         <v>1.0</v>
       </c>
       <c r="C549" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D549" s="14">
         <v>9.097029083E9</v>
@@ -35746,13 +35723,13 @@
     </row>
     <row r="550">
       <c r="A550" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B550" s="13">
         <v>1.0</v>
       </c>
       <c r="C550" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D550" s="14">
         <v>9.097029083E9</v>
@@ -35769,13 +35746,13 @@
     </row>
     <row r="551">
       <c r="A551" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B551" s="13">
         <v>1.0</v>
       </c>
       <c r="C551" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D551" s="14">
         <v>8.023368979E9</v>
@@ -35792,13 +35769,13 @@
     </row>
     <row r="552">
       <c r="A552" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B552" s="13">
         <v>1.0</v>
       </c>
       <c r="C552" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D552" s="14">
         <v>8.023368979E9</v>
@@ -35821,7 +35798,7 @@
         <v>1.0</v>
       </c>
       <c r="C553" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D553" s="14">
         <v>8.033168467E9</v>
@@ -35838,13 +35815,13 @@
     </row>
     <row r="554">
       <c r="A554" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B554" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C554" s="14" t="s">
         <v>589</v>
-      </c>
-      <c r="B554" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C554" s="14" t="s">
-        <v>588</v>
       </c>
       <c r="D554" s="14">
         <v>8.033168467E9</v>
@@ -35861,13 +35838,13 @@
     </row>
     <row r="555">
       <c r="A555" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B555" s="10">
         <v>1.0</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D555" s="10">
         <v>7.961023865E9</v>
@@ -35884,13 +35861,13 @@
     </row>
     <row r="556">
       <c r="A556" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B556" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C556" s="10" t="s">
         <v>549</v>
-      </c>
-      <c r="B556" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C556" s="10" t="s">
-        <v>548</v>
       </c>
       <c r="D556" s="10">
         <v>7.961023865E9</v>
@@ -35907,7 +35884,7 @@
     </row>
     <row r="557">
       <c r="A557" s="24" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B557" s="25"/>
       <c r="C557" s="26"/>
@@ -35922,13 +35899,13 @@
     </row>
     <row r="558">
       <c r="A558" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B558" s="13">
         <v>1.0</v>
       </c>
       <c r="C558" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D558" s="9">
         <v>8.033269954E9</v>
@@ -35945,13 +35922,13 @@
     </row>
     <row r="559">
       <c r="A559" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B559" s="13">
         <v>1.0</v>
       </c>
       <c r="C559" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D559" s="14">
         <v>8.023154013E9</v>
@@ -35974,7 +35951,7 @@
         <v>2.0</v>
       </c>
       <c r="C560" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D560" s="14">
         <v>8.033047088E9</v>
@@ -35991,13 +35968,13 @@
     </row>
     <row r="561">
       <c r="A561" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B561" s="13">
         <v>1.0</v>
       </c>
       <c r="C561" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D561" s="14">
         <v>8.023221192E9</v>
@@ -36014,13 +35991,13 @@
     </row>
     <row r="562">
       <c r="A562" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B562" s="13">
         <v>1.0</v>
       </c>
       <c r="C562" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D562" s="14">
         <v>8.0330693389E10</v>
@@ -36043,7 +36020,7 @@
         <v>2.0</v>
       </c>
       <c r="C563" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D563" s="14">
         <v>8.037404128E9</v>
@@ -36066,10 +36043,10 @@
         <v>2.0</v>
       </c>
       <c r="C564" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D564" s="14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E564" s="14">
         <v>1.0</v>
@@ -36096,7 +36073,7 @@
     </row>
     <row r="566">
       <c r="A566" s="24" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B566" s="25"/>
       <c r="C566" s="26"/>
@@ -36117,7 +36094,7 @@
         <v>2.0</v>
       </c>
       <c r="C567" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D567" s="14">
         <v>8.023230526E9</v>
@@ -36155,7 +36132,7 @@
         <v>2.0</v>
       </c>
       <c r="C568" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D568" s="14">
         <v>7.053152586E9</v>
@@ -36178,7 +36155,7 @@
         <v>2.0</v>
       </c>
       <c r="C569" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D569" s="14">
         <v>8.034360992E9</v>
@@ -36201,7 +36178,7 @@
         <v>2.0</v>
       </c>
       <c r="C570" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D570" s="14">
         <v>8.09944006E9</v>
@@ -36224,7 +36201,7 @@
         <v>2.0</v>
       </c>
       <c r="C571" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D571" s="14">
         <v>8.089886511E9</v>
@@ -36254,7 +36231,7 @@
     </row>
     <row r="573">
       <c r="A573" s="24" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B573" s="25"/>
       <c r="C573" s="26"/>
@@ -36284,13 +36261,13 @@
     </row>
     <row r="574">
       <c r="A574" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B574" s="13">
         <v>1.0</v>
       </c>
       <c r="C574" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D574" s="14">
         <v>8.092731761E9</v>
@@ -36307,13 +36284,13 @@
     </row>
     <row r="575">
       <c r="A575" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B575" s="13">
         <v>1.0</v>
       </c>
       <c r="C575" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D575" s="14">
         <v>8.033329207E9</v>
@@ -36330,13 +36307,13 @@
     </row>
     <row r="576">
       <c r="A576" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B576" s="13">
         <v>1.0</v>
       </c>
       <c r="C576" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D576" s="14">
         <v>8.023057851E9</v>
@@ -36353,13 +36330,13 @@
     </row>
     <row r="577">
       <c r="A577" s="12" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B577" s="13">
         <v>1.0</v>
       </c>
       <c r="C577" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D577" s="14">
         <v>8.023057851E9</v>
@@ -36376,13 +36353,13 @@
     </row>
     <row r="578">
       <c r="A578" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B578" s="13">
         <v>1.0</v>
       </c>
       <c r="C578" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D578" s="14">
         <v>8.029726428E9</v>
@@ -36399,13 +36376,13 @@
     </row>
     <row r="579">
       <c r="A579" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B579" s="13">
         <v>1.0</v>
       </c>
       <c r="C579" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D579" s="14">
         <v>8.092902312E9</v>
@@ -36422,13 +36399,13 @@
     </row>
     <row r="580">
       <c r="A580" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B580" s="13">
         <v>1.0</v>
       </c>
       <c r="C580" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D580" s="14">
         <v>8.023551119E9</v>
@@ -36445,13 +36422,13 @@
     </row>
     <row r="581">
       <c r="A581" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B581" s="13">
         <v>1.0</v>
       </c>
       <c r="C581" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D581" s="14">
         <v>8.023551119E9</v>
@@ -36468,13 +36445,13 @@
     </row>
     <row r="582">
       <c r="A582" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B582" s="13">
         <v>1.0</v>
       </c>
       <c r="C582" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D582" s="13">
         <v>8.023012426E9</v>
@@ -36491,13 +36468,13 @@
     </row>
     <row r="583">
       <c r="A583" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B583" s="13">
         <v>1.0</v>
       </c>
       <c r="C583" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D583" s="14">
         <v>8.023506307E9</v>
@@ -36514,7 +36491,7 @@
     </row>
     <row r="584">
       <c r="A584" s="24" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B584" s="25"/>
       <c r="C584" s="26"/>
@@ -36544,13 +36521,13 @@
     </row>
     <row r="585">
       <c r="A585" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B585" s="13">
         <v>1.0</v>
       </c>
       <c r="C585" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D585" s="13">
         <v>8.182612222E9</v>
@@ -36567,13 +36544,13 @@
     </row>
     <row r="586">
       <c r="A586" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B586" s="13">
         <v>1.0</v>
       </c>
       <c r="C586" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D586" s="13">
         <v>8.182612222E9</v>
@@ -36590,13 +36567,13 @@
     </row>
     <row r="587">
       <c r="A587" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B587" s="13">
         <v>1.0</v>
       </c>
       <c r="C587" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D587" s="13">
         <v>8.026656748E9</v>
@@ -36613,13 +36590,13 @@
     </row>
     <row r="588">
       <c r="A588" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B588" s="13">
         <v>1.0</v>
       </c>
       <c r="C588" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D588" s="13">
         <v>8.023316251E9</v>
@@ -36636,13 +36613,13 @@
     </row>
     <row r="589">
       <c r="A589" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B589" s="13">
         <v>1.0</v>
       </c>
       <c r="C589" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D589" s="13">
         <v>8.023316251E9</v>
@@ -36659,13 +36636,13 @@
     </row>
     <row r="590">
       <c r="A590" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B590" s="13">
         <v>1.0</v>
       </c>
       <c r="C590" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D590" s="13">
         <v>7.467166671E9</v>
@@ -36682,13 +36659,13 @@
     </row>
     <row r="591">
       <c r="A591" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B591" s="13">
         <v>1.0</v>
       </c>
       <c r="C591" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D591" s="13">
         <v>7.467166671E9</v>
@@ -36751,13 +36728,13 @@
     </row>
     <row r="594">
       <c r="A594" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B594" s="13">
         <v>1.0</v>
       </c>
       <c r="C594" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D594" s="14">
         <v>8.06298339E9</v>
@@ -36787,7 +36764,7 @@
     </row>
     <row r="596">
       <c r="A596" s="47" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B596" s="48"/>
       <c r="C596" s="48"/>
@@ -36802,13 +36779,13 @@
     </row>
     <row r="597">
       <c r="A597" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B597" s="13">
         <v>1.0</v>
       </c>
       <c r="C597" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D597" s="14">
         <v>8.023005676E9</v>
@@ -36825,13 +36802,13 @@
     </row>
     <row r="598">
       <c r="A598" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B598" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C598" s="14" t="s">
         <v>642</v>
-      </c>
-      <c r="B598" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C598" s="14" t="s">
-        <v>641</v>
       </c>
       <c r="D598" s="14">
         <v>8.0233004E9</v>
@@ -36848,13 +36825,13 @@
     </row>
     <row r="599">
       <c r="A599" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B599" s="13">
         <v>1.0</v>
       </c>
       <c r="C599" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D599" s="14">
         <v>9.115911396E9</v>
@@ -36871,13 +36848,13 @@
     </row>
     <row r="600">
       <c r="A600" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B600" s="13">
         <v>1.0</v>
       </c>
       <c r="C600" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D600" s="14">
         <v>8.027352376E9</v>
@@ -36894,13 +36871,13 @@
     </row>
     <row r="601">
       <c r="A601" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B601" s="13">
         <v>1.0</v>
       </c>
       <c r="C601" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D601" s="14">
         <v>8.163341596E9</v>
@@ -36932,13 +36909,13 @@
     </row>
     <row r="602">
       <c r="A602" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B602" s="13">
         <v>1.0</v>
       </c>
       <c r="C602" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D602" s="14">
         <v>8.078245569E9</v>
@@ -36955,13 +36932,13 @@
     </row>
     <row r="603">
       <c r="A603" s="29" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B603" s="13">
         <v>1.0</v>
       </c>
       <c r="C603" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D603" s="14">
         <v>8.06298339E9</v>
@@ -36978,13 +36955,13 @@
     </row>
     <row r="604">
       <c r="A604" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B604" s="13">
         <v>1.0</v>
       </c>
       <c r="C604" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D604" s="14">
         <v>7.061041417E9</v>
@@ -37001,13 +36978,13 @@
     </row>
     <row r="605">
       <c r="A605" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B605" s="13">
         <v>1.0</v>
       </c>
       <c r="C605" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D605" s="14">
         <v>7.061041417E9</v>
@@ -37024,13 +37001,13 @@
     </row>
     <row r="606">
       <c r="A606" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B606" s="13">
         <v>1.0</v>
       </c>
       <c r="C606" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D606" s="14">
         <v>8.062316717E9</v>
@@ -37047,13 +37024,13 @@
     </row>
     <row r="607">
       <c r="A607" s="29" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B607" s="13">
         <v>1.0</v>
       </c>
       <c r="C607" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D607" s="14">
         <v>8.023270405E9</v>
@@ -37083,7 +37060,7 @@
     </row>
     <row r="609">
       <c r="A609" s="47" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B609" s="48"/>
       <c r="C609" s="48"/>
@@ -37113,13 +37090,13 @@
     </row>
     <row r="610">
       <c r="A610" s="29" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B610" s="13">
         <v>1.0</v>
       </c>
       <c r="C610" s="13" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D610" s="14">
         <v>8.038500818E9</v>
@@ -37136,13 +37113,13 @@
     </row>
     <row r="611">
       <c r="A611" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="B611" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="C611" s="13" t="s">
         <v>656</v>
-      </c>
-      <c r="B611" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="C611" s="13" t="s">
-        <v>655</v>
       </c>
       <c r="D611" s="14">
         <v>7.030260852E9</v>
@@ -37159,13 +37136,13 @@
     </row>
     <row r="612">
       <c r="A612" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B612" s="13">
         <v>1.0</v>
       </c>
       <c r="C612" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D612" s="14">
         <v>7.055444156E9</v>
@@ -37182,13 +37159,13 @@
     </row>
     <row r="613">
       <c r="A613" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B613" s="13">
         <v>1.0</v>
       </c>
       <c r="C613" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D613" s="14">
         <v>8.032022492E9</v>
@@ -37205,13 +37182,13 @@
     </row>
     <row r="614">
       <c r="A614" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B614" s="13">
         <v>1.0</v>
       </c>
       <c r="C614" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D614" s="14">
         <v>8.023105729E9</v>
@@ -37228,13 +37205,13 @@
     </row>
     <row r="615">
       <c r="A615" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B615" s="13">
         <v>1.0</v>
       </c>
       <c r="C615" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D615" s="14">
         <v>9.134050297E9</v>
@@ -37266,13 +37243,13 @@
     </row>
     <row r="616">
       <c r="A616" s="9" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B616" s="10">
         <v>1.0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D616" s="10">
         <v>9.090140109E9</v>
@@ -37283,13 +37260,13 @@
     </row>
     <row r="617">
       <c r="A617" s="29" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B617" s="13">
         <v>1.0</v>
       </c>
       <c r="C617" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D617" s="13">
         <v>8.035126889E9</v>
@@ -37306,13 +37283,13 @@
     </row>
     <row r="618">
       <c r="A618" s="29" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B618" s="13">
         <v>1.0</v>
       </c>
       <c r="C618" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D618" s="14">
         <v>8.035023802E9</v>
@@ -37329,13 +37306,13 @@
     </row>
     <row r="619">
       <c r="A619" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B619" s="13">
         <v>1.0</v>
       </c>
       <c r="C619" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D619" s="13">
         <v>8.056835983E9</v>
@@ -37365,7 +37342,7 @@
     </row>
     <row r="621">
       <c r="A621" s="24" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B621" s="25"/>
       <c r="C621" s="26"/>
@@ -37380,13 +37357,13 @@
     </row>
     <row r="622">
       <c r="A622" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B622" s="13">
         <v>1.0</v>
       </c>
       <c r="C622" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D622" s="14">
         <v>9.081192203E9</v>
@@ -37403,13 +37380,13 @@
     </row>
     <row r="623">
       <c r="A623" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B623" s="13">
         <v>1.0</v>
       </c>
       <c r="C623" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D623" s="14">
         <v>9.15430212E9</v>
@@ -37426,13 +37403,13 @@
     </row>
     <row r="624">
       <c r="A624" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B624" s="13">
         <v>1.0</v>
       </c>
       <c r="C624" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D624" s="14">
         <v>9.15430212E9</v>
@@ -37449,13 +37426,13 @@
     </row>
     <row r="625">
       <c r="A625" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B625" s="13">
         <v>1.0</v>
       </c>
       <c r="C625" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D625" s="14">
         <v>8.023224437E9</v>
@@ -37472,13 +37449,13 @@
     </row>
     <row r="626">
       <c r="A626" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B626" s="13">
         <v>1.0</v>
       </c>
       <c r="C626" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D626" s="14">
         <v>8.023224437E9</v>
@@ -37495,13 +37472,13 @@
     </row>
     <row r="627">
       <c r="A627" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B627" s="13">
         <v>1.0</v>
       </c>
       <c r="C627" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D627" s="14">
         <v>8.056838983E9</v>
@@ -37518,13 +37495,13 @@
     </row>
     <row r="628">
       <c r="A628" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B628" s="13">
         <v>1.0</v>
       </c>
       <c r="C628" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D628" s="14">
         <v>8.030434094E9</v>
@@ -37541,13 +37518,13 @@
     </row>
     <row r="629">
       <c r="A629" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B629" s="13">
         <v>1.0</v>
       </c>
       <c r="C629" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D629" s="14">
         <v>8.030434094E9</v>
@@ -37564,13 +37541,13 @@
     </row>
     <row r="630">
       <c r="A630" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B630" s="13">
         <v>1.0</v>
       </c>
       <c r="C630" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D630" s="14">
         <v>8.023163719E9</v>
@@ -37587,13 +37564,13 @@
     </row>
     <row r="631">
       <c r="A631" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B631" s="13">
         <v>1.0</v>
       </c>
       <c r="C631" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D631" s="14">
         <v>8.023163719E9</v>
@@ -37623,7 +37600,7 @@
     </row>
     <row r="633">
       <c r="A633" s="47" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B633" s="48"/>
       <c r="C633" s="48"/>
@@ -37653,13 +37630,13 @@
     </row>
     <row r="634">
       <c r="A634" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B634" s="13">
         <v>1.0</v>
       </c>
       <c r="C634" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D634" s="14">
         <v>8.183103038E9</v>
@@ -37682,7 +37659,7 @@
         <v>1.0</v>
       </c>
       <c r="C635" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D635" s="14">
         <v>7.03521206E9</v>
@@ -37699,13 +37676,13 @@
     </row>
     <row r="636">
       <c r="A636" s="12" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B636" s="13">
         <v>1.0</v>
       </c>
       <c r="C636" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D636" s="14">
         <v>7.03521206E9</v>
@@ -42607,7 +42584,7 @@
         <v>1.0</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>717</v>
@@ -42628,7 +42605,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>717</v>
